--- a/outputs/Stack-and-reuse/Supplementary-Tables/Supplementary-Tables.xlsx
+++ b/outputs/Stack-and-reuse/Supplementary-Tables/Supplementary-Tables.xlsx
@@ -2,28 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Contents" sheetId="1" ns1:id="R82e280c1b4da45e1"/>
-    <sheet name="S1" sheetId="2" ns1:id="Rb6a71b4e8df14235"/>
-    <sheet name="S2" sheetId="3" ns1:id="Readb62ee0ea94b9f"/>
-    <sheet name="S3" sheetId="4" ns1:id="R8f34902a0200413f"/>
-    <sheet name="S4" sheetId="5" ns1:id="R66125205199b4870"/>
-    <sheet name="S5" sheetId="6" ns1:id="R8a219f84853743c1"/>
-    <sheet name="S6" sheetId="7" ns1:id="R837a5cc97be245ad"/>
-    <sheet name="S7" sheetId="8" ns1:id="Rff59ebb8410040df"/>
-    <sheet name="S8" sheetId="9" ns1:id="R77122782ff35445d"/>
-    <sheet name="S9" sheetId="10" ns1:id="R733bb6553b1c416b"/>
-    <sheet name="S10" sheetId="11" ns1:id="Rcf064bd52f174d89"/>
-    <sheet name="S11" sheetId="12" ns1:id="R23fb34b8c8fd4b95"/>
-    <sheet name="S12" sheetId="13" ns1:id="R47ccebe2b6ac48db"/>
-    <sheet name="S13" sheetId="14" ns1:id="R25ca4b481771426a"/>
-    <sheet name="S14" sheetId="15" ns1:id="Rab664efbdb7f49b6"/>
-    <sheet name="S15" sheetId="16" ns1:id="R0480ea6cc2eb46ea"/>
-    <sheet name="S16" sheetId="17" ns1:id="R6c757732c92f43db"/>
-    <sheet name="S17" sheetId="18" ns1:id="Ra8ce02b0a8594123"/>
-    <sheet name="S18" sheetId="19" ns1:id="Rf23fa33d2caf4ba8"/>
-    <sheet name="S19" sheetId="20" ns1:id="R0139828233134f9d"/>
-    <sheet name="S20" sheetId="21" ns1:id="Rbbde81ac78b34853"/>
-    <sheet name="S21" sheetId="22" ns1:id="R2edae463e8ec4270"/>
+    <sheet name="Contents" sheetId="1" ns1:id="R6faf48ee4f364b35"/>
+    <sheet name="S1" sheetId="2" ns1:id="Rcd735eb6b43c4442"/>
+    <sheet name="S2" sheetId="3" ns1:id="R882e083dbfe14dcf"/>
+    <sheet name="S3" sheetId="4" ns1:id="R28603e94d4b34147"/>
+    <sheet name="S4" sheetId="5" ns1:id="R668eaa974e3847b8"/>
+    <sheet name="S5" sheetId="6" ns1:id="R2464c7afd8814c49"/>
+    <sheet name="S6" sheetId="7" ns1:id="Rccc85357321e47e6"/>
+    <sheet name="S7" sheetId="8" ns1:id="R2f4e0b8dc1664135"/>
+    <sheet name="S8" sheetId="9" ns1:id="R4019d84ede8e4df4"/>
+    <sheet name="S9" sheetId="10" ns1:id="R16576041fed145ad"/>
+    <sheet name="S10" sheetId="11" ns1:id="Rf4abb955d2fb4ff2"/>
+    <sheet name="S11" sheetId="12" ns1:id="Readd855356344af7"/>
+    <sheet name="S12" sheetId="13" ns1:id="Rfbcdc0595a414ca5"/>
+    <sheet name="S13" sheetId="14" ns1:id="R332fe6b4352f4ae7"/>
+    <sheet name="S14" sheetId="15" ns1:id="R688aec16cc6d4268"/>
+    <sheet name="S15" sheetId="16" ns1:id="R393e235bfd4c4d58"/>
+    <sheet name="S16" sheetId="17" ns1:id="R2ac501d5f0404483"/>
+    <sheet name="S17" sheetId="18" ns1:id="Rc82c2ce9784e444a"/>
+    <sheet name="S18" sheetId="19" ns1:id="R8e7840fc83d1460e"/>
+    <sheet name="S19" sheetId="20" ns1:id="R75d9ab5c37614f48"/>
+    <sheet name="S20" sheetId="21" ns1:id="Ra14b4444d04f4586"/>
+    <sheet name="S21" sheetId="22" ns1:id="R65d4599f1e8443b0"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Contents'!$B$2:$E$35</definedName>
@@ -224,7 +224,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="110">
+  <x:cellXfs count="120">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -492,6 +492,78 @@
     <x:xf numFmtId="201" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
     <x:xf numFmtId="207" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
@@ -546,6 +618,14 @@
     <x:xf numFmtId="208" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="0"/>
     </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
     <x:xf numFmtId="202" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="0"/>
     </x:xf>
@@ -589,6 +669,23 @@
     </x:dxf>
   </x:dxfs>
 </x:styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2611,7 +2708,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS9&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="R7ef9b16751834ccc"/>
+    <tablePart ns1:id="R951ee0b987804f2c"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2766,19 +2863,19 @@
       <c r="E8" s="58" t="str">
         <v>Byonic, Comet, Mascot, MaxQuant, OpenMS, PEAKS, PLGS, PeptideShaker, Progenesis, ProteinPilot, Proteome Discoverer, Scaffold, TPP, X!Tandem</v>
       </c>
-      <c r="F8" s="101" t="n">
+      <c r="F8" s="110" t="n">
         <v>15.41</v>
       </c>
-      <c r="G8" s="103" t="n">
+      <c r="G8" s="112" t="n">
         <v>13.75</v>
       </c>
-      <c r="H8" s="103" t="n">
+      <c r="H8" s="112" t="n">
         <v>17.58</v>
       </c>
-      <c r="I8" s="101" t="n">
+      <c r="I8" s="110" t="n">
         <v>40.49</v>
       </c>
-      <c r="J8" s="101" t="n">
+      <c r="J8" s="110" t="n">
         <v>31.36</v>
       </c>
       <c r="K8" s="3"/>
@@ -2797,19 +2894,19 @@
       <c r="E9" s="59" t="str">
         <v>MS-GF+, MetaMorpheus</v>
       </c>
-      <c r="F9" s="102" t="n">
+      <c r="F9" s="111" t="n">
         <v>54.86</v>
       </c>
-      <c r="G9" s="104" t="n">
+      <c r="G9" s="113" t="n">
         <v>43.86</v>
       </c>
-      <c r="H9" s="104" t="n">
+      <c r="H9" s="113" t="n">
         <v>66.42</v>
       </c>
-      <c r="I9" s="102" t="n">
+      <c r="I9" s="111" t="n">
         <v>68.75</v>
       </c>
-      <c r="J9" s="102" t="n">
+      <c r="J9" s="111" t="n">
         <v>4.17</v>
       </c>
       <c r="K9" s="3"/>
@@ -2828,19 +2925,19 @@
       <c r="E10" s="58" t="str">
         <v>DIA-NN, FragPipe, OpenSWATH, Percolator, Sage, Skyline, pFind</v>
       </c>
-      <c r="F10" s="101" t="n">
+      <c r="F10" s="110" t="n">
         <v>2.68</v>
       </c>
-      <c r="G10" s="103" t="n">
+      <c r="G10" s="112" t="n">
         <v>1.64</v>
       </c>
-      <c r="H10" s="103" t="n">
+      <c r="H10" s="112" t="n">
         <v>3.83</v>
       </c>
-      <c r="I10" s="101" t="n">
+      <c r="I10" s="110" t="n">
         <v>51.58</v>
       </c>
-      <c r="J10" s="101" t="n">
+      <c r="J10" s="110" t="n">
         <v>16.52</v>
       </c>
       <c r="K10" s="3"/>
@@ -2859,19 +2956,19 @@
       <c r="E11" s="66" t="str">
         <v>EncyclopeDIA, Spectronaut</v>
       </c>
-      <c r="F11" s="105" t="n">
+      <c r="F11" s="114" t="n">
         <v>0.4</v>
       </c>
-      <c r="G11" s="106" t="n">
+      <c r="G11" s="115" t="n">
         <v>0.09</v>
       </c>
-      <c r="H11" s="106" t="n">
+      <c r="H11" s="115" t="n">
         <v>0.82</v>
       </c>
-      <c r="I11" s="105" t="n">
+      <c r="I11" s="114" t="n">
         <v>56.82</v>
       </c>
-      <c r="J11" s="105" t="n">
+      <c r="J11" s="114" t="n">
         <v>8.5</v>
       </c>
       <c r="K11" s="3"/>
@@ -3235,7 +3332,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS10&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="Rdf9fdd9f537b4b65"/>
+    <tablePart ns1:id="R93310e9a8fda4149"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4396,7 +4493,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS11&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="Rc7615e603e7e4d41"/>
+    <tablePart ns1:id="Rc6a145580d09437a"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4522,13 +4619,13 @@
       <c r="B8" s="58" t="str">
         <v>MaxQuant 1.6</v>
       </c>
-      <c r="C8" s="101" t="n">
+      <c r="C8" s="110" t="n">
         <v>40.17</v>
       </c>
-      <c r="D8" s="103" t="n">
+      <c r="D8" s="112" t="n">
         <v>34.27</v>
       </c>
-      <c r="E8" s="103" t="n">
+      <c r="E8" s="112" t="n">
         <v>46.58</v>
       </c>
       <c r="F8" s="44" t="n">
@@ -4547,13 +4644,13 @@
       <c r="B9" s="59" t="str">
         <v>MaxQuant 1.x</v>
       </c>
-      <c r="C9" s="102" t="n">
+      <c r="C9" s="111" t="n">
         <v>45.98</v>
       </c>
-      <c r="D9" s="104" t="n">
+      <c r="D9" s="113" t="n">
         <v>40.21</v>
       </c>
-      <c r="E9" s="104" t="n">
+      <c r="E9" s="113" t="n">
         <v>52.45</v>
       </c>
       <c r="F9" s="45" t="n">
@@ -4572,13 +4669,13 @@
       <c r="B10" s="58" t="str">
         <v>DIA-NN 1.8</v>
       </c>
-      <c r="C10" s="101" t="n">
+      <c r="C10" s="110" t="n">
         <v>60.91</v>
       </c>
-      <c r="D10" s="103" t="n">
+      <c r="D10" s="112" t="n">
         <v>47.66</v>
       </c>
-      <c r="E10" s="103" t="n">
+      <c r="E10" s="112" t="n">
         <v>73.79</v>
       </c>
       <c r="F10" s="44" t="n">
@@ -4597,13 +4694,13 @@
       <c r="B11" s="59" t="str">
         <v>Proteome Discoverer 2.x</v>
       </c>
-      <c r="C11" s="102" t="n">
+      <c r="C11" s="111" t="n">
         <v>68.75</v>
       </c>
-      <c r="D11" s="104" t="n">
+      <c r="D11" s="113" t="n">
         <v>56.88</v>
       </c>
-      <c r="E11" s="104" t="n">
+      <c r="E11" s="113" t="n">
         <v>78.85</v>
       </c>
       <c r="F11" s="45" t="n">
@@ -4622,13 +4719,13 @@
       <c r="B12" s="76" t="str">
         <v>FragPipe 22</v>
       </c>
-      <c r="C12" s="107" t="n">
+      <c r="C12" s="116" t="n">
         <v>64.44</v>
       </c>
-      <c r="D12" s="108" t="n">
+      <c r="D12" s="117" t="n">
         <v>44.74</v>
       </c>
-      <c r="E12" s="108" t="n">
+      <c r="E12" s="117" t="n">
         <v>80.4</v>
       </c>
       <c r="F12" s="51" t="n">
@@ -4957,7 +5054,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS12&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="Rfc9a08decfd84997"/>
+    <tablePart ns1:id="R2e185cff09a148d6"/>
   </tableParts>
 </worksheet>
 </file>
@@ -5341,7 +5438,7 @@
         <v>1.5</v>
       </c>
       <c r="M11" s="49" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="N11" s="45" t="n">
         <v>1195</v>
@@ -5684,7 +5781,7 @@
         <v>1.9</v>
       </c>
       <c r="M18" s="48" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="N18" s="44" t="n">
         <v>4616</v>
@@ -6310,7 +6407,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS13&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="R15c3d2d330554e4b"/>
+    <tablePart ns1:id="Rfbc29a51654c47ce"/>
   </tableParts>
 </worksheet>
 </file>
@@ -6426,8 +6523,8 @@
       <c r="B8" s="58" t="str">
         <v>doc_readme</v>
       </c>
-      <c r="C8" s="58" t="str">
-        <v>True</v>
+      <c r="C8" s="97" t="b">
+        <v>1</v>
       </c>
       <c r="D8" s="44" t="n">
         <v>308</v>
@@ -6448,8 +6545,8 @@
       <c r="B9" s="59" t="str">
         <v>doc_readme</v>
       </c>
-      <c r="C9" s="59" t="str">
-        <v>False</v>
+      <c r="C9" s="98" t="b">
+        <v>0</v>
       </c>
       <c r="D9" s="45" t="n">
         <v>22044</v>
@@ -6470,8 +6567,8 @@
       <c r="B10" s="58" t="str">
         <v>doc_sdrf</v>
       </c>
-      <c r="C10" s="58" t="str">
-        <v>True</v>
+      <c r="C10" s="97" t="b">
+        <v>1</v>
       </c>
       <c r="D10" s="44" t="n">
         <v>367</v>
@@ -6492,8 +6589,8 @@
       <c r="B11" s="59" t="str">
         <v>doc_sdrf</v>
       </c>
-      <c r="C11" s="59" t="str">
-        <v>False</v>
+      <c r="C11" s="98" t="b">
+        <v>0</v>
       </c>
       <c r="D11" s="45" t="n">
         <v>21985</v>
@@ -6514,8 +6611,8 @@
       <c r="B12" s="58" t="str">
         <v>doc_design_author</v>
       </c>
-      <c r="C12" s="58" t="str">
-        <v>True</v>
+      <c r="C12" s="97" t="b">
+        <v>1</v>
       </c>
       <c r="D12" s="44" t="n">
         <v>1403</v>
@@ -6536,8 +6633,8 @@
       <c r="B13" s="59" t="str">
         <v>doc_design_author</v>
       </c>
-      <c r="C13" s="59" t="str">
-        <v>False</v>
+      <c r="C13" s="98" t="b">
+        <v>0</v>
       </c>
       <c r="D13" s="45" t="n">
         <v>20949</v>
@@ -6558,14 +6655,14 @@
       <c r="B14" s="58" t="str">
         <v>doc_params</v>
       </c>
-      <c r="C14" s="58" t="str">
-        <v>True</v>
+      <c r="C14" s="97" t="b">
+        <v>1</v>
       </c>
       <c r="D14" s="44" t="n">
-        <v>4056</v>
+        <v>4057</v>
       </c>
       <c r="E14" s="44" t="n">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="F14" s="48" t="n">
         <v>60.3</v>
@@ -6580,19 +6677,19 @@
       <c r="B15" s="66" t="str">
         <v>doc_params</v>
       </c>
-      <c r="C15" s="66" t="str">
-        <v>False</v>
+      <c r="C15" s="118" t="b">
+        <v>0</v>
       </c>
       <c r="D15" s="68" t="n">
-        <v>18296</v>
+        <v>18295</v>
       </c>
       <c r="E15" s="68" t="n">
-        <v>4283</v>
-      </c>
-      <c r="F15" s="109" t="n">
+        <v>4282</v>
+      </c>
+      <c r="F15" s="119" t="n">
         <v>9.3</v>
       </c>
-      <c r="G15" s="109" t="n">
+      <c r="G15" s="119" t="n">
         <v>18.5</v>
       </c>
       <c r="H15" s="3"/>
@@ -6887,7 +6984,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS14&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="R036c64681b1a47e9"/>
+    <tablePart ns1:id="R5f4e38ca00d9404d"/>
   </tableParts>
 </worksheet>
 </file>
@@ -7123,7 +7220,7 @@
         <v>[2.37, 2.6]</v>
       </c>
       <c r="H11" s="81" t="n">
-        <v>0.871</v>
+        <v>0.872</v>
       </c>
       <c r="I11" s="81" t="n">
         <v>0.613</v>
@@ -7610,7 +7707,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS15&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="R429f561e33374239"/>
+    <tablePart ns1:id="R30feec6dd44842c1"/>
   </tableParts>
 </worksheet>
 </file>
@@ -7805,7 +7902,7 @@
         <v>0.8317</v>
       </c>
       <c r="I8" s="82" t="n">
-        <v>0.8146</v>
+        <v>0.8143</v>
       </c>
       <c r="J8" s="82" t="n">
         <v>0.8454</v>
@@ -7814,10 +7911,10 @@
         <v>0.1644</v>
       </c>
       <c r="L8" s="82" t="n">
-        <v>0.1509</v>
+        <v>0.1508</v>
       </c>
       <c r="M8" s="82" t="n">
-        <v>0.181</v>
+        <v>0.1812</v>
       </c>
       <c r="N8" s="3"/>
     </row>
@@ -7845,19 +7942,19 @@
         <v>0.3285</v>
       </c>
       <c r="I9" s="83" t="n">
-        <v>0.3184</v>
+        <v>0.3185</v>
       </c>
       <c r="J9" s="83" t="n">
-        <v>0.3393</v>
+        <v>0.3389</v>
       </c>
       <c r="K9" s="81" t="n">
         <v>0.6156</v>
       </c>
       <c r="L9" s="83" t="n">
-        <v>0.6052</v>
+        <v>0.6055</v>
       </c>
       <c r="M9" s="83" t="n">
-        <v>0.6263</v>
+        <v>0.6256</v>
       </c>
       <c r="N9" s="3"/>
     </row>
@@ -7885,19 +7982,19 @@
         <v>0.3233</v>
       </c>
       <c r="I10" s="89" t="n">
-        <v>0.3148</v>
+        <v>0.3144</v>
       </c>
       <c r="J10" s="89" t="n">
-        <v>0.3323</v>
+        <v>0.3328</v>
       </c>
       <c r="K10" s="88" t="n">
         <v>0.6237</v>
       </c>
       <c r="L10" s="89" t="n">
-        <v>0.615</v>
+        <v>0.6146</v>
       </c>
       <c r="M10" s="89" t="n">
-        <v>0.6326</v>
+        <v>0.6329</v>
       </c>
       <c r="N10" s="3"/>
     </row>
@@ -8335,7 +8432,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS16&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="R4f85fa47917842c2"/>
+    <tablePart ns1:id="Rf4e5108588c742ff"/>
   </tableParts>
 </worksheet>
 </file>
@@ -8606,8 +8703,8 @@
       <c r="Q8" s="80" t="n">
         <v>0.08411</v>
       </c>
-      <c r="R8" s="58" t="str">
-        <v>False</v>
+      <c r="R8" s="97" t="b">
+        <v>0</v>
       </c>
       <c r="S8" s="3"/>
     </row>
@@ -8661,8 +8758,8 @@
       <c r="Q9" s="81" t="n">
         <v>0.03411</v>
       </c>
-      <c r="R9" s="59" t="str">
-        <v>True</v>
+      <c r="R9" s="98" t="b">
+        <v>1</v>
       </c>
       <c r="S9" s="3"/>
     </row>
@@ -8716,8 +8813,8 @@
       <c r="Q10" s="80" t="n">
         <v>0.03333</v>
       </c>
-      <c r="R10" s="58" t="str">
-        <v>True</v>
+      <c r="R10" s="97" t="b">
+        <v>1</v>
       </c>
       <c r="S10" s="3"/>
     </row>
@@ -8771,8 +8868,8 @@
       <c r="Q11" s="81" t="n">
         <v>0.03566</v>
       </c>
-      <c r="R11" s="59" t="str">
-        <v>False</v>
+      <c r="R11" s="98" t="b">
+        <v>0</v>
       </c>
       <c r="S11" s="3"/>
     </row>
@@ -8826,8 +8923,8 @@
       <c r="Q12" s="80" t="n">
         <v>0.02829</v>
       </c>
-      <c r="R12" s="58" t="str">
-        <v>False</v>
+      <c r="R12" s="97" t="b">
+        <v>0</v>
       </c>
       <c r="S12" s="3"/>
     </row>
@@ -8881,8 +8978,8 @@
       <c r="Q13" s="81" t="n">
         <v>0.01008</v>
       </c>
-      <c r="R13" s="59" t="str">
-        <v>True</v>
+      <c r="R13" s="98" t="b">
+        <v>1</v>
       </c>
       <c r="S13" s="3"/>
     </row>
@@ -8936,8 +9033,8 @@
       <c r="Q14" s="80" t="n">
         <v>0.01279</v>
       </c>
-      <c r="R14" s="58" t="str">
-        <v>False</v>
+      <c r="R14" s="97" t="b">
+        <v>0</v>
       </c>
       <c r="S14" s="3"/>
     </row>
@@ -8991,8 +9088,8 @@
       <c r="Q15" s="81" t="n">
         <v>0.00659</v>
       </c>
-      <c r="R15" s="59" t="str">
-        <v>True</v>
+      <c r="R15" s="98" t="b">
+        <v>1</v>
       </c>
       <c r="S15" s="3"/>
     </row>
@@ -9046,8 +9143,8 @@
       <c r="Q16" s="80" t="n">
         <v>0.01977</v>
       </c>
-      <c r="R16" s="58" t="str">
-        <v>False</v>
+      <c r="R16" s="97" t="b">
+        <v>0</v>
       </c>
       <c r="S16" s="3"/>
     </row>
@@ -9101,8 +9198,8 @@
       <c r="Q17" s="81" t="n">
         <v>0.02713</v>
       </c>
-      <c r="R17" s="59" t="str">
-        <v>False</v>
+      <c r="R17" s="98" t="b">
+        <v>0</v>
       </c>
       <c r="S17" s="3"/>
     </row>
@@ -9156,8 +9253,8 @@
       <c r="Q18" s="80" t="n">
         <v>0.0124</v>
       </c>
-      <c r="R18" s="58" t="str">
-        <v>False</v>
+      <c r="R18" s="97" t="b">
+        <v>0</v>
       </c>
       <c r="S18" s="3"/>
     </row>
@@ -9211,8 +9308,8 @@
       <c r="Q19" s="81" t="n">
         <v>0.00698</v>
       </c>
-      <c r="R19" s="59" t="str">
-        <v>False</v>
+      <c r="R19" s="98" t="b">
+        <v>0</v>
       </c>
       <c r="S19" s="3"/>
     </row>
@@ -9266,8 +9363,8 @@
       <c r="Q20" s="80" t="n">
         <v>0.00814</v>
       </c>
-      <c r="R20" s="58" t="str">
-        <v>False</v>
+      <c r="R20" s="97" t="b">
+        <v>0</v>
       </c>
       <c r="S20" s="3"/>
     </row>
@@ -9321,8 +9418,8 @@
       <c r="Q21" s="81" t="n">
         <v>0.00465</v>
       </c>
-      <c r="R21" s="59" t="str">
-        <v>False</v>
+      <c r="R21" s="98" t="b">
+        <v>0</v>
       </c>
       <c r="S21" s="3"/>
     </row>
@@ -9376,8 +9473,8 @@
       <c r="Q22" s="88" t="n">
         <v>0.00078</v>
       </c>
-      <c r="R22" s="76" t="str">
-        <v>False</v>
+      <c r="R22" s="99" t="b">
+        <v>0</v>
       </c>
       <c r="S22" s="3"/>
     </row>
@@ -9946,7 +10043,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS17&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="Rf1ab6ede5d934428"/>
+    <tablePart ns1:id="R3e1f851e96244e95"/>
   </tableParts>
 </worksheet>
 </file>
@@ -10923,7 +11020,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS18&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="Rb891a47ca33844d2"/>
+    <tablePart ns1:id="Rbb122c67b0d34abc"/>
   </tableParts>
 </worksheet>
 </file>
@@ -12054,7 +12151,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS1&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="R9c8afd3dfccd46a0"/>
+    <tablePart ns1:id="Rbd7f472a9ec94ed9"/>
   </tableParts>
 </worksheet>
 </file>
@@ -12199,16 +12296,16 @@
       <c r="E8" s="44" t="n">
         <v>20684</v>
       </c>
-      <c r="F8" s="101" t="n">
+      <c r="F8" s="110" t="n">
         <v>2.34</v>
       </c>
-      <c r="G8" s="101" t="n">
+      <c r="G8" s="110" t="n">
         <v>2.34</v>
       </c>
-      <c r="H8" s="103" t="n">
+      <c r="H8" s="112" t="n">
         <v>2.07</v>
       </c>
-      <c r="I8" s="103" t="n">
+      <c r="I8" s="112" t="n">
         <v>2.63</v>
       </c>
       <c r="J8" s="3"/>
@@ -12227,16 +12324,16 @@
       <c r="E9" s="45" t="n">
         <v>3793</v>
       </c>
-      <c r="F9" s="102" t="n">
+      <c r="F9" s="111" t="n">
         <v>2.11</v>
       </c>
-      <c r="G9" s="102" t="n">
+      <c r="G9" s="111" t="n">
         <v>2.09</v>
       </c>
-      <c r="H9" s="104" t="n">
+      <c r="H9" s="113" t="n">
         <v>1.56</v>
       </c>
-      <c r="I9" s="104" t="n">
+      <c r="I9" s="113" t="n">
         <v>2.66</v>
       </c>
       <c r="J9" s="3"/>
@@ -12255,16 +12352,16 @@
       <c r="E10" s="44" t="n">
         <v>16891</v>
       </c>
-      <c r="F10" s="101" t="n">
+      <c r="F10" s="110" t="n">
         <v>2.39</v>
       </c>
-      <c r="G10" s="101" t="n">
+      <c r="G10" s="110" t="n">
         <v>2.38</v>
       </c>
-      <c r="H10" s="103" t="n">
+      <c r="H10" s="112" t="n">
         <v>2.07</v>
       </c>
-      <c r="I10" s="103" t="n">
+      <c r="I10" s="112" t="n">
         <v>2.72</v>
       </c>
       <c r="J10" s="3"/>
@@ -12283,16 +12380,16 @@
       <c r="E11" s="45" t="n">
         <v>17574</v>
       </c>
-      <c r="F11" s="102" t="n">
+      <c r="F11" s="111" t="n">
         <v>2.45</v>
       </c>
-      <c r="G11" s="102" t="n">
+      <c r="G11" s="111" t="n">
         <v>2.44</v>
       </c>
-      <c r="H11" s="104" t="n">
+      <c r="H11" s="113" t="n">
         <v>2.16</v>
       </c>
-      <c r="I11" s="104" t="n">
+      <c r="I11" s="113" t="n">
         <v>2.7</v>
       </c>
       <c r="J11" s="3"/>
@@ -12311,16 +12408,16 @@
       <c r="E12" s="44" t="n">
         <v>3110</v>
       </c>
-      <c r="F12" s="101" t="n">
+      <c r="F12" s="110" t="n">
         <v>1.7</v>
       </c>
-      <c r="G12" s="101" t="n">
+      <c r="G12" s="110" t="n">
         <v>1.81</v>
       </c>
-      <c r="H12" s="103" t="n">
+      <c r="H12" s="112" t="n">
         <v>1.23</v>
       </c>
-      <c r="I12" s="103" t="n">
+      <c r="I12" s="112" t="n">
         <v>2.44</v>
       </c>
       <c r="J12" s="3"/>
@@ -12339,16 +12436,16 @@
       <c r="E13" s="45" t="n">
         <v>726</v>
       </c>
-      <c r="F13" s="102" t="n">
+      <c r="F13" s="111" t="n">
         <v>2.34</v>
       </c>
-      <c r="G13" s="102" t="n">
+      <c r="G13" s="111" t="n">
         <v>1.92</v>
       </c>
-      <c r="H13" s="104" t="n">
+      <c r="H13" s="113" t="n">
         <v>0.95</v>
       </c>
-      <c r="I13" s="104" t="n">
+      <c r="I13" s="113" t="n">
         <v>3.23</v>
       </c>
       <c r="J13" s="3"/>
@@ -12367,16 +12464,16 @@
       <c r="E14" s="44" t="n">
         <v>19958</v>
       </c>
-      <c r="F14" s="101" t="n">
+      <c r="F14" s="110" t="n">
         <v>2.33</v>
       </c>
-      <c r="G14" s="101" t="n">
+      <c r="G14" s="110" t="n">
         <v>2.33</v>
       </c>
-      <c r="H14" s="103" t="n">
+      <c r="H14" s="112" t="n">
         <v>2.08</v>
       </c>
-      <c r="I14" s="103" t="n">
+      <c r="I14" s="112" t="n">
         <v>2.6</v>
       </c>
       <c r="J14" s="3"/>
@@ -12395,16 +12492,16 @@
       <c r="E15" s="45" t="n">
         <v>1038</v>
       </c>
-      <c r="F15" s="102" t="n">
+      <c r="F15" s="111" t="n">
         <v>4.62</v>
       </c>
-      <c r="G15" s="102" t="n">
+      <c r="G15" s="111" t="n">
         <v>4.45</v>
       </c>
-      <c r="H15" s="104" t="n">
+      <c r="H15" s="113" t="n">
         <v>3.05</v>
       </c>
-      <c r="I15" s="104" t="n">
+      <c r="I15" s="113" t="n">
         <v>5.69</v>
       </c>
       <c r="J15" s="3"/>
@@ -12423,16 +12520,16 @@
       <c r="E16" s="44" t="n">
         <v>19646</v>
       </c>
-      <c r="F16" s="101" t="n">
+      <c r="F16" s="110" t="n">
         <v>2.21</v>
       </c>
-      <c r="G16" s="101" t="n">
+      <c r="G16" s="110" t="n">
         <v>2.22</v>
       </c>
-      <c r="H16" s="103" t="n">
+      <c r="H16" s="112" t="n">
         <v>1.96</v>
       </c>
-      <c r="I16" s="103" t="n">
+      <c r="I16" s="112" t="n">
         <v>2.48</v>
       </c>
       <c r="J16" s="3"/>
@@ -12451,16 +12548,16 @@
       <c r="E17" s="45" t="n">
         <v>286</v>
       </c>
-      <c r="F17" s="102" t="n">
+      <c r="F17" s="111" t="n">
         <v>5.24</v>
       </c>
-      <c r="G17" s="102" t="n">
+      <c r="G17" s="111" t="n">
         <v>5.52</v>
       </c>
-      <c r="H17" s="104" t="n">
+      <c r="H17" s="113" t="n">
         <v>2.5</v>
       </c>
-      <c r="I17" s="104" t="n">
+      <c r="I17" s="113" t="n">
         <v>10.39</v>
       </c>
       <c r="J17" s="3"/>
@@ -12479,16 +12576,16 @@
       <c r="E18" s="44" t="n">
         <v>20398</v>
       </c>
-      <c r="F18" s="101" t="n">
+      <c r="F18" s="110" t="n">
         <v>2.29</v>
       </c>
-      <c r="G18" s="101" t="n">
+      <c r="G18" s="110" t="n">
         <v>2.29</v>
       </c>
-      <c r="H18" s="103" t="n">
+      <c r="H18" s="112" t="n">
         <v>2.05</v>
       </c>
-      <c r="I18" s="103" t="n">
+      <c r="I18" s="112" t="n">
         <v>2.56</v>
       </c>
       <c r="J18" s="3"/>
@@ -12507,16 +12604,16 @@
       <c r="E19" s="45" t="n">
         <v>205</v>
       </c>
-      <c r="F19" s="102" t="n">
+      <c r="F19" s="111" t="n">
         <v>15.61</v>
       </c>
-      <c r="G19" s="102" t="n">
+      <c r="G19" s="111" t="n">
         <v>17.34</v>
       </c>
-      <c r="H19" s="104" t="n">
+      <c r="H19" s="113" t="n">
         <v>9.39</v>
       </c>
-      <c r="I19" s="104" t="n">
+      <c r="I19" s="113" t="n">
         <v>25.95</v>
       </c>
       <c r="J19" s="3"/>
@@ -12535,16 +12632,16 @@
       <c r="E20" s="44" t="n">
         <v>20479</v>
       </c>
-      <c r="F20" s="101" t="n">
+      <c r="F20" s="110" t="n">
         <v>2.2</v>
       </c>
-      <c r="G20" s="101" t="n">
+      <c r="G20" s="110" t="n">
         <v>2.21</v>
       </c>
-      <c r="H20" s="103" t="n">
+      <c r="H20" s="112" t="n">
         <v>1.95</v>
       </c>
-      <c r="I20" s="103" t="n">
+      <c r="I20" s="112" t="n">
         <v>2.46</v>
       </c>
       <c r="J20" s="3"/>
@@ -12563,16 +12660,16 @@
       <c r="E21" s="45" t="n">
         <v>18068</v>
       </c>
-      <c r="F21" s="102" t="n">
+      <c r="F21" s="111" t="n">
         <v>2.29</v>
       </c>
-      <c r="G21" s="102" t="n">
+      <c r="G21" s="111" t="n">
         <v>2.29</v>
       </c>
-      <c r="H21" s="104" t="n">
+      <c r="H21" s="113" t="n">
         <v>2</v>
       </c>
-      <c r="I21" s="104" t="n">
+      <c r="I21" s="113" t="n">
         <v>2.57</v>
       </c>
       <c r="J21" s="3"/>
@@ -12591,16 +12688,16 @@
       <c r="E22" s="44" t="n">
         <v>2616</v>
       </c>
-      <c r="F22" s="101" t="n">
+      <c r="F22" s="110" t="n">
         <v>2.64</v>
       </c>
-      <c r="G22" s="101" t="n">
+      <c r="G22" s="110" t="n">
         <v>2.72</v>
       </c>
-      <c r="H22" s="103" t="n">
+      <c r="H22" s="112" t="n">
         <v>2.01</v>
       </c>
-      <c r="I22" s="103" t="n">
+      <c r="I22" s="112" t="n">
         <v>3.43</v>
       </c>
       <c r="J22" s="3"/>
@@ -12619,16 +12716,16 @@
       <c r="E23" s="45" t="n">
         <v>9366</v>
       </c>
-      <c r="F23" s="102" t="n">
+      <c r="F23" s="111" t="n">
         <v>3.05</v>
       </c>
-      <c r="G23" s="102" t="n">
+      <c r="G23" s="111" t="n">
         <v>3.05</v>
       </c>
-      <c r="H23" s="104" t="n">
+      <c r="H23" s="113" t="n">
         <v>2.62</v>
       </c>
-      <c r="I23" s="104" t="n">
+      <c r="I23" s="113" t="n">
         <v>3.49</v>
       </c>
       <c r="J23" s="3"/>
@@ -12647,16 +12744,16 @@
       <c r="E24" s="44" t="n">
         <v>11318</v>
       </c>
-      <c r="F24" s="101" t="n">
+      <c r="F24" s="110" t="n">
         <v>1.74</v>
       </c>
-      <c r="G24" s="101" t="n">
+      <c r="G24" s="110" t="n">
         <v>1.74</v>
       </c>
-      <c r="H24" s="103" t="n">
+      <c r="H24" s="112" t="n">
         <v>1.46</v>
       </c>
-      <c r="I24" s="103" t="n">
+      <c r="I24" s="112" t="n">
         <v>2.03</v>
       </c>
       <c r="J24" s="3"/>
@@ -12675,16 +12772,16 @@
       <c r="E25" s="45" t="n">
         <v>7360</v>
       </c>
-      <c r="F25" s="102" t="n">
+      <c r="F25" s="111" t="n">
         <v>2.66</v>
       </c>
-      <c r="G25" s="102" t="n">
+      <c r="G25" s="111" t="n">
         <v>2.61</v>
       </c>
-      <c r="H25" s="104" t="n">
+      <c r="H25" s="113" t="n">
         <v>2.15</v>
       </c>
-      <c r="I25" s="104" t="n">
+      <c r="I25" s="113" t="n">
         <v>3.13</v>
       </c>
       <c r="J25" s="3"/>
@@ -12703,16 +12800,16 @@
       <c r="E26" s="44" t="n">
         <v>3015</v>
       </c>
-      <c r="F26" s="101" t="n">
+      <c r="F26" s="110" t="n">
         <v>2.55</v>
       </c>
-      <c r="G26" s="101" t="n">
+      <c r="G26" s="110" t="n">
         <v>2.6</v>
       </c>
-      <c r="H26" s="103" t="n">
+      <c r="H26" s="112" t="n">
         <v>1.92</v>
       </c>
-      <c r="I26" s="103" t="n">
+      <c r="I26" s="112" t="n">
         <v>3.32</v>
       </c>
       <c r="J26" s="3"/>
@@ -12731,16 +12828,16 @@
       <c r="E27" s="45" t="n">
         <v>2734</v>
       </c>
-      <c r="F27" s="102" t="n">
+      <c r="F27" s="111" t="n">
         <v>2.05</v>
       </c>
-      <c r="G27" s="102" t="n">
+      <c r="G27" s="111" t="n">
         <v>2.05</v>
       </c>
-      <c r="H27" s="104" t="n">
+      <c r="H27" s="113" t="n">
         <v>1.46</v>
       </c>
-      <c r="I27" s="104" t="n">
+      <c r="I27" s="113" t="n">
         <v>2.68</v>
       </c>
       <c r="J27" s="3"/>
@@ -12759,16 +12856,16 @@
       <c r="E28" s="44" t="n">
         <v>2577</v>
       </c>
-      <c r="F28" s="101" t="n">
+      <c r="F28" s="110" t="n">
         <v>1.75</v>
       </c>
-      <c r="G28" s="101" t="n">
+      <c r="G28" s="110" t="n">
         <v>1.83</v>
       </c>
-      <c r="H28" s="103" t="n">
+      <c r="H28" s="112" t="n">
         <v>1.31</v>
       </c>
-      <c r="I28" s="103" t="n">
+      <c r="I28" s="112" t="n">
         <v>2.45</v>
       </c>
       <c r="J28" s="3"/>
@@ -12787,16 +12884,16 @@
       <c r="E29" s="45" t="n">
         <v>2478</v>
       </c>
-      <c r="F29" s="102" t="n">
+      <c r="F29" s="111" t="n">
         <v>1.78</v>
       </c>
-      <c r="G29" s="102" t="n">
+      <c r="G29" s="111" t="n">
         <v>1.84</v>
       </c>
-      <c r="H29" s="104" t="n">
+      <c r="H29" s="113" t="n">
         <v>1.33</v>
       </c>
-      <c r="I29" s="104" t="n">
+      <c r="I29" s="113" t="n">
         <v>2.4</v>
       </c>
       <c r="J29" s="3"/>
@@ -12815,16 +12912,16 @@
       <c r="E30" s="44" t="n">
         <v>2168</v>
       </c>
-      <c r="F30" s="101" t="n">
+      <c r="F30" s="110" t="n">
         <v>1.98</v>
       </c>
-      <c r="G30" s="101" t="n">
+      <c r="G30" s="110" t="n">
         <v>1.67</v>
       </c>
-      <c r="H30" s="103" t="n">
+      <c r="H30" s="112" t="n">
         <v>1.09</v>
       </c>
-      <c r="I30" s="103" t="n">
+      <c r="I30" s="112" t="n">
         <v>2.27</v>
       </c>
       <c r="J30" s="3"/>
@@ -12843,16 +12940,16 @@
       <c r="E31" s="45" t="n">
         <v>234</v>
       </c>
-      <c r="F31" s="102" t="n">
+      <c r="F31" s="111" t="n">
         <v>5.13</v>
       </c>
-      <c r="G31" s="102" t="n">
+      <c r="G31" s="111" t="n">
         <v>5.57</v>
       </c>
-      <c r="H31" s="104" t="n">
+      <c r="H31" s="113" t="n">
         <v>2.15</v>
       </c>
-      <c r="I31" s="104" t="n">
+      <c r="I31" s="113" t="n">
         <v>10.74</v>
       </c>
       <c r="J31" s="3"/>
@@ -12871,16 +12968,16 @@
       <c r="E32" s="44" t="n">
         <v>66</v>
       </c>
-      <c r="F32" s="101" t="n">
+      <c r="F32" s="110" t="n">
         <v>10.61</v>
       </c>
-      <c r="G32" s="101" t="n">
+      <c r="G32" s="110" t="n">
         <v>13.64</v>
       </c>
-      <c r="H32" s="103" t="n">
+      <c r="H32" s="112" t="n">
         <v>2.26</v>
       </c>
-      <c r="I32" s="103" t="n">
+      <c r="I32" s="112" t="n">
         <v>26.47</v>
       </c>
       <c r="J32" s="3"/>
@@ -12899,16 +12996,16 @@
       <c r="E33" s="45" t="n">
         <v>3030</v>
       </c>
-      <c r="F33" s="102" t="n">
+      <c r="F33" s="111" t="n">
         <v>2.11</v>
       </c>
-      <c r="G33" s="102" t="n">
+      <c r="G33" s="111" t="n">
         <v>2.04</v>
       </c>
-      <c r="H33" s="104" t="n">
+      <c r="H33" s="113" t="n">
         <v>1.43</v>
       </c>
-      <c r="I33" s="104" t="n">
+      <c r="I33" s="113" t="n">
         <v>2.76</v>
       </c>
       <c r="J33" s="3"/>
@@ -12927,16 +13024,16 @@
       <c r="E34" s="44" t="n">
         <v>2655</v>
       </c>
-      <c r="F34" s="101" t="n">
+      <c r="F34" s="110" t="n">
         <v>3.39</v>
       </c>
-      <c r="G34" s="101" t="n">
+      <c r="G34" s="110" t="n">
         <v>3.43</v>
       </c>
-      <c r="H34" s="103" t="n">
+      <c r="H34" s="112" t="n">
         <v>2.47</v>
       </c>
-      <c r="I34" s="103" t="n">
+      <c r="I34" s="112" t="n">
         <v>4.54</v>
       </c>
       <c r="J34" s="3"/>
@@ -12955,16 +13052,16 @@
       <c r="E35" s="45" t="n">
         <v>1645</v>
       </c>
-      <c r="F35" s="102" t="n">
+      <c r="F35" s="111" t="n">
         <v>1.82</v>
       </c>
-      <c r="G35" s="102" t="n">
+      <c r="G35" s="111" t="n">
         <v>2.12</v>
       </c>
-      <c r="H35" s="104" t="n">
+      <c r="H35" s="113" t="n">
         <v>1.18</v>
       </c>
-      <c r="I35" s="104" t="n">
+      <c r="I35" s="113" t="n">
         <v>2.84</v>
       </c>
       <c r="J35" s="3"/>
@@ -12983,16 +13080,16 @@
       <c r="E36" s="44" t="n">
         <v>1315</v>
       </c>
-      <c r="F36" s="101" t="n">
+      <c r="F36" s="110" t="n">
         <v>2.36</v>
       </c>
-      <c r="G36" s="101" t="n">
+      <c r="G36" s="110" t="n">
         <v>2.35</v>
       </c>
-      <c r="H36" s="103" t="n">
+      <c r="H36" s="112" t="n">
         <v>1.53</v>
       </c>
-      <c r="I36" s="103" t="n">
+      <c r="I36" s="112" t="n">
         <v>3.16</v>
       </c>
       <c r="J36" s="3"/>
@@ -13011,16 +13108,16 @@
       <c r="E37" s="45" t="n">
         <v>841</v>
       </c>
-      <c r="F37" s="102" t="n">
+      <c r="F37" s="111" t="n">
         <v>2.85</v>
       </c>
-      <c r="G37" s="102" t="n">
+      <c r="G37" s="111" t="n">
         <v>2.45</v>
       </c>
-      <c r="H37" s="104" t="n">
+      <c r="H37" s="113" t="n">
         <v>1.44</v>
       </c>
-      <c r="I37" s="104" t="n">
+      <c r="I37" s="113" t="n">
         <v>3.51</v>
       </c>
       <c r="J37" s="3"/>
@@ -13039,16 +13136,16 @@
       <c r="E38" s="44" t="n">
         <v>605</v>
       </c>
-      <c r="F38" s="101" t="n">
+      <c r="F38" s="110" t="n">
         <v>2.48</v>
       </c>
-      <c r="G38" s="101" t="n">
+      <c r="G38" s="110" t="n">
         <v>2.57</v>
       </c>
-      <c r="H38" s="103" t="n">
+      <c r="H38" s="112" t="n">
         <v>1.31</v>
       </c>
-      <c r="I38" s="103" t="n">
+      <c r="I38" s="112" t="n">
         <v>4.01</v>
       </c>
       <c r="J38" s="3"/>
@@ -13067,16 +13164,16 @@
       <c r="E39" s="45" t="n">
         <v>576</v>
       </c>
-      <c r="F39" s="102" t="n">
+      <c r="F39" s="111" t="n">
         <v>2.08</v>
       </c>
-      <c r="G39" s="102" t="n">
+      <c r="G39" s="111" t="n">
         <v>2.24</v>
       </c>
-      <c r="H39" s="104" t="n">
+      <c r="H39" s="113" t="n">
         <v>0.75</v>
       </c>
-      <c r="I39" s="104" t="n">
+      <c r="I39" s="113" t="n">
         <v>4.22</v>
       </c>
       <c r="J39" s="3"/>
@@ -13095,16 +13192,16 @@
       <c r="E40" s="44" t="n">
         <v>512</v>
       </c>
-      <c r="F40" s="101" t="n">
+      <c r="F40" s="110" t="n">
         <v>5.08</v>
       </c>
-      <c r="G40" s="101" t="n">
+      <c r="G40" s="110" t="n">
         <v>4.4</v>
       </c>
-      <c r="H40" s="103" t="n">
+      <c r="H40" s="112" t="n">
         <v>1.96</v>
       </c>
-      <c r="I40" s="103" t="n">
+      <c r="I40" s="112" t="n">
         <v>7.04</v>
       </c>
       <c r="J40" s="3"/>
@@ -13123,16 +13220,16 @@
       <c r="E41" s="45" t="n">
         <v>470</v>
       </c>
-      <c r="F41" s="102" t="n">
+      <c r="F41" s="111" t="n">
         <v>1.91</v>
       </c>
-      <c r="G41" s="102" t="n">
+      <c r="G41" s="111" t="n">
         <v>1.65</v>
       </c>
-      <c r="H41" s="104" t="n">
+      <c r="H41" s="113" t="n">
         <v>0.64</v>
       </c>
-      <c r="I41" s="104" t="n">
+      <c r="I41" s="113" t="n">
         <v>3.18</v>
       </c>
       <c r="J41" s="3"/>
@@ -13151,16 +13248,16 @@
       <c r="E42" s="44" t="n">
         <v>435</v>
       </c>
-      <c r="F42" s="101" t="n">
+      <c r="F42" s="110" t="n">
         <v>2.3</v>
       </c>
-      <c r="G42" s="101" t="n">
+      <c r="G42" s="110" t="n">
         <v>2.19</v>
       </c>
-      <c r="H42" s="103" t="n">
+      <c r="H42" s="112" t="n">
         <v>0.84</v>
       </c>
-      <c r="I42" s="103" t="n">
+      <c r="I42" s="112" t="n">
         <v>3.84</v>
       </c>
       <c r="J42" s="3"/>
@@ -13179,16 +13276,16 @@
       <c r="E43" s="45" t="n">
         <v>404</v>
       </c>
-      <c r="F43" s="102" t="n">
+      <c r="F43" s="111" t="n">
         <v>4.7</v>
       </c>
-      <c r="G43" s="102" t="n">
+      <c r="G43" s="111" t="n">
         <v>4.08</v>
       </c>
-      <c r="H43" s="104" t="n">
+      <c r="H43" s="113" t="n">
         <v>2.2</v>
       </c>
-      <c r="I43" s="104" t="n">
+      <c r="I43" s="113" t="n">
         <v>6.29</v>
       </c>
       <c r="J43" s="3"/>
@@ -13207,16 +13304,16 @@
       <c r="E44" s="44" t="n">
         <v>354</v>
       </c>
-      <c r="F44" s="101" t="n">
+      <c r="F44" s="110" t="n">
         <v>1.41</v>
       </c>
-      <c r="G44" s="101" t="n">
+      <c r="G44" s="110" t="n">
         <v>2.63</v>
       </c>
-      <c r="H44" s="103" t="n">
+      <c r="H44" s="112" t="n">
         <v>0.34</v>
       </c>
-      <c r="I44" s="103" t="n">
+      <c r="I44" s="112" t="n">
         <v>6.03</v>
       </c>
       <c r="J44" s="3"/>
@@ -13235,16 +13332,16 @@
       <c r="E45" s="45" t="n">
         <v>17574</v>
       </c>
-      <c r="F45" s="102" t="n">
+      <c r="F45" s="111" t="n">
         <v>2.45</v>
       </c>
-      <c r="G45" s="102" t="n">
+      <c r="G45" s="111" t="n">
         <v>2.44</v>
       </c>
-      <c r="H45" s="104" t="n">
+      <c r="H45" s="113" t="n">
         <v>2.15</v>
       </c>
-      <c r="I45" s="104" t="n">
+      <c r="I45" s="113" t="n">
         <v>2.73</v>
       </c>
       <c r="J45" s="3"/>
@@ -13263,16 +13360,16 @@
       <c r="E46" s="44" t="n">
         <v>1232</v>
       </c>
-      <c r="F46" s="101" t="n">
+      <c r="F46" s="110" t="n">
         <v>1.95</v>
       </c>
-      <c r="G46" s="101" t="n">
+      <c r="G46" s="110" t="n">
         <v>1.88</v>
       </c>
-      <c r="H46" s="103" t="n">
+      <c r="H46" s="112" t="n">
         <v>0.88</v>
       </c>
-      <c r="I46" s="103" t="n">
+      <c r="I46" s="112" t="n">
         <v>2.73</v>
       </c>
       <c r="J46" s="3"/>
@@ -13291,16 +13388,16 @@
       <c r="E47" s="45" t="n">
         <v>726</v>
       </c>
-      <c r="F47" s="102" t="n">
+      <c r="F47" s="111" t="n">
         <v>2.34</v>
       </c>
-      <c r="G47" s="102" t="n">
+      <c r="G47" s="111" t="n">
         <v>1.92</v>
       </c>
-      <c r="H47" s="104" t="n">
+      <c r="H47" s="113" t="n">
         <v>0.91</v>
       </c>
-      <c r="I47" s="104" t="n">
+      <c r="I47" s="113" t="n">
         <v>3.19</v>
       </c>
       <c r="J47" s="3"/>
@@ -13319,16 +13416,16 @@
       <c r="E48" s="44" t="n">
         <v>489</v>
       </c>
-      <c r="F48" s="101" t="n">
+      <c r="F48" s="110" t="n">
         <v>0.2</v>
       </c>
-      <c r="G48" s="101" t="n">
+      <c r="G48" s="110" t="n">
         <v>0.22</v>
       </c>
-      <c r="H48" s="103" t="n">
+      <c r="H48" s="112" t="n">
         <v>0</v>
       </c>
-      <c r="I48" s="103" t="n">
+      <c r="I48" s="112" t="n">
         <v>0.76</v>
       </c>
       <c r="J48" s="3"/>
@@ -13347,16 +13444,16 @@
       <c r="E49" s="45" t="n">
         <v>355</v>
       </c>
-      <c r="F49" s="102" t="n">
+      <c r="F49" s="111" t="n">
         <v>2.25</v>
       </c>
-      <c r="G49" s="102" t="n">
+      <c r="G49" s="111" t="n">
         <v>2.96</v>
       </c>
-      <c r="H49" s="104" t="n">
+      <c r="H49" s="113" t="n">
         <v>1.04</v>
       </c>
-      <c r="I49" s="104" t="n">
+      <c r="I49" s="113" t="n">
         <v>5.25</v>
       </c>
       <c r="J49" s="3"/>
@@ -13375,16 +13472,16 @@
       <c r="E50" s="44" t="n">
         <v>20684</v>
       </c>
-      <c r="F50" s="101" t="n">
+      <c r="F50" s="110" t="n">
         <v>2.9</v>
       </c>
-      <c r="G50" s="101" t="n">
+      <c r="G50" s="110" t="n">
         <v>2.9</v>
       </c>
-      <c r="H50" s="103" t="n">
+      <c r="H50" s="112" t="n">
         <v>2.6</v>
       </c>
-      <c r="I50" s="103" t="n">
+      <c r="I50" s="112" t="n">
         <v>3.26</v>
       </c>
       <c r="J50" s="3"/>
@@ -13403,16 +13500,16 @@
       <c r="E51" s="45" t="n">
         <v>3793</v>
       </c>
-      <c r="F51" s="102" t="n">
+      <c r="F51" s="111" t="n">
         <v>2.66</v>
       </c>
-      <c r="G51" s="102" t="n">
+      <c r="G51" s="111" t="n">
         <v>2.72</v>
       </c>
-      <c r="H51" s="104" t="n">
+      <c r="H51" s="113" t="n">
         <v>2.14</v>
       </c>
-      <c r="I51" s="104" t="n">
+      <c r="I51" s="113" t="n">
         <v>3.31</v>
       </c>
       <c r="J51" s="3"/>
@@ -13431,16 +13528,16 @@
       <c r="E52" s="44" t="n">
         <v>16891</v>
       </c>
-      <c r="F52" s="101" t="n">
+      <c r="F52" s="110" t="n">
         <v>2.95</v>
       </c>
-      <c r="G52" s="101" t="n">
+      <c r="G52" s="110" t="n">
         <v>2.94</v>
       </c>
-      <c r="H52" s="103" t="n">
+      <c r="H52" s="112" t="n">
         <v>2.62</v>
       </c>
-      <c r="I52" s="103" t="n">
+      <c r="I52" s="112" t="n">
         <v>3.36</v>
       </c>
       <c r="J52" s="3"/>
@@ -13459,16 +13556,16 @@
       <c r="E53" s="45" t="n">
         <v>17574</v>
       </c>
-      <c r="F53" s="102" t="n">
+      <c r="F53" s="111" t="n">
         <v>2.97</v>
       </c>
-      <c r="G53" s="102" t="n">
+      <c r="G53" s="111" t="n">
         <v>2.96</v>
       </c>
-      <c r="H53" s="104" t="n">
+      <c r="H53" s="113" t="n">
         <v>2.66</v>
       </c>
-      <c r="I53" s="104" t="n">
+      <c r="I53" s="113" t="n">
         <v>3.31</v>
       </c>
       <c r="J53" s="3"/>
@@ -13487,16 +13584,16 @@
       <c r="E54" s="44" t="n">
         <v>3110</v>
       </c>
-      <c r="F54" s="101" t="n">
+      <c r="F54" s="110" t="n">
         <v>2.51</v>
       </c>
-      <c r="G54" s="101" t="n">
+      <c r="G54" s="110" t="n">
         <v>2.67</v>
       </c>
-      <c r="H54" s="103" t="n">
+      <c r="H54" s="112" t="n">
         <v>1.89</v>
       </c>
-      <c r="I54" s="103" t="n">
+      <c r="I54" s="112" t="n">
         <v>3.53</v>
       </c>
       <c r="J54" s="3"/>
@@ -13515,16 +13612,16 @@
       <c r="E55" s="45" t="n">
         <v>726</v>
       </c>
-      <c r="F55" s="102" t="n">
+      <c r="F55" s="111" t="n">
         <v>3.17</v>
       </c>
-      <c r="G55" s="102" t="n">
+      <c r="G55" s="111" t="n">
         <v>2.83</v>
       </c>
-      <c r="H55" s="104" t="n">
+      <c r="H55" s="113" t="n">
         <v>1.4</v>
       </c>
-      <c r="I55" s="104" t="n">
+      <c r="I55" s="113" t="n">
         <v>5.04</v>
       </c>
       <c r="J55" s="3"/>
@@ -13543,16 +13640,16 @@
       <c r="E56" s="44" t="n">
         <v>19958</v>
       </c>
-      <c r="F56" s="101" t="n">
+      <c r="F56" s="110" t="n">
         <v>2.89</v>
       </c>
-      <c r="G56" s="101" t="n">
+      <c r="G56" s="110" t="n">
         <v>2.89</v>
       </c>
-      <c r="H56" s="103" t="n">
+      <c r="H56" s="112" t="n">
         <v>2.63</v>
       </c>
-      <c r="I56" s="103" t="n">
+      <c r="I56" s="112" t="n">
         <v>3.2</v>
       </c>
       <c r="J56" s="3"/>
@@ -13571,16 +13668,16 @@
       <c r="E57" s="45" t="n">
         <v>1038</v>
       </c>
-      <c r="F57" s="102" t="n">
+      <c r="F57" s="111" t="n">
         <v>6.55</v>
       </c>
-      <c r="G57" s="102" t="n">
+      <c r="G57" s="111" t="n">
         <v>6.41</v>
       </c>
-      <c r="H57" s="104" t="n">
+      <c r="H57" s="113" t="n">
         <v>4.44</v>
       </c>
-      <c r="I57" s="104" t="n">
+      <c r="I57" s="113" t="n">
         <v>8.09</v>
       </c>
       <c r="J57" s="3"/>
@@ -13599,16 +13696,16 @@
       <c r="E58" s="44" t="n">
         <v>19646</v>
       </c>
-      <c r="F58" s="101" t="n">
+      <c r="F58" s="110" t="n">
         <v>2.71</v>
       </c>
-      <c r="G58" s="101" t="n">
+      <c r="G58" s="110" t="n">
         <v>2.71</v>
       </c>
-      <c r="H58" s="103" t="n">
+      <c r="H58" s="112" t="n">
         <v>2.44</v>
       </c>
-      <c r="I58" s="103" t="n">
+      <c r="I58" s="112" t="n">
         <v>3.03</v>
       </c>
       <c r="J58" s="3"/>
@@ -13627,16 +13724,16 @@
       <c r="E59" s="45" t="n">
         <v>286</v>
       </c>
-      <c r="F59" s="102" t="n">
+      <c r="F59" s="111" t="n">
         <v>6.99</v>
       </c>
-      <c r="G59" s="102" t="n">
+      <c r="G59" s="111" t="n">
         <v>9.09</v>
       </c>
-      <c r="H59" s="104" t="n">
+      <c r="H59" s="113" t="n">
         <v>3.47</v>
       </c>
-      <c r="I59" s="104" t="n">
+      <c r="I59" s="113" t="n">
         <v>16.96</v>
       </c>
       <c r="J59" s="3"/>
@@ -13655,16 +13752,16 @@
       <c r="E60" s="44" t="n">
         <v>20398</v>
       </c>
-      <c r="F60" s="101" t="n">
+      <c r="F60" s="110" t="n">
         <v>2.84</v>
       </c>
-      <c r="G60" s="101" t="n">
+      <c r="G60" s="110" t="n">
         <v>2.84</v>
       </c>
-      <c r="H60" s="103" t="n">
+      <c r="H60" s="112" t="n">
         <v>2.54</v>
       </c>
-      <c r="I60" s="103" t="n">
+      <c r="I60" s="112" t="n">
         <v>3.19</v>
       </c>
       <c r="J60" s="3"/>
@@ -13683,16 +13780,16 @@
       <c r="E61" s="45" t="n">
         <v>205</v>
       </c>
-      <c r="F61" s="102" t="n">
+      <c r="F61" s="111" t="n">
         <v>12.68</v>
       </c>
-      <c r="G61" s="102" t="n">
+      <c r="G61" s="111" t="n">
         <v>16.56</v>
       </c>
-      <c r="H61" s="104" t="n">
+      <c r="H61" s="113" t="n">
         <v>8.93</v>
       </c>
-      <c r="I61" s="104" t="n">
+      <c r="I61" s="113" t="n">
         <v>24.82</v>
       </c>
       <c r="J61" s="3"/>
@@ -13711,16 +13808,16 @@
       <c r="E62" s="44" t="n">
         <v>20479</v>
       </c>
-      <c r="F62" s="101" t="n">
+      <c r="F62" s="110" t="n">
         <v>2.8</v>
       </c>
-      <c r="G62" s="101" t="n">
+      <c r="G62" s="110" t="n">
         <v>2.81</v>
       </c>
-      <c r="H62" s="103" t="n">
+      <c r="H62" s="112" t="n">
         <v>2.51</v>
       </c>
-      <c r="I62" s="103" t="n">
+      <c r="I62" s="112" t="n">
         <v>3.13</v>
       </c>
       <c r="J62" s="3"/>
@@ -13739,16 +13836,16 @@
       <c r="E63" s="45" t="n">
         <v>18068</v>
       </c>
-      <c r="F63" s="102" t="n">
+      <c r="F63" s="111" t="n">
         <v>2.79</v>
       </c>
-      <c r="G63" s="102" t="n">
+      <c r="G63" s="111" t="n">
         <v>2.79</v>
       </c>
-      <c r="H63" s="104" t="n">
+      <c r="H63" s="113" t="n">
         <v>2.47</v>
       </c>
-      <c r="I63" s="104" t="n">
+      <c r="I63" s="113" t="n">
         <v>3.15</v>
       </c>
       <c r="J63" s="3"/>
@@ -13767,16 +13864,16 @@
       <c r="E64" s="44" t="n">
         <v>2616</v>
       </c>
-      <c r="F64" s="101" t="n">
+      <c r="F64" s="110" t="n">
         <v>3.67</v>
       </c>
-      <c r="G64" s="101" t="n">
+      <c r="G64" s="110" t="n">
         <v>3.62</v>
       </c>
-      <c r="H64" s="103" t="n">
+      <c r="H64" s="112" t="n">
         <v>2.81</v>
       </c>
-      <c r="I64" s="103" t="n">
+      <c r="I64" s="112" t="n">
         <v>4.47</v>
       </c>
       <c r="J64" s="3"/>
@@ -13795,16 +13892,16 @@
       <c r="E65" s="45" t="n">
         <v>9366</v>
       </c>
-      <c r="F65" s="102" t="n">
+      <c r="F65" s="111" t="n">
         <v>3.87</v>
       </c>
-      <c r="G65" s="102" t="n">
+      <c r="G65" s="111" t="n">
         <v>3.87</v>
       </c>
-      <c r="H65" s="104" t="n">
+      <c r="H65" s="113" t="n">
         <v>3.32</v>
       </c>
-      <c r="I65" s="104" t="n">
+      <c r="I65" s="113" t="n">
         <v>4.44</v>
       </c>
       <c r="J65" s="3"/>
@@ -13823,16 +13920,16 @@
       <c r="E66" s="44" t="n">
         <v>11318</v>
       </c>
-      <c r="F66" s="101" t="n">
+      <c r="F66" s="110" t="n">
         <v>2.1</v>
       </c>
-      <c r="G66" s="101" t="n">
+      <c r="G66" s="110" t="n">
         <v>2.1</v>
       </c>
-      <c r="H66" s="103" t="n">
+      <c r="H66" s="112" t="n">
         <v>1.81</v>
       </c>
-      <c r="I66" s="103" t="n">
+      <c r="I66" s="112" t="n">
         <v>2.4</v>
       </c>
       <c r="J66" s="3"/>
@@ -13851,16 +13948,16 @@
       <c r="E67" s="45" t="n">
         <v>7360</v>
       </c>
-      <c r="F67" s="102" t="n">
+      <c r="F67" s="111" t="n">
         <v>2.96</v>
       </c>
-      <c r="G67" s="102" t="n">
+      <c r="G67" s="111" t="n">
         <v>2.92</v>
       </c>
-      <c r="H67" s="104" t="n">
+      <c r="H67" s="113" t="n">
         <v>2.38</v>
       </c>
-      <c r="I67" s="104" t="n">
+      <c r="I67" s="113" t="n">
         <v>3.5</v>
       </c>
       <c r="J67" s="3"/>
@@ -13879,16 +13976,16 @@
       <c r="E68" s="44" t="n">
         <v>3015</v>
       </c>
-      <c r="F68" s="101" t="n">
+      <c r="F68" s="110" t="n">
         <v>2.95</v>
       </c>
-      <c r="G68" s="101" t="n">
+      <c r="G68" s="110" t="n">
         <v>2.97</v>
       </c>
-      <c r="H68" s="103" t="n">
+      <c r="H68" s="112" t="n">
         <v>2.28</v>
       </c>
-      <c r="I68" s="103" t="n">
+      <c r="I68" s="112" t="n">
         <v>3.69</v>
       </c>
       <c r="J68" s="3"/>
@@ -13907,16 +14004,16 @@
       <c r="E69" s="45" t="n">
         <v>2734</v>
       </c>
-      <c r="F69" s="102" t="n">
+      <c r="F69" s="111" t="n">
         <v>3.15</v>
       </c>
-      <c r="G69" s="102" t="n">
+      <c r="G69" s="111" t="n">
         <v>2.99</v>
       </c>
-      <c r="H69" s="104" t="n">
+      <c r="H69" s="113" t="n">
         <v>2.36</v>
       </c>
-      <c r="I69" s="104" t="n">
+      <c r="I69" s="113" t="n">
         <v>3.75</v>
       </c>
       <c r="J69" s="3"/>
@@ -13935,16 +14032,16 @@
       <c r="E70" s="44" t="n">
         <v>2577</v>
       </c>
-      <c r="F70" s="101" t="n">
+      <c r="F70" s="110" t="n">
         <v>1.9</v>
       </c>
-      <c r="G70" s="101" t="n">
+      <c r="G70" s="110" t="n">
         <v>2.03</v>
       </c>
-      <c r="H70" s="103" t="n">
+      <c r="H70" s="112" t="n">
         <v>1.41</v>
       </c>
-      <c r="I70" s="103" t="n">
+      <c r="I70" s="112" t="n">
         <v>2.63</v>
       </c>
       <c r="J70" s="3"/>
@@ -13963,16 +14060,16 @@
       <c r="E71" s="45" t="n">
         <v>2478</v>
       </c>
-      <c r="F71" s="102" t="n">
+      <c r="F71" s="111" t="n">
         <v>2.99</v>
       </c>
-      <c r="G71" s="102" t="n">
+      <c r="G71" s="111" t="n">
         <v>2.99</v>
       </c>
-      <c r="H71" s="104" t="n">
+      <c r="H71" s="113" t="n">
         <v>2.24</v>
       </c>
-      <c r="I71" s="104" t="n">
+      <c r="I71" s="113" t="n">
         <v>3.79</v>
       </c>
       <c r="J71" s="3"/>
@@ -13991,16 +14088,16 @@
       <c r="E72" s="44" t="n">
         <v>2168</v>
       </c>
-      <c r="F72" s="101" t="n">
+      <c r="F72" s="110" t="n">
         <v>2.77</v>
       </c>
-      <c r="G72" s="101" t="n">
+      <c r="G72" s="110" t="n">
         <v>2.52</v>
       </c>
-      <c r="H72" s="103" t="n">
+      <c r="H72" s="112" t="n">
         <v>1.81</v>
       </c>
-      <c r="I72" s="103" t="n">
+      <c r="I72" s="112" t="n">
         <v>3.27</v>
       </c>
       <c r="J72" s="3"/>
@@ -14019,16 +14116,16 @@
       <c r="E73" s="45" t="n">
         <v>234</v>
       </c>
-      <c r="F73" s="102" t="n">
+      <c r="F73" s="111" t="n">
         <v>7.69</v>
       </c>
-      <c r="G73" s="102" t="n">
+      <c r="G73" s="111" t="n">
         <v>9.51</v>
       </c>
-      <c r="H73" s="104" t="n">
+      <c r="H73" s="113" t="n">
         <v>4.11</v>
       </c>
-      <c r="I73" s="104" t="n">
+      <c r="I73" s="113" t="n">
         <v>16.83</v>
       </c>
       <c r="J73" s="3"/>
@@ -14047,16 +14144,16 @@
       <c r="E74" s="44" t="n">
         <v>66</v>
       </c>
-      <c r="F74" s="101" t="n">
+      <c r="F74" s="110" t="n">
         <v>6.06</v>
       </c>
-      <c r="G74" s="101" t="n">
+      <c r="G74" s="110" t="n">
         <v>3.21</v>
       </c>
-      <c r="H74" s="103" t="n">
+      <c r="H74" s="112" t="n">
         <v>0</v>
       </c>
-      <c r="I74" s="103" t="n">
+      <c r="I74" s="112" t="n">
         <v>6.65</v>
       </c>
       <c r="J74" s="3"/>
@@ -14075,16 +14172,16 @@
       <c r="E75" s="45" t="n">
         <v>3030</v>
       </c>
-      <c r="F75" s="102" t="n">
+      <c r="F75" s="111" t="n">
         <v>3.23</v>
       </c>
-      <c r="G75" s="102" t="n">
+      <c r="G75" s="111" t="n">
         <v>3.15</v>
       </c>
-      <c r="H75" s="104" t="n">
+      <c r="H75" s="113" t="n">
         <v>2.45</v>
       </c>
-      <c r="I75" s="104" t="n">
+      <c r="I75" s="113" t="n">
         <v>3.89</v>
       </c>
       <c r="J75" s="3"/>
@@ -14103,16 +14200,16 @@
       <c r="E76" s="44" t="n">
         <v>2655</v>
       </c>
-      <c r="F76" s="101" t="n">
+      <c r="F76" s="110" t="n">
         <v>3.54</v>
       </c>
-      <c r="G76" s="101" t="n">
+      <c r="G76" s="110" t="n">
         <v>3.59</v>
       </c>
-      <c r="H76" s="103" t="n">
+      <c r="H76" s="112" t="n">
         <v>2.54</v>
       </c>
-      <c r="I76" s="103" t="n">
+      <c r="I76" s="112" t="n">
         <v>4.84</v>
       </c>
       <c r="J76" s="3"/>
@@ -14131,16 +14228,16 @@
       <c r="E77" s="45" t="n">
         <v>1645</v>
       </c>
-      <c r="F77" s="102" t="n">
+      <c r="F77" s="111" t="n">
         <v>2.07</v>
       </c>
-      <c r="G77" s="102" t="n">
+      <c r="G77" s="111" t="n">
         <v>2.31</v>
       </c>
-      <c r="H77" s="104" t="n">
+      <c r="H77" s="113" t="n">
         <v>1.4</v>
       </c>
-      <c r="I77" s="104" t="n">
+      <c r="I77" s="113" t="n">
         <v>3.04</v>
       </c>
       <c r="J77" s="3"/>
@@ -14159,16 +14256,16 @@
       <c r="E78" s="44" t="n">
         <v>1315</v>
       </c>
-      <c r="F78" s="101" t="n">
+      <c r="F78" s="110" t="n">
         <v>3.73</v>
       </c>
-      <c r="G78" s="101" t="n">
+      <c r="G78" s="110" t="n">
         <v>3.72</v>
       </c>
-      <c r="H78" s="103" t="n">
+      <c r="H78" s="112" t="n">
         <v>2.66</v>
       </c>
-      <c r="I78" s="103" t="n">
+      <c r="I78" s="112" t="n">
         <v>4.83</v>
       </c>
       <c r="J78" s="3"/>
@@ -14187,16 +14284,16 @@
       <c r="E79" s="45" t="n">
         <v>841</v>
       </c>
-      <c r="F79" s="102" t="n">
+      <c r="F79" s="111" t="n">
         <v>2.38</v>
       </c>
-      <c r="G79" s="102" t="n">
+      <c r="G79" s="111" t="n">
         <v>2.25</v>
       </c>
-      <c r="H79" s="104" t="n">
+      <c r="H79" s="113" t="n">
         <v>1.02</v>
       </c>
-      <c r="I79" s="104" t="n">
+      <c r="I79" s="113" t="n">
         <v>3.32</v>
       </c>
       <c r="J79" s="3"/>
@@ -14215,16 +14312,16 @@
       <c r="E80" s="44" t="n">
         <v>605</v>
       </c>
-      <c r="F80" s="101" t="n">
+      <c r="F80" s="110" t="n">
         <v>2.64</v>
       </c>
-      <c r="G80" s="101" t="n">
+      <c r="G80" s="110" t="n">
         <v>2.59</v>
       </c>
-      <c r="H80" s="103" t="n">
+      <c r="H80" s="112" t="n">
         <v>1.26</v>
       </c>
-      <c r="I80" s="103" t="n">
+      <c r="I80" s="112" t="n">
         <v>4.23</v>
       </c>
       <c r="J80" s="3"/>
@@ -14243,16 +14340,16 @@
       <c r="E81" s="45" t="n">
         <v>576</v>
       </c>
-      <c r="F81" s="102" t="n">
+      <c r="F81" s="111" t="n">
         <v>2.6</v>
       </c>
-      <c r="G81" s="102" t="n">
+      <c r="G81" s="111" t="n">
         <v>2.06</v>
       </c>
-      <c r="H81" s="104" t="n">
+      <c r="H81" s="113" t="n">
         <v>0.94</v>
       </c>
-      <c r="I81" s="104" t="n">
+      <c r="I81" s="113" t="n">
         <v>3.29</v>
       </c>
       <c r="J81" s="3"/>
@@ -14271,16 +14368,16 @@
       <c r="E82" s="44" t="n">
         <v>512</v>
       </c>
-      <c r="F82" s="101" t="n">
+      <c r="F82" s="110" t="n">
         <v>5.08</v>
       </c>
-      <c r="G82" s="101" t="n">
+      <c r="G82" s="110" t="n">
         <v>4.32</v>
       </c>
-      <c r="H82" s="103" t="n">
+      <c r="H82" s="112" t="n">
         <v>2.3</v>
       </c>
-      <c r="I82" s="103" t="n">
+      <c r="I82" s="112" t="n">
         <v>5.84</v>
       </c>
       <c r="J82" s="3"/>
@@ -14299,16 +14396,16 @@
       <c r="E83" s="45" t="n">
         <v>470</v>
       </c>
-      <c r="F83" s="102" t="n">
+      <c r="F83" s="111" t="n">
         <v>2.34</v>
       </c>
-      <c r="G83" s="102" t="n">
+      <c r="G83" s="111" t="n">
         <v>2.21</v>
       </c>
-      <c r="H83" s="104" t="n">
+      <c r="H83" s="113" t="n">
         <v>0.86</v>
       </c>
-      <c r="I83" s="104" t="n">
+      <c r="I83" s="113" t="n">
         <v>4.07</v>
       </c>
       <c r="J83" s="3"/>
@@ -14327,16 +14424,16 @@
       <c r="E84" s="44" t="n">
         <v>435</v>
       </c>
-      <c r="F84" s="101" t="n">
+      <c r="F84" s="110" t="n">
         <v>3.91</v>
       </c>
-      <c r="G84" s="101" t="n">
+      <c r="G84" s="110" t="n">
         <v>3.44</v>
       </c>
-      <c r="H84" s="103" t="n">
+      <c r="H84" s="112" t="n">
         <v>1.72</v>
       </c>
-      <c r="I84" s="103" t="n">
+      <c r="I84" s="112" t="n">
         <v>5.21</v>
       </c>
       <c r="J84" s="3"/>
@@ -14355,16 +14452,16 @@
       <c r="E85" s="45" t="n">
         <v>404</v>
       </c>
-      <c r="F85" s="102" t="n">
+      <c r="F85" s="111" t="n">
         <v>4.7</v>
       </c>
-      <c r="G85" s="102" t="n">
+      <c r="G85" s="111" t="n">
         <v>4.02</v>
       </c>
-      <c r="H85" s="104" t="n">
+      <c r="H85" s="113" t="n">
         <v>2.12</v>
       </c>
-      <c r="I85" s="104" t="n">
+      <c r="I85" s="113" t="n">
         <v>6.58</v>
       </c>
       <c r="J85" s="3"/>
@@ -14383,16 +14480,16 @@
       <c r="E86" s="44" t="n">
         <v>354</v>
       </c>
-      <c r="F86" s="101" t="n">
+      <c r="F86" s="110" t="n">
         <v>1.69</v>
       </c>
-      <c r="G86" s="101" t="n">
+      <c r="G86" s="110" t="n">
         <v>2.66</v>
       </c>
-      <c r="H86" s="103" t="n">
+      <c r="H86" s="112" t="n">
         <v>0.37</v>
       </c>
-      <c r="I86" s="103" t="n">
+      <c r="I86" s="112" t="n">
         <v>5.86</v>
       </c>
       <c r="J86" s="3"/>
@@ -14411,16 +14508,16 @@
       <c r="E87" s="45" t="n">
         <v>17574</v>
       </c>
-      <c r="F87" s="102" t="n">
+      <c r="F87" s="111" t="n">
         <v>2.97</v>
       </c>
-      <c r="G87" s="102" t="n">
+      <c r="G87" s="111" t="n">
         <v>2.96</v>
       </c>
-      <c r="H87" s="104" t="n">
+      <c r="H87" s="113" t="n">
         <v>2.68</v>
       </c>
-      <c r="I87" s="104" t="n">
+      <c r="I87" s="113" t="n">
         <v>3.28</v>
       </c>
       <c r="J87" s="3"/>
@@ -14439,16 +14536,16 @@
       <c r="E88" s="44" t="n">
         <v>1232</v>
       </c>
-      <c r="F88" s="101" t="n">
+      <c r="F88" s="110" t="n">
         <v>3</v>
       </c>
-      <c r="G88" s="101" t="n">
+      <c r="G88" s="110" t="n">
         <v>3.13</v>
       </c>
-      <c r="H88" s="103" t="n">
+      <c r="H88" s="112" t="n">
         <v>1.83</v>
       </c>
-      <c r="I88" s="103" t="n">
+      <c r="I88" s="112" t="n">
         <v>4.76</v>
       </c>
       <c r="J88" s="3"/>
@@ -14467,16 +14564,16 @@
       <c r="E89" s="45" t="n">
         <v>726</v>
       </c>
-      <c r="F89" s="102" t="n">
+      <c r="F89" s="111" t="n">
         <v>3.17</v>
       </c>
-      <c r="G89" s="102" t="n">
+      <c r="G89" s="111" t="n">
         <v>2.83</v>
       </c>
-      <c r="H89" s="104" t="n">
+      <c r="H89" s="113" t="n">
         <v>1.41</v>
       </c>
-      <c r="I89" s="104" t="n">
+      <c r="I89" s="113" t="n">
         <v>5.03</v>
       </c>
       <c r="J89" s="3"/>
@@ -14495,16 +14592,16 @@
       <c r="E90" s="44" t="n">
         <v>489</v>
       </c>
-      <c r="F90" s="101" t="n">
+      <c r="F90" s="110" t="n">
         <v>1.02</v>
       </c>
-      <c r="G90" s="101" t="n">
+      <c r="G90" s="110" t="n">
         <v>1.1</v>
       </c>
-      <c r="H90" s="103" t="n">
+      <c r="H90" s="112" t="n">
         <v>0.25</v>
       </c>
-      <c r="I90" s="103" t="n">
+      <c r="I90" s="112" t="n">
         <v>2.1</v>
       </c>
       <c r="J90" s="3"/>
@@ -14523,16 +14620,16 @@
       <c r="E91" s="45" t="n">
         <v>355</v>
       </c>
-      <c r="F91" s="102" t="n">
+      <c r="F91" s="111" t="n">
         <v>2.25</v>
       </c>
-      <c r="G91" s="102" t="n">
+      <c r="G91" s="111" t="n">
         <v>2.48</v>
       </c>
-      <c r="H91" s="104" t="n">
+      <c r="H91" s="113" t="n">
         <v>0.77</v>
       </c>
-      <c r="I91" s="104" t="n">
+      <c r="I91" s="113" t="n">
         <v>4.78</v>
       </c>
       <c r="J91" s="3"/>
@@ -14551,16 +14648,16 @@
       <c r="E92" s="44" t="n">
         <v>20684</v>
       </c>
-      <c r="F92" s="101" t="n">
+      <c r="F92" s="110" t="n">
         <v>1.45</v>
       </c>
-      <c r="G92" s="101" t="n">
+      <c r="G92" s="110" t="n">
         <v>1.45</v>
       </c>
-      <c r="H92" s="103" t="n">
+      <c r="H92" s="112" t="n">
         <v>1.26</v>
       </c>
-      <c r="I92" s="103" t="n">
+      <c r="I92" s="112" t="n">
         <v>1.65</v>
       </c>
       <c r="J92" s="3"/>
@@ -14579,16 +14676,16 @@
       <c r="E93" s="45" t="n">
         <v>3793</v>
       </c>
-      <c r="F93" s="102" t="n">
+      <c r="F93" s="111" t="n">
         <v>1.13</v>
       </c>
-      <c r="G93" s="102" t="n">
+      <c r="G93" s="111" t="n">
         <v>1.14</v>
       </c>
-      <c r="H93" s="104" t="n">
+      <c r="H93" s="113" t="n">
         <v>0.76</v>
       </c>
-      <c r="I93" s="104" t="n">
+      <c r="I93" s="113" t="n">
         <v>1.57</v>
       </c>
       <c r="J93" s="3"/>
@@ -14607,16 +14704,16 @@
       <c r="E94" s="44" t="n">
         <v>16891</v>
       </c>
-      <c r="F94" s="101" t="n">
+      <c r="F94" s="110" t="n">
         <v>1.52</v>
       </c>
-      <c r="G94" s="101" t="n">
+      <c r="G94" s="110" t="n">
         <v>1.51</v>
       </c>
-      <c r="H94" s="103" t="n">
+      <c r="H94" s="112" t="n">
         <v>1.31</v>
       </c>
-      <c r="I94" s="103" t="n">
+      <c r="I94" s="112" t="n">
         <v>1.72</v>
       </c>
       <c r="J94" s="3"/>
@@ -14635,16 +14732,16 @@
       <c r="E95" s="45" t="n">
         <v>17574</v>
       </c>
-      <c r="F95" s="102" t="n">
+      <c r="F95" s="111" t="n">
         <v>1.51</v>
       </c>
-      <c r="G95" s="102" t="n">
+      <c r="G95" s="111" t="n">
         <v>1.5</v>
       </c>
-      <c r="H95" s="104" t="n">
+      <c r="H95" s="113" t="n">
         <v>1.3</v>
       </c>
-      <c r="I95" s="104" t="n">
+      <c r="I95" s="113" t="n">
         <v>1.7</v>
       </c>
       <c r="J95" s="3"/>
@@ -14663,16 +14760,16 @@
       <c r="E96" s="44" t="n">
         <v>3110</v>
       </c>
-      <c r="F96" s="101" t="n">
+      <c r="F96" s="110" t="n">
         <v>1.13</v>
       </c>
-      <c r="G96" s="101" t="n">
+      <c r="G96" s="110" t="n">
         <v>1.22</v>
       </c>
-      <c r="H96" s="103" t="n">
+      <c r="H96" s="112" t="n">
         <v>0.7</v>
       </c>
-      <c r="I96" s="103" t="n">
+      <c r="I96" s="112" t="n">
         <v>1.76</v>
       </c>
       <c r="J96" s="3"/>
@@ -14691,16 +14788,16 @@
       <c r="E97" s="45" t="n">
         <v>726</v>
       </c>
-      <c r="F97" s="102" t="n">
+      <c r="F97" s="111" t="n">
         <v>1.65</v>
       </c>
-      <c r="G97" s="102" t="n">
+      <c r="G97" s="111" t="n">
         <v>1.3</v>
       </c>
-      <c r="H97" s="104" t="n">
+      <c r="H97" s="113" t="n">
         <v>0.51</v>
       </c>
-      <c r="I97" s="104" t="n">
+      <c r="I97" s="113" t="n">
         <v>2.3</v>
       </c>
       <c r="J97" s="3"/>
@@ -14719,16 +14816,16 @@
       <c r="E98" s="44" t="n">
         <v>19958</v>
       </c>
-      <c r="F98" s="101" t="n">
+      <c r="F98" s="110" t="n">
         <v>1.44</v>
       </c>
-      <c r="G98" s="101" t="n">
+      <c r="G98" s="110" t="n">
         <v>1.44</v>
       </c>
-      <c r="H98" s="103" t="n">
+      <c r="H98" s="112" t="n">
         <v>1.26</v>
       </c>
-      <c r="I98" s="103" t="n">
+      <c r="I98" s="112" t="n">
         <v>1.63</v>
       </c>
       <c r="J98" s="3"/>
@@ -14747,16 +14844,16 @@
       <c r="E99" s="45" t="n">
         <v>1038</v>
       </c>
-      <c r="F99" s="102" t="n">
+      <c r="F99" s="111" t="n">
         <v>3.85</v>
       </c>
-      <c r="G99" s="102" t="n">
+      <c r="G99" s="111" t="n">
         <v>3.72</v>
       </c>
-      <c r="H99" s="104" t="n">
+      <c r="H99" s="113" t="n">
         <v>2.47</v>
       </c>
-      <c r="I99" s="104" t="n">
+      <c r="I99" s="113" t="n">
         <v>4.88</v>
       </c>
       <c r="J99" s="3"/>
@@ -14775,16 +14872,16 @@
       <c r="E100" s="44" t="n">
         <v>19646</v>
       </c>
-      <c r="F100" s="101" t="n">
+      <c r="F100" s="110" t="n">
         <v>1.32</v>
       </c>
-      <c r="G100" s="101" t="n">
+      <c r="G100" s="110" t="n">
         <v>1.33</v>
       </c>
-      <c r="H100" s="103" t="n">
+      <c r="H100" s="112" t="n">
         <v>1.14</v>
       </c>
-      <c r="I100" s="103" t="n">
+      <c r="I100" s="112" t="n">
         <v>1.52</v>
       </c>
       <c r="J100" s="3"/>
@@ -14803,16 +14900,16 @@
       <c r="E101" s="45" t="n">
         <v>286</v>
       </c>
-      <c r="F101" s="102" t="n">
+      <c r="F101" s="111" t="n">
         <v>4.2</v>
       </c>
-      <c r="G101" s="102" t="n">
+      <c r="G101" s="111" t="n">
         <v>4.96</v>
       </c>
-      <c r="H101" s="104" t="n">
+      <c r="H101" s="113" t="n">
         <v>1.85</v>
       </c>
-      <c r="I101" s="104" t="n">
+      <c r="I101" s="113" t="n">
         <v>10.05</v>
       </c>
       <c r="J101" s="3"/>
@@ -14831,16 +14928,16 @@
       <c r="E102" s="44" t="n">
         <v>20398</v>
       </c>
-      <c r="F102" s="101" t="n">
+      <c r="F102" s="110" t="n">
         <v>1.41</v>
       </c>
-      <c r="G102" s="101" t="n">
+      <c r="G102" s="110" t="n">
         <v>1.41</v>
       </c>
-      <c r="H102" s="103" t="n">
+      <c r="H102" s="112" t="n">
         <v>1.22</v>
       </c>
-      <c r="I102" s="103" t="n">
+      <c r="I102" s="112" t="n">
         <v>1.63</v>
       </c>
       <c r="J102" s="3"/>
@@ -14859,16 +14956,16 @@
       <c r="E103" s="45" t="n">
         <v>205</v>
       </c>
-      <c r="F103" s="102" t="n">
+      <c r="F103" s="111" t="n">
         <v>10.73</v>
       </c>
-      <c r="G103" s="102" t="n">
+      <c r="G103" s="111" t="n">
         <v>15.07</v>
       </c>
-      <c r="H103" s="104" t="n">
+      <c r="H103" s="113" t="n">
         <v>6.97</v>
       </c>
-      <c r="I103" s="104" t="n">
+      <c r="I103" s="113" t="n">
         <v>23.2</v>
       </c>
       <c r="J103" s="3"/>
@@ -14887,16 +14984,16 @@
       <c r="E104" s="44" t="n">
         <v>20479</v>
       </c>
-      <c r="F104" s="101" t="n">
+      <c r="F104" s="110" t="n">
         <v>1.36</v>
       </c>
-      <c r="G104" s="101" t="n">
+      <c r="G104" s="110" t="n">
         <v>1.36</v>
       </c>
-      <c r="H104" s="103" t="n">
+      <c r="H104" s="112" t="n">
         <v>1.19</v>
       </c>
-      <c r="I104" s="103" t="n">
+      <c r="I104" s="112" t="n">
         <v>1.55</v>
       </c>
       <c r="J104" s="3"/>
@@ -14915,16 +15012,16 @@
       <c r="E105" s="45" t="n">
         <v>18068</v>
       </c>
-      <c r="F105" s="102" t="n">
+      <c r="F105" s="111" t="n">
         <v>1.39</v>
       </c>
-      <c r="G105" s="102" t="n">
+      <c r="G105" s="111" t="n">
         <v>1.4</v>
       </c>
-      <c r="H105" s="104" t="n">
+      <c r="H105" s="113" t="n">
         <v>1.2</v>
       </c>
-      <c r="I105" s="104" t="n">
+      <c r="I105" s="113" t="n">
         <v>1.64</v>
       </c>
       <c r="J105" s="3"/>
@@ -14943,16 +15040,16 @@
       <c r="E106" s="44" t="n">
         <v>2616</v>
       </c>
-      <c r="F106" s="101" t="n">
+      <c r="F106" s="110" t="n">
         <v>1.83</v>
       </c>
-      <c r="G106" s="101" t="n">
+      <c r="G106" s="110" t="n">
         <v>1.85</v>
       </c>
-      <c r="H106" s="103" t="n">
+      <c r="H106" s="112" t="n">
         <v>1.31</v>
       </c>
-      <c r="I106" s="103" t="n">
+      <c r="I106" s="112" t="n">
         <v>2.43</v>
       </c>
       <c r="J106" s="3"/>
@@ -14971,16 +15068,16 @@
       <c r="E107" s="45" t="n">
         <v>9366</v>
       </c>
-      <c r="F107" s="102" t="n">
+      <c r="F107" s="111" t="n">
         <v>2.12</v>
       </c>
-      <c r="G107" s="102" t="n">
+      <c r="G107" s="111" t="n">
         <v>2.12</v>
       </c>
-      <c r="H107" s="104" t="n">
+      <c r="H107" s="113" t="n">
         <v>1.79</v>
       </c>
-      <c r="I107" s="104" t="n">
+      <c r="I107" s="113" t="n">
         <v>2.49</v>
       </c>
       <c r="J107" s="3"/>
@@ -14999,16 +15096,16 @@
       <c r="E108" s="44" t="n">
         <v>11318</v>
       </c>
-      <c r="F108" s="101" t="n">
+      <c r="F108" s="110" t="n">
         <v>0.89</v>
       </c>
-      <c r="G108" s="101" t="n">
+      <c r="G108" s="110" t="n">
         <v>0.89</v>
       </c>
-      <c r="H108" s="103" t="n">
+      <c r="H108" s="112" t="n">
         <v>0.71</v>
       </c>
-      <c r="I108" s="103" t="n">
+      <c r="I108" s="112" t="n">
         <v>1.1</v>
       </c>
       <c r="J108" s="3"/>
@@ -15027,16 +15124,16 @@
       <c r="E109" s="45" t="n">
         <v>7360</v>
       </c>
-      <c r="F109" s="102" t="n">
+      <c r="F109" s="111" t="n">
         <v>1.6</v>
       </c>
-      <c r="G109" s="102" t="n">
+      <c r="G109" s="111" t="n">
         <v>1.54</v>
       </c>
-      <c r="H109" s="104" t="n">
+      <c r="H109" s="113" t="n">
         <v>1.23</v>
       </c>
-      <c r="I109" s="104" t="n">
+      <c r="I109" s="113" t="n">
         <v>1.87</v>
       </c>
       <c r="J109" s="3"/>
@@ -15055,16 +15152,16 @@
       <c r="E110" s="44" t="n">
         <v>3015</v>
       </c>
-      <c r="F110" s="101" t="n">
+      <c r="F110" s="110" t="n">
         <v>1.36</v>
       </c>
-      <c r="G110" s="101" t="n">
+      <c r="G110" s="110" t="n">
         <v>1.38</v>
       </c>
-      <c r="H110" s="103" t="n">
+      <c r="H110" s="112" t="n">
         <v>0.91</v>
       </c>
-      <c r="I110" s="103" t="n">
+      <c r="I110" s="112" t="n">
         <v>1.82</v>
       </c>
       <c r="J110" s="3"/>
@@ -15083,16 +15180,16 @@
       <c r="E111" s="45" t="n">
         <v>2734</v>
       </c>
-      <c r="F111" s="102" t="n">
+      <c r="F111" s="111" t="n">
         <v>1.57</v>
       </c>
-      <c r="G111" s="102" t="n">
+      <c r="G111" s="111" t="n">
         <v>1.56</v>
       </c>
-      <c r="H111" s="104" t="n">
+      <c r="H111" s="113" t="n">
         <v>1.06</v>
       </c>
-      <c r="I111" s="104" t="n">
+      <c r="I111" s="113" t="n">
         <v>2.15</v>
       </c>
       <c r="J111" s="3"/>
@@ -15111,16 +15208,16 @@
       <c r="E112" s="44" t="n">
         <v>2577</v>
       </c>
-      <c r="F112" s="101" t="n">
+      <c r="F112" s="110" t="n">
         <v>0.97</v>
       </c>
-      <c r="G112" s="101" t="n">
+      <c r="G112" s="110" t="n">
         <v>1.1</v>
       </c>
-      <c r="H112" s="103" t="n">
+      <c r="H112" s="112" t="n">
         <v>0.66</v>
       </c>
-      <c r="I112" s="103" t="n">
+      <c r="I112" s="112" t="n">
         <v>1.62</v>
       </c>
       <c r="J112" s="3"/>
@@ -15139,16 +15236,16 @@
       <c r="E113" s="45" t="n">
         <v>2478</v>
       </c>
-      <c r="F113" s="102" t="n">
+      <c r="F113" s="111" t="n">
         <v>1.25</v>
       </c>
-      <c r="G113" s="102" t="n">
+      <c r="G113" s="111" t="n">
         <v>1.32</v>
       </c>
-      <c r="H113" s="104" t="n">
+      <c r="H113" s="113" t="n">
         <v>0.86</v>
       </c>
-      <c r="I113" s="104" t="n">
+      <c r="I113" s="113" t="n">
         <v>1.86</v>
       </c>
       <c r="J113" s="3"/>
@@ -15167,16 +15264,16 @@
       <c r="E114" s="44" t="n">
         <v>2168</v>
       </c>
-      <c r="F114" s="101" t="n">
+      <c r="F114" s="110" t="n">
         <v>1.29</v>
       </c>
-      <c r="G114" s="101" t="n">
+      <c r="G114" s="110" t="n">
         <v>1.04</v>
       </c>
-      <c r="H114" s="103" t="n">
+      <c r="H114" s="112" t="n">
         <v>0.62</v>
       </c>
-      <c r="I114" s="103" t="n">
+      <c r="I114" s="112" t="n">
         <v>1.57</v>
       </c>
       <c r="J114" s="3"/>
@@ -15195,16 +15292,16 @@
       <c r="E115" s="45" t="n">
         <v>234</v>
       </c>
-      <c r="F115" s="102" t="n">
+      <c r="F115" s="111" t="n">
         <v>4.27</v>
       </c>
-      <c r="G115" s="102" t="n">
+      <c r="G115" s="111" t="n">
         <v>5.03</v>
       </c>
-      <c r="H115" s="104" t="n">
+      <c r="H115" s="113" t="n">
         <v>1.92</v>
       </c>
-      <c r="I115" s="104" t="n">
+      <c r="I115" s="113" t="n">
         <v>10.61</v>
       </c>
       <c r="J115" s="3"/>
@@ -15223,16 +15320,16 @@
       <c r="E116" s="44" t="n">
         <v>66</v>
       </c>
-      <c r="F116" s="101" t="n">
+      <c r="F116" s="110" t="n">
         <v>3.03</v>
       </c>
-      <c r="G116" s="101" t="n">
+      <c r="G116" s="110" t="n">
         <v>1.6</v>
       </c>
-      <c r="H116" s="103" t="n">
+      <c r="H116" s="112" t="n">
         <v>0</v>
       </c>
-      <c r="I116" s="103" t="n">
+      <c r="I116" s="112" t="n">
         <v>4.1</v>
       </c>
       <c r="J116" s="3"/>
@@ -15251,16 +15348,16 @@
       <c r="E117" s="45" t="n">
         <v>3030</v>
       </c>
-      <c r="F117" s="102" t="n">
+      <c r="F117" s="111" t="n">
         <v>1.35</v>
       </c>
-      <c r="G117" s="102" t="n">
+      <c r="G117" s="111" t="n">
         <v>1.32</v>
       </c>
-      <c r="H117" s="104" t="n">
+      <c r="H117" s="113" t="n">
         <v>0.89</v>
       </c>
-      <c r="I117" s="104" t="n">
+      <c r="I117" s="113" t="n">
         <v>1.83</v>
       </c>
       <c r="J117" s="3"/>
@@ -15279,16 +15376,16 @@
       <c r="E118" s="44" t="n">
         <v>2655</v>
       </c>
-      <c r="F118" s="101" t="n">
+      <c r="F118" s="110" t="n">
         <v>2.11</v>
       </c>
-      <c r="G118" s="101" t="n">
+      <c r="G118" s="110" t="n">
         <v>2.15</v>
       </c>
-      <c r="H118" s="103" t="n">
+      <c r="H118" s="112" t="n">
         <v>1.45</v>
       </c>
-      <c r="I118" s="103" t="n">
+      <c r="I118" s="112" t="n">
         <v>2.88</v>
       </c>
       <c r="J118" s="3"/>
@@ -15307,16 +15404,16 @@
       <c r="E119" s="45" t="n">
         <v>1645</v>
       </c>
-      <c r="F119" s="102" t="n">
+      <c r="F119" s="111" t="n">
         <v>1.34</v>
       </c>
-      <c r="G119" s="102" t="n">
+      <c r="G119" s="111" t="n">
         <v>1.67</v>
       </c>
-      <c r="H119" s="104" t="n">
+      <c r="H119" s="113" t="n">
         <v>0.83</v>
       </c>
-      <c r="I119" s="104" t="n">
+      <c r="I119" s="113" t="n">
         <v>2.3</v>
       </c>
       <c r="J119" s="3"/>
@@ -15335,16 +15432,16 @@
       <c r="E120" s="44" t="n">
         <v>1315</v>
       </c>
-      <c r="F120" s="101" t="n">
+      <c r="F120" s="110" t="n">
         <v>1.67</v>
       </c>
-      <c r="G120" s="101" t="n">
+      <c r="G120" s="110" t="n">
         <v>1.7</v>
       </c>
-      <c r="H120" s="103" t="n">
+      <c r="H120" s="112" t="n">
         <v>1.08</v>
       </c>
-      <c r="I120" s="103" t="n">
+      <c r="I120" s="112" t="n">
         <v>2.37</v>
       </c>
       <c r="J120" s="3"/>
@@ -15363,16 +15460,16 @@
       <c r="E121" s="45" t="n">
         <v>841</v>
       </c>
-      <c r="F121" s="102" t="n">
+      <c r="F121" s="111" t="n">
         <v>1.31</v>
       </c>
-      <c r="G121" s="102" t="n">
+      <c r="G121" s="111" t="n">
         <v>1.17</v>
       </c>
-      <c r="H121" s="104" t="n">
+      <c r="H121" s="113" t="n">
         <v>0.4</v>
       </c>
-      <c r="I121" s="104" t="n">
+      <c r="I121" s="113" t="n">
         <v>1.96</v>
       </c>
       <c r="J121" s="3"/>
@@ -15391,16 +15488,16 @@
       <c r="E122" s="44" t="n">
         <v>605</v>
       </c>
-      <c r="F122" s="101" t="n">
+      <c r="F122" s="110" t="n">
         <v>1.16</v>
       </c>
-      <c r="G122" s="101" t="n">
+      <c r="G122" s="110" t="n">
         <v>1.24</v>
       </c>
-      <c r="H122" s="103" t="n">
+      <c r="H122" s="112" t="n">
         <v>0.41</v>
       </c>
-      <c r="I122" s="103" t="n">
+      <c r="I122" s="112" t="n">
         <v>2.28</v>
       </c>
       <c r="J122" s="3"/>
@@ -15419,16 +15516,16 @@
       <c r="E123" s="45" t="n">
         <v>576</v>
       </c>
-      <c r="F123" s="102" t="n">
+      <c r="F123" s="111" t="n">
         <v>0.87</v>
       </c>
-      <c r="G123" s="102" t="n">
+      <c r="G123" s="111" t="n">
         <v>0.82</v>
       </c>
-      <c r="H123" s="104" t="n">
+      <c r="H123" s="113" t="n">
         <v>0.22</v>
       </c>
-      <c r="I123" s="104" t="n">
+      <c r="I123" s="113" t="n">
         <v>1.69</v>
       </c>
       <c r="J123" s="3"/>
@@ -15447,16 +15544,16 @@
       <c r="E124" s="44" t="n">
         <v>512</v>
       </c>
-      <c r="F124" s="101" t="n">
+      <c r="F124" s="110" t="n">
         <v>2.93</v>
       </c>
-      <c r="G124" s="101" t="n">
+      <c r="G124" s="110" t="n">
         <v>2.4</v>
       </c>
-      <c r="H124" s="103" t="n">
+      <c r="H124" s="112" t="n">
         <v>0.79</v>
       </c>
-      <c r="I124" s="103" t="n">
+      <c r="I124" s="112" t="n">
         <v>4.27</v>
       </c>
       <c r="J124" s="3"/>
@@ -15475,16 +15572,16 @@
       <c r="E125" s="45" t="n">
         <v>470</v>
       </c>
-      <c r="F125" s="102" t="n">
+      <c r="F125" s="111" t="n">
         <v>0.43</v>
       </c>
-      <c r="G125" s="102" t="n">
+      <c r="G125" s="111" t="n">
         <v>0.42</v>
       </c>
-      <c r="H125" s="104" t="n">
+      <c r="H125" s="113" t="n">
         <v>0</v>
       </c>
-      <c r="I125" s="104" t="n">
+      <c r="I125" s="113" t="n">
         <v>1.39</v>
       </c>
       <c r="J125" s="3"/>
@@ -15503,16 +15600,16 @@
       <c r="E126" s="44" t="n">
         <v>435</v>
       </c>
-      <c r="F126" s="101" t="n">
+      <c r="F126" s="110" t="n">
         <v>1.38</v>
       </c>
-      <c r="G126" s="101" t="n">
+      <c r="G126" s="110" t="n">
         <v>1.05</v>
       </c>
-      <c r="H126" s="103" t="n">
+      <c r="H126" s="112" t="n">
         <v>0.35</v>
       </c>
-      <c r="I126" s="103" t="n">
+      <c r="I126" s="112" t="n">
         <v>2.05</v>
       </c>
       <c r="J126" s="3"/>
@@ -15531,16 +15628,16 @@
       <c r="E127" s="45" t="n">
         <v>404</v>
       </c>
-      <c r="F127" s="102" t="n">
+      <c r="F127" s="111" t="n">
         <v>3.71</v>
       </c>
-      <c r="G127" s="102" t="n">
+      <c r="G127" s="111" t="n">
         <v>3.16</v>
       </c>
-      <c r="H127" s="104" t="n">
+      <c r="H127" s="113" t="n">
         <v>1.59</v>
       </c>
-      <c r="I127" s="104" t="n">
+      <c r="I127" s="113" t="n">
         <v>5.07</v>
       </c>
       <c r="J127" s="3"/>
@@ -15559,16 +15656,16 @@
       <c r="E128" s="44" t="n">
         <v>354</v>
       </c>
-      <c r="F128" s="101" t="n">
+      <c r="F128" s="110" t="n">
         <v>1.13</v>
       </c>
-      <c r="G128" s="101" t="n">
+      <c r="G128" s="110" t="n">
         <v>2.11</v>
       </c>
-      <c r="H128" s="103" t="n">
+      <c r="H128" s="112" t="n">
         <v>0</v>
       </c>
-      <c r="I128" s="103" t="n">
+      <c r="I128" s="112" t="n">
         <v>5.37</v>
       </c>
       <c r="J128" s="3"/>
@@ -15587,16 +15684,16 @@
       <c r="E129" s="45" t="n">
         <v>17574</v>
       </c>
-      <c r="F129" s="102" t="n">
+      <c r="F129" s="111" t="n">
         <v>1.51</v>
       </c>
-      <c r="G129" s="102" t="n">
+      <c r="G129" s="111" t="n">
         <v>1.5</v>
       </c>
-      <c r="H129" s="104" t="n">
+      <c r="H129" s="113" t="n">
         <v>1.3</v>
       </c>
-      <c r="I129" s="104" t="n">
+      <c r="I129" s="113" t="n">
         <v>1.72</v>
       </c>
       <c r="J129" s="3"/>
@@ -15615,16 +15712,16 @@
       <c r="E130" s="44" t="n">
         <v>1232</v>
       </c>
-      <c r="F130" s="101" t="n">
+      <c r="F130" s="110" t="n">
         <v>1.62</v>
       </c>
-      <c r="G130" s="101" t="n">
+      <c r="G130" s="110" t="n">
         <v>1.55</v>
       </c>
-      <c r="H130" s="103" t="n">
+      <c r="H130" s="112" t="n">
         <v>0.79</v>
       </c>
-      <c r="I130" s="103" t="n">
+      <c r="I130" s="112" t="n">
         <v>2.38</v>
       </c>
       <c r="J130" s="3"/>
@@ -15643,16 +15740,16 @@
       <c r="E131" s="45" t="n">
         <v>726</v>
       </c>
-      <c r="F131" s="102" t="n">
+      <c r="F131" s="111" t="n">
         <v>1.65</v>
       </c>
-      <c r="G131" s="102" t="n">
+      <c r="G131" s="111" t="n">
         <v>1.3</v>
       </c>
-      <c r="H131" s="104" t="n">
+      <c r="H131" s="113" t="n">
         <v>0.42</v>
       </c>
-      <c r="I131" s="104" t="n">
+      <c r="I131" s="113" t="n">
         <v>2.3</v>
       </c>
       <c r="J131" s="3"/>
@@ -15671,16 +15768,16 @@
       <c r="E132" s="44" t="n">
         <v>489</v>
       </c>
-      <c r="F132" s="101" t="n">
+      <c r="F132" s="110" t="n">
         <v>0</v>
       </c>
-      <c r="G132" s="101" t="n">
+      <c r="G132" s="110" t="n">
         <v>0</v>
       </c>
-      <c r="H132" s="103" t="n">
+      <c r="H132" s="112" t="n">
         <v>0</v>
       </c>
-      <c r="I132" s="103" t="n">
+      <c r="I132" s="112" t="n">
         <v>0</v>
       </c>
       <c r="J132" s="3"/>
@@ -15699,16 +15796,16 @@
       <c r="E133" s="45" t="n">
         <v>355</v>
       </c>
-      <c r="F133" s="102" t="n">
+      <c r="F133" s="111" t="n">
         <v>0.85</v>
       </c>
-      <c r="G133" s="102" t="n">
+      <c r="G133" s="111" t="n">
         <v>1.43</v>
       </c>
-      <c r="H133" s="104" t="n">
+      <c r="H133" s="113" t="n">
         <v>0</v>
       </c>
-      <c r="I133" s="104" t="n">
+      <c r="I133" s="113" t="n">
         <v>3.45</v>
       </c>
       <c r="J133" s="3"/>
@@ -15727,16 +15824,16 @@
       <c r="E134" s="44" t="n">
         <v>20684</v>
       </c>
-      <c r="F134" s="101" t="n">
+      <c r="F134" s="110" t="n">
         <v>2.34</v>
       </c>
-      <c r="G134" s="101" t="n">
+      <c r="G134" s="110" t="n">
         <v>2.34</v>
       </c>
-      <c r="H134" s="103" t="n">
+      <c r="H134" s="112" t="n">
         <v>2.07</v>
       </c>
-      <c r="I134" s="103" t="n">
+      <c r="I134" s="112" t="n">
         <v>2.65</v>
       </c>
       <c r="J134" s="3"/>
@@ -15755,16 +15852,16 @@
       <c r="E135" s="45" t="n">
         <v>3793</v>
       </c>
-      <c r="F135" s="102" t="n">
+      <c r="F135" s="111" t="n">
         <v>2.11</v>
       </c>
-      <c r="G135" s="102" t="n">
+      <c r="G135" s="111" t="n">
         <v>2.09</v>
       </c>
-      <c r="H135" s="104" t="n">
+      <c r="H135" s="113" t="n">
         <v>1.61</v>
       </c>
-      <c r="I135" s="104" t="n">
+      <c r="I135" s="113" t="n">
         <v>2.7</v>
       </c>
       <c r="J135" s="3"/>
@@ -15783,16 +15880,16 @@
       <c r="E136" s="44" t="n">
         <v>16891</v>
       </c>
-      <c r="F136" s="101" t="n">
+      <c r="F136" s="110" t="n">
         <v>2.39</v>
       </c>
-      <c r="G136" s="101" t="n">
+      <c r="G136" s="110" t="n">
         <v>2.38</v>
       </c>
-      <c r="H136" s="103" t="n">
+      <c r="H136" s="112" t="n">
         <v>2.1</v>
       </c>
-      <c r="I136" s="103" t="n">
+      <c r="I136" s="112" t="n">
         <v>2.7</v>
       </c>
       <c r="J136" s="3"/>
@@ -15811,16 +15908,16 @@
       <c r="E137" s="45" t="n">
         <v>17574</v>
       </c>
-      <c r="F137" s="102" t="n">
+      <c r="F137" s="111" t="n">
         <v>2.45</v>
       </c>
-      <c r="G137" s="102" t="n">
+      <c r="G137" s="111" t="n">
         <v>2.44</v>
       </c>
-      <c r="H137" s="104" t="n">
+      <c r="H137" s="113" t="n">
         <v>2.13</v>
       </c>
-      <c r="I137" s="104" t="n">
+      <c r="I137" s="113" t="n">
         <v>2.72</v>
       </c>
       <c r="J137" s="3"/>
@@ -15839,16 +15936,16 @@
       <c r="E138" s="44" t="n">
         <v>3110</v>
       </c>
-      <c r="F138" s="101" t="n">
+      <c r="F138" s="110" t="n">
         <v>1.7</v>
       </c>
-      <c r="G138" s="101" t="n">
+      <c r="G138" s="110" t="n">
         <v>1.81</v>
       </c>
-      <c r="H138" s="103" t="n">
+      <c r="H138" s="112" t="n">
         <v>1.19</v>
       </c>
-      <c r="I138" s="103" t="n">
+      <c r="I138" s="112" t="n">
         <v>2.46</v>
       </c>
       <c r="J138" s="3"/>
@@ -15867,16 +15964,16 @@
       <c r="E139" s="45" t="n">
         <v>726</v>
       </c>
-      <c r="F139" s="102" t="n">
+      <c r="F139" s="111" t="n">
         <v>2.34</v>
       </c>
-      <c r="G139" s="102" t="n">
+      <c r="G139" s="111" t="n">
         <v>1.92</v>
       </c>
-      <c r="H139" s="104" t="n">
+      <c r="H139" s="113" t="n">
         <v>0.94</v>
       </c>
-      <c r="I139" s="104" t="n">
+      <c r="I139" s="113" t="n">
         <v>3.17</v>
       </c>
       <c r="J139" s="3"/>
@@ -15895,16 +15992,16 @@
       <c r="E140" s="44" t="n">
         <v>19958</v>
       </c>
-      <c r="F140" s="101" t="n">
+      <c r="F140" s="110" t="n">
         <v>2.33</v>
       </c>
-      <c r="G140" s="101" t="n">
+      <c r="G140" s="110" t="n">
         <v>2.33</v>
       </c>
-      <c r="H140" s="103" t="n">
+      <c r="H140" s="112" t="n">
         <v>2.08</v>
       </c>
-      <c r="I140" s="103" t="n">
+      <c r="I140" s="112" t="n">
         <v>2.61</v>
       </c>
       <c r="J140" s="3"/>
@@ -15923,16 +16020,16 @@
       <c r="E141" s="45" t="n">
         <v>1038</v>
       </c>
-      <c r="F141" s="102" t="n">
+      <c r="F141" s="111" t="n">
         <v>4.62</v>
       </c>
-      <c r="G141" s="102" t="n">
+      <c r="G141" s="111" t="n">
         <v>4.45</v>
       </c>
-      <c r="H141" s="104" t="n">
+      <c r="H141" s="113" t="n">
         <v>3.04</v>
       </c>
-      <c r="I141" s="104" t="n">
+      <c r="I141" s="113" t="n">
         <v>5.78</v>
       </c>
       <c r="J141" s="3"/>
@@ -15951,16 +16048,16 @@
       <c r="E142" s="44" t="n">
         <v>19646</v>
       </c>
-      <c r="F142" s="101" t="n">
+      <c r="F142" s="110" t="n">
         <v>2.21</v>
       </c>
-      <c r="G142" s="101" t="n">
+      <c r="G142" s="110" t="n">
         <v>2.22</v>
       </c>
-      <c r="H142" s="103" t="n">
+      <c r="H142" s="112" t="n">
         <v>1.96</v>
       </c>
-      <c r="I142" s="103" t="n">
+      <c r="I142" s="112" t="n">
         <v>2.54</v>
       </c>
       <c r="J142" s="3"/>
@@ -15979,16 +16076,16 @@
       <c r="E143" s="45" t="n">
         <v>286</v>
       </c>
-      <c r="F143" s="102" t="n">
+      <c r="F143" s="111" t="n">
         <v>5.24</v>
       </c>
-      <c r="G143" s="102" t="n">
+      <c r="G143" s="111" t="n">
         <v>5.52</v>
       </c>
-      <c r="H143" s="104" t="n">
+      <c r="H143" s="113" t="n">
         <v>2.27</v>
       </c>
-      <c r="I143" s="104" t="n">
+      <c r="I143" s="113" t="n">
         <v>10.35</v>
       </c>
       <c r="J143" s="3"/>
@@ -16007,16 +16104,16 @@
       <c r="E144" s="44" t="n">
         <v>20398</v>
       </c>
-      <c r="F144" s="101" t="n">
+      <c r="F144" s="110" t="n">
         <v>2.29</v>
       </c>
-      <c r="G144" s="101" t="n">
+      <c r="G144" s="110" t="n">
         <v>2.29</v>
       </c>
-      <c r="H144" s="103" t="n">
+      <c r="H144" s="112" t="n">
         <v>2.03</v>
       </c>
-      <c r="I144" s="103" t="n">
+      <c r="I144" s="112" t="n">
         <v>2.55</v>
       </c>
       <c r="J144" s="3"/>
@@ -16035,16 +16132,16 @@
       <c r="E145" s="45" t="n">
         <v>205</v>
       </c>
-      <c r="F145" s="102" t="n">
+      <c r="F145" s="111" t="n">
         <v>15.61</v>
       </c>
-      <c r="G145" s="102" t="n">
+      <c r="G145" s="111" t="n">
         <v>17.34</v>
       </c>
-      <c r="H145" s="104" t="n">
+      <c r="H145" s="113" t="n">
         <v>9.82</v>
       </c>
-      <c r="I145" s="104" t="n">
+      <c r="I145" s="113" t="n">
         <v>25.11</v>
       </c>
       <c r="J145" s="3"/>
@@ -16063,16 +16160,16 @@
       <c r="E146" s="44" t="n">
         <v>20479</v>
       </c>
-      <c r="F146" s="101" t="n">
+      <c r="F146" s="110" t="n">
         <v>2.2</v>
       </c>
-      <c r="G146" s="101" t="n">
+      <c r="G146" s="110" t="n">
         <v>2.21</v>
       </c>
-      <c r="H146" s="103" t="n">
+      <c r="H146" s="112" t="n">
         <v>1.95</v>
       </c>
-      <c r="I146" s="103" t="n">
+      <c r="I146" s="112" t="n">
         <v>2.49</v>
       </c>
       <c r="J146" s="3"/>
@@ -16091,16 +16188,16 @@
       <c r="E147" s="45" t="n">
         <v>18068</v>
       </c>
-      <c r="F147" s="102" t="n">
+      <c r="F147" s="111" t="n">
         <v>2.29</v>
       </c>
-      <c r="G147" s="102" t="n">
+      <c r="G147" s="111" t="n">
         <v>2.29</v>
       </c>
-      <c r="H147" s="104" t="n">
+      <c r="H147" s="113" t="n">
         <v>2</v>
       </c>
-      <c r="I147" s="104" t="n">
+      <c r="I147" s="113" t="n">
         <v>2.57</v>
       </c>
       <c r="J147" s="3"/>
@@ -16119,16 +16216,16 @@
       <c r="E148" s="44" t="n">
         <v>2616</v>
       </c>
-      <c r="F148" s="101" t="n">
+      <c r="F148" s="110" t="n">
         <v>2.64</v>
       </c>
-      <c r="G148" s="101" t="n">
+      <c r="G148" s="110" t="n">
         <v>2.72</v>
       </c>
-      <c r="H148" s="103" t="n">
+      <c r="H148" s="112" t="n">
         <v>2.05</v>
       </c>
-      <c r="I148" s="103" t="n">
+      <c r="I148" s="112" t="n">
         <v>3.42</v>
       </c>
       <c r="J148" s="3"/>
@@ -16147,16 +16244,16 @@
       <c r="E149" s="45" t="n">
         <v>9366</v>
       </c>
-      <c r="F149" s="102" t="n">
+      <c r="F149" s="111" t="n">
         <v>3.05</v>
       </c>
-      <c r="G149" s="102" t="n">
+      <c r="G149" s="111" t="n">
         <v>3.05</v>
       </c>
-      <c r="H149" s="104" t="n">
+      <c r="H149" s="113" t="n">
         <v>2.61</v>
       </c>
-      <c r="I149" s="104" t="n">
+      <c r="I149" s="113" t="n">
         <v>3.55</v>
       </c>
       <c r="J149" s="3"/>
@@ -16175,16 +16272,16 @@
       <c r="E150" s="44" t="n">
         <v>11318</v>
       </c>
-      <c r="F150" s="101" t="n">
+      <c r="F150" s="110" t="n">
         <v>1.74</v>
       </c>
-      <c r="G150" s="101" t="n">
+      <c r="G150" s="110" t="n">
         <v>1.74</v>
       </c>
-      <c r="H150" s="103" t="n">
+      <c r="H150" s="112" t="n">
         <v>1.47</v>
       </c>
-      <c r="I150" s="103" t="n">
+      <c r="I150" s="112" t="n">
         <v>2.01</v>
       </c>
       <c r="J150" s="3"/>
@@ -16203,16 +16300,16 @@
       <c r="E151" s="45" t="n">
         <v>7360</v>
       </c>
-      <c r="F151" s="102" t="n">
+      <c r="F151" s="111" t="n">
         <v>2.66</v>
       </c>
-      <c r="G151" s="102" t="n">
+      <c r="G151" s="111" t="n">
         <v>2.61</v>
       </c>
-      <c r="H151" s="104" t="n">
+      <c r="H151" s="113" t="n">
         <v>2.14</v>
       </c>
-      <c r="I151" s="104" t="n">
+      <c r="I151" s="113" t="n">
         <v>3.1</v>
       </c>
       <c r="J151" s="3"/>
@@ -16231,16 +16328,16 @@
       <c r="E152" s="44" t="n">
         <v>3015</v>
       </c>
-      <c r="F152" s="101" t="n">
+      <c r="F152" s="110" t="n">
         <v>2.55</v>
       </c>
-      <c r="G152" s="101" t="n">
+      <c r="G152" s="110" t="n">
         <v>2.6</v>
       </c>
-      <c r="H152" s="103" t="n">
+      <c r="H152" s="112" t="n">
         <v>1.94</v>
       </c>
-      <c r="I152" s="103" t="n">
+      <c r="I152" s="112" t="n">
         <v>3.25</v>
       </c>
       <c r="J152" s="3"/>
@@ -16259,16 +16356,16 @@
       <c r="E153" s="45" t="n">
         <v>2734</v>
       </c>
-      <c r="F153" s="102" t="n">
+      <c r="F153" s="111" t="n">
         <v>2.05</v>
       </c>
-      <c r="G153" s="102" t="n">
+      <c r="G153" s="111" t="n">
         <v>2.05</v>
       </c>
-      <c r="H153" s="104" t="n">
+      <c r="H153" s="113" t="n">
         <v>1.48</v>
       </c>
-      <c r="I153" s="104" t="n">
+      <c r="I153" s="113" t="n">
         <v>2.7</v>
       </c>
       <c r="J153" s="3"/>
@@ -16287,16 +16384,16 @@
       <c r="E154" s="44" t="n">
         <v>2577</v>
       </c>
-      <c r="F154" s="101" t="n">
+      <c r="F154" s="110" t="n">
         <v>1.75</v>
       </c>
-      <c r="G154" s="101" t="n">
+      <c r="G154" s="110" t="n">
         <v>1.83</v>
       </c>
-      <c r="H154" s="103" t="n">
+      <c r="H154" s="112" t="n">
         <v>1.31</v>
       </c>
-      <c r="I154" s="103" t="n">
+      <c r="I154" s="112" t="n">
         <v>2.42</v>
       </c>
       <c r="J154" s="3"/>
@@ -16315,16 +16412,16 @@
       <c r="E155" s="45" t="n">
         <v>2478</v>
       </c>
-      <c r="F155" s="102" t="n">
+      <c r="F155" s="111" t="n">
         <v>1.78</v>
       </c>
-      <c r="G155" s="102" t="n">
+      <c r="G155" s="111" t="n">
         <v>1.84</v>
       </c>
-      <c r="H155" s="104" t="n">
+      <c r="H155" s="113" t="n">
         <v>1.32</v>
       </c>
-      <c r="I155" s="104" t="n">
+      <c r="I155" s="113" t="n">
         <v>2.44</v>
       </c>
       <c r="J155" s="3"/>
@@ -16343,16 +16440,16 @@
       <c r="E156" s="44" t="n">
         <v>2168</v>
       </c>
-      <c r="F156" s="101" t="n">
+      <c r="F156" s="110" t="n">
         <v>1.98</v>
       </c>
-      <c r="G156" s="101" t="n">
+      <c r="G156" s="110" t="n">
         <v>1.67</v>
       </c>
-      <c r="H156" s="103" t="n">
+      <c r="H156" s="112" t="n">
         <v>1.14</v>
       </c>
-      <c r="I156" s="103" t="n">
+      <c r="I156" s="112" t="n">
         <v>2.35</v>
       </c>
       <c r="J156" s="3"/>
@@ -16371,16 +16468,16 @@
       <c r="E157" s="45" t="n">
         <v>234</v>
       </c>
-      <c r="F157" s="102" t="n">
+      <c r="F157" s="111" t="n">
         <v>5.13</v>
       </c>
-      <c r="G157" s="102" t="n">
+      <c r="G157" s="111" t="n">
         <v>5.57</v>
       </c>
-      <c r="H157" s="104" t="n">
+      <c r="H157" s="113" t="n">
         <v>2.26</v>
       </c>
-      <c r="I157" s="104" t="n">
+      <c r="I157" s="113" t="n">
         <v>10.83</v>
       </c>
       <c r="J157" s="3"/>
@@ -16399,16 +16496,16 @@
       <c r="E158" s="44" t="n">
         <v>66</v>
       </c>
-      <c r="F158" s="101" t="n">
+      <c r="F158" s="110" t="n">
         <v>10.61</v>
       </c>
-      <c r="G158" s="101" t="n">
+      <c r="G158" s="110" t="n">
         <v>13.64</v>
       </c>
-      <c r="H158" s="103" t="n">
+      <c r="H158" s="112" t="n">
         <v>2.23</v>
       </c>
-      <c r="I158" s="103" t="n">
+      <c r="I158" s="112" t="n">
         <v>26.13</v>
       </c>
       <c r="J158" s="3"/>
@@ -16427,16 +16524,16 @@
       <c r="E159" s="45" t="n">
         <v>3030</v>
       </c>
-      <c r="F159" s="102" t="n">
+      <c r="F159" s="111" t="n">
         <v>2.11</v>
       </c>
-      <c r="G159" s="102" t="n">
+      <c r="G159" s="111" t="n">
         <v>2.04</v>
       </c>
-      <c r="H159" s="104" t="n">
+      <c r="H159" s="113" t="n">
         <v>1.48</v>
       </c>
-      <c r="I159" s="104" t="n">
+      <c r="I159" s="113" t="n">
         <v>2.75</v>
       </c>
       <c r="J159" s="3"/>
@@ -16455,16 +16552,16 @@
       <c r="E160" s="44" t="n">
         <v>2655</v>
       </c>
-      <c r="F160" s="101" t="n">
+      <c r="F160" s="110" t="n">
         <v>3.39</v>
       </c>
-      <c r="G160" s="101" t="n">
+      <c r="G160" s="110" t="n">
         <v>3.43</v>
       </c>
-      <c r="H160" s="103" t="n">
+      <c r="H160" s="112" t="n">
         <v>2.46</v>
       </c>
-      <c r="I160" s="103" t="n">
+      <c r="I160" s="112" t="n">
         <v>4.51</v>
       </c>
       <c r="J160" s="3"/>
@@ -16483,16 +16580,16 @@
       <c r="E161" s="45" t="n">
         <v>1645</v>
       </c>
-      <c r="F161" s="102" t="n">
+      <c r="F161" s="111" t="n">
         <v>1.82</v>
       </c>
-      <c r="G161" s="102" t="n">
+      <c r="G161" s="111" t="n">
         <v>2.12</v>
       </c>
-      <c r="H161" s="104" t="n">
+      <c r="H161" s="113" t="n">
         <v>1.18</v>
       </c>
-      <c r="I161" s="104" t="n">
+      <c r="I161" s="113" t="n">
         <v>2.83</v>
       </c>
       <c r="J161" s="3"/>
@@ -16511,16 +16608,16 @@
       <c r="E162" s="44" t="n">
         <v>1315</v>
       </c>
-      <c r="F162" s="101" t="n">
+      <c r="F162" s="110" t="n">
         <v>2.36</v>
       </c>
-      <c r="G162" s="101" t="n">
+      <c r="G162" s="110" t="n">
         <v>2.35</v>
       </c>
-      <c r="H162" s="103" t="n">
+      <c r="H162" s="112" t="n">
         <v>1.55</v>
       </c>
-      <c r="I162" s="103" t="n">
+      <c r="I162" s="112" t="n">
         <v>3.11</v>
       </c>
       <c r="J162" s="3"/>
@@ -16539,16 +16636,16 @@
       <c r="E163" s="45" t="n">
         <v>841</v>
       </c>
-      <c r="F163" s="102" t="n">
+      <c r="F163" s="111" t="n">
         <v>2.85</v>
       </c>
-      <c r="G163" s="102" t="n">
+      <c r="G163" s="111" t="n">
         <v>2.45</v>
       </c>
-      <c r="H163" s="104" t="n">
+      <c r="H163" s="113" t="n">
         <v>1.46</v>
       </c>
-      <c r="I163" s="104" t="n">
+      <c r="I163" s="113" t="n">
         <v>3.59</v>
       </c>
       <c r="J163" s="3"/>
@@ -16567,16 +16664,16 @@
       <c r="E164" s="44" t="n">
         <v>605</v>
       </c>
-      <c r="F164" s="101" t="n">
+      <c r="F164" s="110" t="n">
         <v>2.48</v>
       </c>
-      <c r="G164" s="101" t="n">
+      <c r="G164" s="110" t="n">
         <v>2.57</v>
       </c>
-      <c r="H164" s="103" t="n">
+      <c r="H164" s="112" t="n">
         <v>1.22</v>
       </c>
-      <c r="I164" s="103" t="n">
+      <c r="I164" s="112" t="n">
         <v>4.11</v>
       </c>
       <c r="J164" s="3"/>
@@ -16595,16 +16692,16 @@
       <c r="E165" s="45" t="n">
         <v>576</v>
       </c>
-      <c r="F165" s="102" t="n">
+      <c r="F165" s="111" t="n">
         <v>2.08</v>
       </c>
-      <c r="G165" s="102" t="n">
+      <c r="G165" s="111" t="n">
         <v>2.24</v>
       </c>
-      <c r="H165" s="104" t="n">
+      <c r="H165" s="113" t="n">
         <v>0.79</v>
       </c>
-      <c r="I165" s="104" t="n">
+      <c r="I165" s="113" t="n">
         <v>4.33</v>
       </c>
       <c r="J165" s="3"/>
@@ -16623,16 +16720,16 @@
       <c r="E166" s="44" t="n">
         <v>512</v>
       </c>
-      <c r="F166" s="101" t="n">
+      <c r="F166" s="110" t="n">
         <v>5.08</v>
       </c>
-      <c r="G166" s="101" t="n">
+      <c r="G166" s="110" t="n">
         <v>4.4</v>
       </c>
-      <c r="H166" s="103" t="n">
+      <c r="H166" s="112" t="n">
         <v>1.96</v>
       </c>
-      <c r="I166" s="103" t="n">
+      <c r="I166" s="112" t="n">
         <v>7.6</v>
       </c>
       <c r="J166" s="3"/>
@@ -16651,16 +16748,16 @@
       <c r="E167" s="45" t="n">
         <v>470</v>
       </c>
-      <c r="F167" s="102" t="n">
+      <c r="F167" s="111" t="n">
         <v>1.91</v>
       </c>
-      <c r="G167" s="102" t="n">
+      <c r="G167" s="111" t="n">
         <v>1.65</v>
       </c>
-      <c r="H167" s="104" t="n">
+      <c r="H167" s="113" t="n">
         <v>0.64</v>
       </c>
-      <c r="I167" s="104" t="n">
+      <c r="I167" s="113" t="n">
         <v>3.08</v>
       </c>
       <c r="J167" s="3"/>
@@ -16679,16 +16776,16 @@
       <c r="E168" s="44" t="n">
         <v>435</v>
       </c>
-      <c r="F168" s="101" t="n">
+      <c r="F168" s="110" t="n">
         <v>2.3</v>
       </c>
-      <c r="G168" s="101" t="n">
+      <c r="G168" s="110" t="n">
         <v>2.19</v>
       </c>
-      <c r="H168" s="103" t="n">
+      <c r="H168" s="112" t="n">
         <v>0.86</v>
       </c>
-      <c r="I168" s="103" t="n">
+      <c r="I168" s="112" t="n">
         <v>3.9</v>
       </c>
       <c r="J168" s="3"/>
@@ -16707,16 +16804,16 @@
       <c r="E169" s="45" t="n">
         <v>404</v>
       </c>
-      <c r="F169" s="102" t="n">
+      <c r="F169" s="111" t="n">
         <v>4.7</v>
       </c>
-      <c r="G169" s="102" t="n">
+      <c r="G169" s="111" t="n">
         <v>4.08</v>
       </c>
-      <c r="H169" s="104" t="n">
+      <c r="H169" s="113" t="n">
         <v>1.99</v>
       </c>
-      <c r="I169" s="104" t="n">
+      <c r="I169" s="113" t="n">
         <v>6.4</v>
       </c>
       <c r="J169" s="3"/>
@@ -16735,16 +16832,16 @@
       <c r="E170" s="44" t="n">
         <v>354</v>
       </c>
-      <c r="F170" s="101" t="n">
+      <c r="F170" s="110" t="n">
         <v>1.41</v>
       </c>
-      <c r="G170" s="101" t="n">
+      <c r="G170" s="110" t="n">
         <v>2.63</v>
       </c>
-      <c r="H170" s="103" t="n">
+      <c r="H170" s="112" t="n">
         <v>0.12</v>
       </c>
-      <c r="I170" s="103" t="n">
+      <c r="I170" s="112" t="n">
         <v>5.86</v>
       </c>
       <c r="J170" s="3"/>
@@ -16763,16 +16860,16 @@
       <c r="E171" s="45" t="n">
         <v>17574</v>
       </c>
-      <c r="F171" s="102" t="n">
+      <c r="F171" s="111" t="n">
         <v>2.45</v>
       </c>
-      <c r="G171" s="102" t="n">
+      <c r="G171" s="111" t="n">
         <v>2.44</v>
       </c>
-      <c r="H171" s="104" t="n">
+      <c r="H171" s="113" t="n">
         <v>2.13</v>
       </c>
-      <c r="I171" s="104" t="n">
+      <c r="I171" s="113" t="n">
         <v>2.74</v>
       </c>
       <c r="J171" s="3"/>
@@ -16791,16 +16888,16 @@
       <c r="E172" s="44" t="n">
         <v>1232</v>
       </c>
-      <c r="F172" s="101" t="n">
+      <c r="F172" s="110" t="n">
         <v>1.95</v>
       </c>
-      <c r="G172" s="101" t="n">
+      <c r="G172" s="110" t="n">
         <v>1.88</v>
       </c>
-      <c r="H172" s="103" t="n">
+      <c r="H172" s="112" t="n">
         <v>0.93</v>
       </c>
-      <c r="I172" s="103" t="n">
+      <c r="I172" s="112" t="n">
         <v>2.76</v>
       </c>
       <c r="J172" s="3"/>
@@ -16819,16 +16916,16 @@
       <c r="E173" s="45" t="n">
         <v>726</v>
       </c>
-      <c r="F173" s="102" t="n">
+      <c r="F173" s="111" t="n">
         <v>2.34</v>
       </c>
-      <c r="G173" s="102" t="n">
+      <c r="G173" s="111" t="n">
         <v>1.92</v>
       </c>
-      <c r="H173" s="104" t="n">
+      <c r="H173" s="113" t="n">
         <v>0.98</v>
       </c>
-      <c r="I173" s="104" t="n">
+      <c r="I173" s="113" t="n">
         <v>2.99</v>
       </c>
       <c r="J173" s="3"/>
@@ -16847,16 +16944,16 @@
       <c r="E174" s="44" t="n">
         <v>489</v>
       </c>
-      <c r="F174" s="101" t="n">
+      <c r="F174" s="110" t="n">
         <v>0.2</v>
       </c>
-      <c r="G174" s="101" t="n">
+      <c r="G174" s="110" t="n">
         <v>0.22</v>
       </c>
-      <c r="H174" s="103" t="n">
+      <c r="H174" s="112" t="n">
         <v>0</v>
       </c>
-      <c r="I174" s="103" t="n">
+      <c r="I174" s="112" t="n">
         <v>0.68</v>
       </c>
       <c r="J174" s="3"/>
@@ -16875,16 +16972,16 @@
       <c r="E175" s="68" t="n">
         <v>355</v>
       </c>
-      <c r="F175" s="105" t="n">
+      <c r="F175" s="114" t="n">
         <v>2.25</v>
       </c>
-      <c r="G175" s="105" t="n">
+      <c r="G175" s="114" t="n">
         <v>2.96</v>
       </c>
-      <c r="H175" s="106" t="n">
+      <c r="H175" s="115" t="n">
         <v>0.97</v>
       </c>
-      <c r="I175" s="106" t="n">
+      <c r="I175" s="115" t="n">
         <v>5.41</v>
       </c>
       <c r="J175" s="3"/>
@@ -17229,7 +17326,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS19&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="R963d398414614916"/>
+    <tablePart ns1:id="R52443122152f4039"/>
   </tableParts>
 </worksheet>
 </file>
@@ -17918,7 +18015,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS20&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="R508c803aae424245"/>
+    <tablePart ns1:id="Ref800e8f925946d3"/>
   </tableParts>
 </worksheet>
 </file>
@@ -19942,7 +20039,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS21&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="R7f68dfb5e97e411c"/>
+    <tablePart ns1:id="Re6a747c84e6048eb"/>
   </tableParts>
 </worksheet>
 </file>
@@ -20081,10 +20178,10 @@
         <v>5.162</v>
       </c>
       <c r="G8" s="64" t="n">
-        <v>4.654</v>
+        <v>4.577</v>
       </c>
       <c r="H8" s="64" t="n">
-        <v>5.66</v>
+        <v>5.611</v>
       </c>
       <c r="I8" s="3"/>
     </row>
@@ -20106,10 +20203,10 @@
         <v>4.705</v>
       </c>
       <c r="G9" s="65" t="n">
-        <v>4.179</v>
+        <v>4.152</v>
       </c>
       <c r="H9" s="65" t="n">
-        <v>5.195</v>
+        <v>5.323</v>
       </c>
       <c r="I9" s="3"/>
     </row>
@@ -20131,10 +20228,10 @@
         <v>4.835</v>
       </c>
       <c r="G10" s="64" t="n">
-        <v>4.405</v>
+        <v>4.416</v>
       </c>
       <c r="H10" s="64" t="n">
-        <v>5.283</v>
+        <v>5.265</v>
       </c>
       <c r="I10" s="3"/>
     </row>
@@ -20156,10 +20253,10 @@
         <v>4.854</v>
       </c>
       <c r="G11" s="65" t="n">
-        <v>4.424</v>
+        <v>4.454</v>
       </c>
       <c r="H11" s="65" t="n">
-        <v>5.365</v>
+        <v>5.293</v>
       </c>
       <c r="I11" s="3"/>
     </row>
@@ -20181,10 +20278,10 @@
         <v>4.585</v>
       </c>
       <c r="G12" s="64" t="n">
-        <v>4.239</v>
+        <v>4.216</v>
       </c>
       <c r="H12" s="64" t="n">
-        <v>4.947</v>
+        <v>4.936</v>
       </c>
       <c r="I12" s="3"/>
     </row>
@@ -20206,10 +20303,10 @@
         <v>4.379</v>
       </c>
       <c r="G13" s="65" t="n">
-        <v>4.051</v>
+        <v>4.073</v>
       </c>
       <c r="H13" s="65" t="n">
-        <v>4.707</v>
+        <v>4.736</v>
       </c>
       <c r="I13" s="3"/>
     </row>
@@ -20231,10 +20328,10 @@
         <v>5.04</v>
       </c>
       <c r="G14" s="64" t="n">
-        <v>4.702</v>
+        <v>4.729</v>
       </c>
       <c r="H14" s="64" t="n">
-        <v>5.349</v>
+        <v>5.394</v>
       </c>
       <c r="I14" s="3"/>
     </row>
@@ -20256,10 +20353,10 @@
         <v>4.886</v>
       </c>
       <c r="G15" s="65" t="n">
-        <v>4.515</v>
+        <v>4.565</v>
       </c>
       <c r="H15" s="65" t="n">
-        <v>5.241</v>
+        <v>5.215</v>
       </c>
       <c r="I15" s="3"/>
     </row>
@@ -20281,10 +20378,10 @@
         <v>5.562</v>
       </c>
       <c r="G16" s="64" t="n">
-        <v>5.182</v>
+        <v>5.141</v>
       </c>
       <c r="H16" s="64" t="n">
-        <v>5.918</v>
+        <v>5.963</v>
       </c>
       <c r="I16" s="3"/>
     </row>
@@ -20306,10 +20403,10 @@
         <v>7.096</v>
       </c>
       <c r="G17" s="65" t="n">
-        <v>6.633</v>
+        <v>6.645</v>
       </c>
       <c r="H17" s="65" t="n">
-        <v>7.551</v>
+        <v>7.562</v>
       </c>
       <c r="I17" s="3"/>
     </row>
@@ -20791,10 +20888,10 @@
         <v>6.079</v>
       </c>
       <c r="G38" s="64" t="n">
-        <v>5.489</v>
+        <v>5.413</v>
       </c>
       <c r="H38" s="64" t="n">
-        <v>6.689</v>
+        <v>6.706</v>
       </c>
       <c r="I38" s="3"/>
     </row>
@@ -20816,10 +20913,10 @@
         <v>5.262</v>
       </c>
       <c r="G39" s="65" t="n">
-        <v>4.594</v>
+        <v>4.642</v>
       </c>
       <c r="H39" s="65" t="n">
-        <v>5.787</v>
+        <v>5.862</v>
       </c>
       <c r="I39" s="3"/>
     </row>
@@ -20841,10 +20938,10 @@
         <v>5.328</v>
       </c>
       <c r="G40" s="64" t="n">
-        <v>4.856</v>
+        <v>4.834</v>
       </c>
       <c r="H40" s="64" t="n">
-        <v>5.867</v>
+        <v>5.875</v>
       </c>
       <c r="I40" s="3"/>
     </row>
@@ -20866,10 +20963,10 @@
         <v>5.687</v>
       </c>
       <c r="G41" s="65" t="n">
-        <v>5.205</v>
+        <v>5.108</v>
       </c>
       <c r="H41" s="65" t="n">
-        <v>6.225</v>
+        <v>6.258</v>
       </c>
       <c r="I41" s="3"/>
     </row>
@@ -20891,10 +20988,10 @@
         <v>6.809</v>
       </c>
       <c r="G42" s="64" t="n">
-        <v>6.231</v>
+        <v>6.182</v>
       </c>
       <c r="H42" s="64" t="n">
-        <v>7.417</v>
+        <v>7.363</v>
       </c>
       <c r="I42" s="3"/>
     </row>
@@ -20916,10 +21013,10 @@
         <v>8.218</v>
       </c>
       <c r="G43" s="65" t="n">
-        <v>7.749</v>
+        <v>7.818</v>
       </c>
       <c r="H43" s="65" t="n">
-        <v>8.597</v>
+        <v>8.625</v>
       </c>
       <c r="I43" s="3"/>
     </row>
@@ -20941,10 +21038,10 @@
         <v>9.041</v>
       </c>
       <c r="G44" s="64" t="n">
-        <v>8.441</v>
+        <v>8.529</v>
       </c>
       <c r="H44" s="64" t="n">
-        <v>9.544</v>
+        <v>9.485</v>
       </c>
       <c r="I44" s="3"/>
     </row>
@@ -20966,10 +21063,10 @@
         <v>9.498</v>
       </c>
       <c r="G45" s="65" t="n">
-        <v>8.937</v>
+        <v>9.008</v>
       </c>
       <c r="H45" s="65" t="n">
-        <v>10.006</v>
+        <v>9.976</v>
       </c>
       <c r="I45" s="3"/>
     </row>
@@ -20991,10 +21088,10 @@
         <v>10.222</v>
       </c>
       <c r="G46" s="64" t="n">
-        <v>9.754</v>
+        <v>9.692</v>
       </c>
       <c r="H46" s="64" t="n">
-        <v>10.694</v>
+        <v>10.681</v>
       </c>
       <c r="I46" s="3"/>
     </row>
@@ -21016,10 +21113,10 @@
         <v>12.135</v>
       </c>
       <c r="G47" s="65" t="n">
-        <v>11.485</v>
+        <v>11.561</v>
       </c>
       <c r="H47" s="65" t="n">
-        <v>12.721</v>
+        <v>12.783</v>
       </c>
       <c r="I47" s="3"/>
     </row>
@@ -21791,10 +21888,10 @@
         <v>5.364</v>
       </c>
       <c r="G78" s="64" t="n">
-        <v>4.59</v>
+        <v>4.6</v>
       </c>
       <c r="H78" s="64" t="n">
-        <v>6.35</v>
+        <v>6.137</v>
       </c>
       <c r="I78" s="3"/>
     </row>
@@ -21816,10 +21913,10 @@
         <v>5.442</v>
       </c>
       <c r="G79" s="65" t="n">
-        <v>4.791</v>
+        <v>4.592</v>
       </c>
       <c r="H79" s="65" t="n">
-        <v>6.245</v>
+        <v>6.291</v>
       </c>
       <c r="I79" s="3"/>
     </row>
@@ -21841,10 +21938,10 @@
         <v>4.674</v>
       </c>
       <c r="G80" s="64" t="n">
-        <v>4.225</v>
+        <v>4.172</v>
       </c>
       <c r="H80" s="64" t="n">
-        <v>5.213</v>
+        <v>5.196</v>
       </c>
       <c r="I80" s="3"/>
     </row>
@@ -21866,10 +21963,10 @@
         <v>5.046</v>
       </c>
       <c r="G81" s="65" t="n">
-        <v>4.562</v>
+        <v>4.543</v>
       </c>
       <c r="H81" s="65" t="n">
-        <v>5.605</v>
+        <v>5.619</v>
       </c>
       <c r="I81" s="3"/>
     </row>
@@ -21891,10 +21988,10 @@
         <v>5.134</v>
       </c>
       <c r="G82" s="64" t="n">
-        <v>4.678</v>
+        <v>4.662</v>
       </c>
       <c r="H82" s="64" t="n">
-        <v>5.639</v>
+        <v>5.6</v>
       </c>
       <c r="I82" s="3"/>
     </row>
@@ -21916,10 +22013,10 @@
         <v>4.581</v>
       </c>
       <c r="G83" s="65" t="n">
-        <v>4.221</v>
+        <v>4.197</v>
       </c>
       <c r="H83" s="65" t="n">
-        <v>4.97</v>
+        <v>5.048</v>
       </c>
       <c r="I83" s="3"/>
     </row>
@@ -21941,10 +22038,10 @@
         <v>4.152</v>
       </c>
       <c r="G84" s="64" t="n">
-        <v>3.804</v>
+        <v>3.836</v>
       </c>
       <c r="H84" s="64" t="n">
-        <v>4.485</v>
+        <v>4.507</v>
       </c>
       <c r="I84" s="3"/>
     </row>
@@ -21966,10 +22063,10 @@
         <v>3.949</v>
       </c>
       <c r="G85" s="65" t="n">
-        <v>3.688</v>
+        <v>3.656</v>
       </c>
       <c r="H85" s="65" t="n">
-        <v>4.238</v>
+        <v>4.266</v>
       </c>
       <c r="I85" s="3"/>
     </row>
@@ -21991,10 +22088,10 @@
         <v>3.987</v>
       </c>
       <c r="G86" s="64" t="n">
-        <v>3.73</v>
+        <v>3.701</v>
       </c>
       <c r="H86" s="64" t="n">
-        <v>4.28</v>
+        <v>4.312</v>
       </c>
       <c r="I86" s="3"/>
     </row>
@@ -22016,10 +22113,10 @@
         <v>3.535</v>
       </c>
       <c r="G87" s="70" t="n">
-        <v>3.31</v>
+        <v>3.303</v>
       </c>
       <c r="H87" s="70" t="n">
-        <v>3.745</v>
+        <v>3.777</v>
       </c>
       <c r="I87" s="3"/>
     </row>
@@ -22338,7 +22435,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS2&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="R54b5b6882f0b413f"/>
+    <tablePart ns1:id="R7ccc65d368944179"/>
   </tableParts>
 </worksheet>
 </file>
@@ -22580,10 +22677,10 @@
         <v>1.065</v>
       </c>
       <c r="H8" s="64" t="n">
-        <v>0.947</v>
+        <v>0.952</v>
       </c>
       <c r="I8" s="64" t="n">
-        <v>1.224</v>
+        <v>1.229</v>
       </c>
       <c r="J8" s="62" t="n">
         <v>8.284</v>
@@ -22595,19 +22692,19 @@
         <v>1.191</v>
       </c>
       <c r="M8" s="64" t="n">
-        <v>1.098</v>
+        <v>1.086</v>
       </c>
       <c r="N8" s="64" t="n">
-        <v>1.355</v>
+        <v>1.341</v>
       </c>
       <c r="O8" s="44" t="n">
         <v>19</v>
       </c>
       <c r="P8" s="62" t="n">
-        <v>21.94</v>
+        <v>21.9</v>
       </c>
       <c r="Q8" s="62" t="n">
-        <v>1.155</v>
+        <v>1.153</v>
       </c>
       <c r="R8" s="44" t="n">
         <v>1096</v>
@@ -22737,10 +22834,10 @@
         <v>1.785</v>
       </c>
       <c r="H11" s="65" t="n">
-        <v>1.613</v>
+        <v>1.614</v>
       </c>
       <c r="I11" s="65" t="n">
-        <v>1.999</v>
+        <v>1.981</v>
       </c>
       <c r="J11" s="63" t="n">
         <v>10.584</v>
@@ -22752,19 +22849,19 @@
         <v>1.622</v>
       </c>
       <c r="M11" s="65" t="n">
-        <v>1.499</v>
+        <v>1.494</v>
       </c>
       <c r="N11" s="65" t="n">
-        <v>1.829</v>
+        <v>1.863</v>
       </c>
       <c r="O11" s="45" t="n">
         <v>66</v>
       </c>
       <c r="P11" s="63" t="n">
-        <v>60.94</v>
+        <v>61.74</v>
       </c>
       <c r="Q11" s="63" t="n">
-        <v>0.923</v>
+        <v>0.935</v>
       </c>
       <c r="R11" s="45" t="n">
         <v>1500</v>
@@ -22957,10 +23054,10 @@
         <v>0.672</v>
       </c>
       <c r="H15" s="70" t="n">
-        <v>0.58</v>
+        <v>0.564</v>
       </c>
       <c r="I15" s="70" t="n">
-        <v>0.811</v>
+        <v>0.796</v>
       </c>
       <c r="J15" s="69" t="n">
         <v>26.492</v>
@@ -22972,19 +23069,19 @@
         <v>0.683</v>
       </c>
       <c r="M15" s="70" t="n">
-        <v>0.585</v>
+        <v>0.595</v>
       </c>
       <c r="N15" s="70" t="n">
-        <v>0.902</v>
+        <v>0.92</v>
       </c>
       <c r="O15" s="68" t="n">
         <v>350</v>
       </c>
       <c r="P15" s="69" t="n">
-        <v>320.7</v>
+        <v>318.72</v>
       </c>
       <c r="Q15" s="69" t="n">
-        <v>0.916</v>
+        <v>0.911</v>
       </c>
       <c r="R15" s="68" t="n">
         <v>1527</v>
@@ -23556,7 +23653,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS3&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="R38074993334a4398"/>
+    <tablePart ns1:id="Rb20cb82031ab44c5"/>
   </tableParts>
 </worksheet>
 </file>
@@ -23723,7 +23820,7 @@
       <c r="I8" s="44" t="n">
         <v>36244</v>
       </c>
-      <c r="J8" s="62" t="n">
+      <c r="J8" s="44" t="n">
         <v>36244</v>
       </c>
       <c r="K8" s="3"/>
@@ -23754,7 +23851,7 @@
       <c r="I9" s="45" t="n">
         <v>36244</v>
       </c>
-      <c r="J9" s="63" t="n">
+      <c r="J9" s="45" t="n">
         <v>36244</v>
       </c>
       <c r="K9" s="3"/>
@@ -23785,7 +23882,7 @@
       <c r="I10" s="44" t="n">
         <v>36244</v>
       </c>
-      <c r="J10" s="62" t="n">
+      <c r="J10" s="44" t="n">
         <v>36244</v>
       </c>
       <c r="K10" s="3"/>
@@ -23909,7 +24006,7 @@
       <c r="I14" s="44" t="n">
         <v>4036</v>
       </c>
-      <c r="J14" s="62" t="n">
+      <c r="J14" s="44" t="n">
         <v>4036</v>
       </c>
       <c r="K14" s="3"/>
@@ -23940,7 +24037,7 @@
       <c r="I15" s="45" t="n">
         <v>4036</v>
       </c>
-      <c r="J15" s="63" t="n">
+      <c r="J15" s="45" t="n">
         <v>4036</v>
       </c>
       <c r="K15" s="3"/>
@@ -23971,7 +24068,7 @@
       <c r="I16" s="44" t="n">
         <v>4036</v>
       </c>
-      <c r="J16" s="62" t="n">
+      <c r="J16" s="44" t="n">
         <v>4036</v>
       </c>
       <c r="K16" s="3"/>
@@ -24095,7 +24192,7 @@
       <c r="I20" s="44" t="n">
         <v>24503</v>
       </c>
-      <c r="J20" s="62" t="n">
+      <c r="J20" s="44" t="n">
         <v>24503</v>
       </c>
       <c r="K20" s="3"/>
@@ -24126,7 +24223,7 @@
       <c r="I21" s="45" t="n">
         <v>24503</v>
       </c>
-      <c r="J21" s="63" t="n">
+      <c r="J21" s="45" t="n">
         <v>24503</v>
       </c>
       <c r="K21" s="3"/>
@@ -24157,7 +24254,7 @@
       <c r="I22" s="44" t="n">
         <v>24503</v>
       </c>
-      <c r="J22" s="62" t="n">
+      <c r="J22" s="44" t="n">
         <v>24503</v>
       </c>
       <c r="K22" s="3"/>
@@ -24189,7 +24286,7 @@
         <v>24503</v>
       </c>
       <c r="J23" s="73" t="n">
-        <v>1886552693493852.2</v>
+        <v>1886552693493852</v>
       </c>
       <c r="K23" s="3"/>
     </row>
@@ -24220,7 +24317,7 @@
         <v>24503</v>
       </c>
       <c r="J24" s="74" t="n">
-        <v>1886552693493852.2</v>
+        <v>1886552693493852</v>
       </c>
       <c r="K24" s="3"/>
     </row>
@@ -24251,7 +24348,7 @@
         <v>24503</v>
       </c>
       <c r="J25" s="75" t="n">
-        <v>1886552693493852.2</v>
+        <v>1886552693493852</v>
       </c>
       <c r="K25" s="3"/>
     </row>
@@ -24620,7 +24717,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS4&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="Rc3057c1e89834a4e"/>
+    <tablePart ns1:id="R8f449789c18c440a"/>
   </tableParts>
 </worksheet>
 </file>
@@ -24743,7 +24840,7 @@
     </row>
     <row r="8" ht="27" customHeight="1">
       <c r="A8" s="3"/>
-      <c r="B8" s="58" t="n">
+      <c r="B8" s="58" t="str">
         <v>1</v>
       </c>
       <c r="C8" s="44" t="n">
@@ -24768,7 +24865,7 @@
     </row>
     <row r="9" ht="27" customHeight="1">
       <c r="A9" s="3"/>
-      <c r="B9" s="59" t="n">
+      <c r="B9" s="59" t="str">
         <v>2</v>
       </c>
       <c r="C9" s="45" t="n">
@@ -25225,7 +25322,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS5&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="R2eb76b71816540ae"/>
+    <tablePart ns1:id="R4dbcff9f68df435f"/>
   </tableParts>
 </worksheet>
 </file>
@@ -25490,11 +25587,11 @@
       <c r="O8" s="62" t="n">
         <v>489.5</v>
       </c>
-      <c r="P8" s="64" t="n">
+      <c r="P8" s="84" t="n">
         <v>425</v>
       </c>
-      <c r="Q8" s="84" t="n">
-        <v>541</v>
+      <c r="Q8" s="64" t="n">
+        <v>547</v>
       </c>
       <c r="R8" s="80" t="n">
         <v>0.372</v>
@@ -25545,11 +25642,11 @@
       <c r="O9" s="63" t="n">
         <v>448</v>
       </c>
-      <c r="P9" s="65" t="n">
-        <v>405.975</v>
-      </c>
-      <c r="Q9" s="85" t="n">
-        <v>506</v>
+      <c r="P9" s="85" t="n">
+        <v>405</v>
+      </c>
+      <c r="Q9" s="65" t="n">
+        <v>503</v>
       </c>
       <c r="R9" s="81" t="n">
         <v>0.391</v>
@@ -25600,11 +25697,11 @@
       <c r="O10" s="62" t="n">
         <v>454</v>
       </c>
-      <c r="P10" s="64" t="n">
+      <c r="P10" s="84" t="n">
         <v>397</v>
       </c>
-      <c r="Q10" s="84" t="n">
-        <v>554</v>
+      <c r="Q10" s="64" t="n">
+        <v>556</v>
       </c>
       <c r="R10" s="80" t="n">
         <v>0.149</v>
@@ -25655,11 +25752,11 @@
       <c r="O11" s="63" t="n">
         <v>612.5</v>
       </c>
-      <c r="P11" s="65" t="n">
+      <c r="P11" s="85" t="n">
         <v>544</v>
       </c>
-      <c r="Q11" s="85" t="n">
-        <v>683</v>
+      <c r="Q11" s="65" t="n">
+        <v>689</v>
       </c>
       <c r="R11" s="81" t="n">
         <v>0.349</v>
@@ -25710,10 +25807,10 @@
       <c r="O12" s="62" t="n">
         <v>650.5</v>
       </c>
-      <c r="P12" s="64" t="n">
+      <c r="P12" s="84" t="n">
         <v>522</v>
       </c>
-      <c r="Q12" s="84" t="n">
+      <c r="Q12" s="64" t="n">
         <v>756</v>
       </c>
       <c r="R12" s="80" t="n">
@@ -25765,11 +25862,11 @@
       <c r="O13" s="63" t="n">
         <v>443.5</v>
       </c>
-      <c r="P13" s="65" t="n">
+      <c r="P13" s="85" t="n">
         <v>376</v>
       </c>
-      <c r="Q13" s="85" t="n">
-        <v>542</v>
+      <c r="Q13" s="65" t="n">
+        <v>538.05</v>
       </c>
       <c r="R13" s="81" t="n">
         <v>0.483</v>
@@ -25820,10 +25917,10 @@
       <c r="O14" s="62" t="n">
         <v>478.5</v>
       </c>
-      <c r="P14" s="64" t="n">
+      <c r="P14" s="84" t="n">
         <v>372</v>
       </c>
-      <c r="Q14" s="84" t="n">
+      <c r="Q14" s="64" t="n">
         <v>595</v>
       </c>
       <c r="R14" s="80" t="n">
@@ -25875,11 +25972,11 @@
       <c r="O15" s="63" t="n">
         <v>730.5</v>
       </c>
-      <c r="P15" s="65" t="n">
-        <v>639</v>
-      </c>
-      <c r="Q15" s="85" t="n">
-        <v>856</v>
+      <c r="P15" s="85" t="n">
+        <v>638</v>
+      </c>
+      <c r="Q15" s="65" t="n">
+        <v>848</v>
       </c>
       <c r="R15" s="81" t="n">
         <v>0.287</v>
@@ -25930,11 +26027,11 @@
       <c r="O16" s="62" t="n">
         <v>428</v>
       </c>
-      <c r="P16" s="64" t="n">
-        <v>367</v>
-      </c>
-      <c r="Q16" s="84" t="n">
-        <v>509</v>
+      <c r="P16" s="84" t="n">
+        <v>369</v>
+      </c>
+      <c r="Q16" s="64" t="n">
+        <v>508</v>
       </c>
       <c r="R16" s="80" t="n">
         <v>0.515</v>
@@ -25985,11 +26082,11 @@
       <c r="O17" s="63" t="n">
         <v>535</v>
       </c>
-      <c r="P17" s="65" t="n">
+      <c r="P17" s="85" t="n">
         <v>437</v>
       </c>
-      <c r="Q17" s="85" t="n">
-        <v>740</v>
+      <c r="Q17" s="65" t="n">
+        <v>727</v>
       </c>
       <c r="R17" s="81" t="n">
         <v>0.298</v>
@@ -26040,11 +26137,11 @@
       <c r="O18" s="62" t="n">
         <v>458</v>
       </c>
-      <c r="P18" s="64" t="n">
-        <v>365</v>
-      </c>
-      <c r="Q18" s="84" t="n">
-        <v>539</v>
+      <c r="P18" s="84" t="n">
+        <v>347</v>
+      </c>
+      <c r="Q18" s="64" t="n">
+        <v>533</v>
       </c>
       <c r="R18" s="80" t="n">
         <v>0.302</v>
@@ -26095,11 +26192,11 @@
       <c r="O19" s="63" t="n">
         <v>412</v>
       </c>
-      <c r="P19" s="65" t="n">
-        <v>326</v>
-      </c>
-      <c r="Q19" s="85" t="n">
-        <v>548</v>
+      <c r="P19" s="85" t="n">
+        <v>323</v>
+      </c>
+      <c r="Q19" s="65" t="n">
+        <v>536</v>
       </c>
       <c r="R19" s="81" t="n">
         <v>0.52</v>
@@ -26150,10 +26247,10 @@
       <c r="O20" s="62" t="n">
         <v>585</v>
       </c>
-      <c r="P20" s="64" t="n">
+      <c r="P20" s="84" t="n">
         <v>490</v>
       </c>
-      <c r="Q20" s="84" t="n">
+      <c r="Q20" s="64" t="n">
         <v>619</v>
       </c>
       <c r="R20" s="80" t="n">
@@ -26205,11 +26302,11 @@
       <c r="O21" s="63" t="n">
         <v>448.5</v>
       </c>
-      <c r="P21" s="65" t="n">
-        <v>314.625</v>
-      </c>
-      <c r="Q21" s="85" t="n">
-        <v>643</v>
+      <c r="P21" s="85" t="n">
+        <v>315</v>
+      </c>
+      <c r="Q21" s="65" t="n">
+        <v>622</v>
       </c>
       <c r="R21" s="81" t="n">
         <v>0.271</v>
@@ -26256,8 +26353,8 @@
       </c>
       <c r="N22" s="44"/>
       <c r="O22" s="62"/>
-      <c r="P22" s="64"/>
-      <c r="Q22" s="84"/>
+      <c r="P22" s="84"/>
+      <c r="Q22" s="64"/>
       <c r="R22" s="80"/>
       <c r="S22" s="3"/>
     </row>
@@ -26301,8 +26398,8 @@
       </c>
       <c r="N23" s="45"/>
       <c r="O23" s="63"/>
-      <c r="P23" s="65"/>
-      <c r="Q23" s="85"/>
+      <c r="P23" s="85"/>
+      <c r="Q23" s="65"/>
       <c r="R23" s="81"/>
       <c r="S23" s="3"/>
     </row>
@@ -26350,10 +26447,10 @@
       <c r="O24" s="62" t="n">
         <v>609</v>
       </c>
-      <c r="P24" s="64" t="n">
-        <v>447</v>
-      </c>
-      <c r="Q24" s="84" t="n">
+      <c r="P24" s="84" t="n">
+        <v>452</v>
+      </c>
+      <c r="Q24" s="64" t="n">
         <v>720</v>
       </c>
       <c r="R24" s="80" t="n">
@@ -26401,8 +26498,8 @@
       </c>
       <c r="N25" s="45"/>
       <c r="O25" s="63"/>
-      <c r="P25" s="65"/>
-      <c r="Q25" s="85"/>
+      <c r="P25" s="85"/>
+      <c r="Q25" s="65"/>
       <c r="R25" s="81"/>
       <c r="S25" s="3"/>
     </row>
@@ -26446,8 +26543,8 @@
       </c>
       <c r="N26" s="44"/>
       <c r="O26" s="62"/>
-      <c r="P26" s="64"/>
-      <c r="Q26" s="84"/>
+      <c r="P26" s="84"/>
+      <c r="Q26" s="64"/>
       <c r="R26" s="80"/>
       <c r="S26" s="3"/>
     </row>
@@ -26491,8 +26588,8 @@
       </c>
       <c r="N27" s="45"/>
       <c r="O27" s="63"/>
-      <c r="P27" s="65"/>
-      <c r="Q27" s="85"/>
+      <c r="P27" s="85"/>
+      <c r="Q27" s="65"/>
       <c r="R27" s="81"/>
       <c r="S27" s="3"/>
     </row>
@@ -26536,8 +26633,8 @@
       </c>
       <c r="N28" s="44"/>
       <c r="O28" s="62"/>
-      <c r="P28" s="64"/>
-      <c r="Q28" s="84"/>
+      <c r="P28" s="84"/>
+      <c r="Q28" s="64"/>
       <c r="R28" s="80"/>
       <c r="S28" s="3"/>
     </row>
@@ -26581,8 +26678,8 @@
       </c>
       <c r="N29" s="45"/>
       <c r="O29" s="63"/>
-      <c r="P29" s="65"/>
-      <c r="Q29" s="85"/>
+      <c r="P29" s="85"/>
+      <c r="Q29" s="65"/>
       <c r="R29" s="81"/>
       <c r="S29" s="3"/>
     </row>
@@ -26618,8 +26715,8 @@
       <c r="M30" s="82"/>
       <c r="N30" s="44"/>
       <c r="O30" s="62"/>
-      <c r="P30" s="64"/>
-      <c r="Q30" s="84"/>
+      <c r="P30" s="84"/>
+      <c r="Q30" s="64"/>
       <c r="R30" s="80"/>
       <c r="S30" s="3"/>
     </row>
@@ -26655,8 +26752,8 @@
       <c r="M31" s="83"/>
       <c r="N31" s="45"/>
       <c r="O31" s="63"/>
-      <c r="P31" s="65"/>
-      <c r="Q31" s="85"/>
+      <c r="P31" s="85"/>
+      <c r="Q31" s="65"/>
       <c r="R31" s="81"/>
       <c r="S31" s="3"/>
     </row>
@@ -26692,8 +26789,8 @@
       <c r="M32" s="82"/>
       <c r="N32" s="44"/>
       <c r="O32" s="62"/>
-      <c r="P32" s="64"/>
-      <c r="Q32" s="84"/>
+      <c r="P32" s="84"/>
+      <c r="Q32" s="64"/>
       <c r="R32" s="80"/>
       <c r="S32" s="3"/>
     </row>
@@ -26725,36 +26822,36 @@
       <c r="M33" s="83"/>
       <c r="N33" s="45"/>
       <c r="O33" s="63"/>
-      <c r="P33" s="65"/>
-      <c r="Q33" s="85"/>
+      <c r="P33" s="85"/>
+      <c r="Q33" s="65"/>
       <c r="R33" s="81"/>
       <c r="S33" s="3"/>
     </row>
     <row r="34" ht="27" customHeight="1">
       <c r="A34" s="3"/>
       <c r="B34" s="58" t="str">
-        <v>Japan</v>
+        <v>Taiwan</v>
       </c>
       <c r="C34" s="58" t="str">
         <v>Asia</v>
       </c>
       <c r="D34" s="44" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="E34" s="44" t="n">
         <v>64</v>
       </c>
       <c r="F34" s="44" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="G34" s="62" t="n">
-        <v>1.3333</v>
+        <v>2.2069</v>
       </c>
       <c r="H34" s="64" t="n">
-        <v>0.6071</v>
+        <v>1.2307</v>
       </c>
       <c r="I34" s="64" t="n">
-        <v>3.3796</v>
+        <v>4.143</v>
       </c>
       <c r="J34" s="44"/>
       <c r="K34" s="80"/>
@@ -26762,36 +26859,36 @@
       <c r="M34" s="82"/>
       <c r="N34" s="44"/>
       <c r="O34" s="62"/>
-      <c r="P34" s="64"/>
-      <c r="Q34" s="84"/>
+      <c r="P34" s="84"/>
+      <c r="Q34" s="64"/>
       <c r="R34" s="80"/>
       <c r="S34" s="3"/>
     </row>
     <row r="35" ht="27" customHeight="1">
       <c r="A35" s="3"/>
       <c r="B35" s="59" t="str">
-        <v>Taiwan</v>
+        <v>Japan</v>
       </c>
       <c r="C35" s="59" t="str">
         <v>Asia</v>
       </c>
       <c r="D35" s="45" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="E35" s="45" t="n">
         <v>64</v>
       </c>
       <c r="F35" s="45" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="G35" s="63" t="n">
-        <v>2.2069</v>
+        <v>1.3333</v>
       </c>
       <c r="H35" s="65" t="n">
-        <v>1.2307</v>
+        <v>0.6071</v>
       </c>
       <c r="I35" s="65" t="n">
-        <v>4.143</v>
+        <v>3.3796</v>
       </c>
       <c r="J35" s="45"/>
       <c r="K35" s="81"/>
@@ -26799,8 +26896,8 @@
       <c r="M35" s="83"/>
       <c r="N35" s="45"/>
       <c r="O35" s="63"/>
-      <c r="P35" s="65"/>
-      <c r="Q35" s="85"/>
+      <c r="P35" s="85"/>
+      <c r="Q35" s="65"/>
       <c r="R35" s="81"/>
       <c r="S35" s="3"/>
     </row>
@@ -26836,8 +26933,8 @@
       <c r="M36" s="82"/>
       <c r="N36" s="44"/>
       <c r="O36" s="62"/>
-      <c r="P36" s="64"/>
-      <c r="Q36" s="84"/>
+      <c r="P36" s="84"/>
+      <c r="Q36" s="64"/>
       <c r="R36" s="80"/>
       <c r="S36" s="3"/>
     </row>
@@ -26873,8 +26970,8 @@
       <c r="M37" s="83"/>
       <c r="N37" s="45"/>
       <c r="O37" s="63"/>
-      <c r="P37" s="65"/>
-      <c r="Q37" s="85"/>
+      <c r="P37" s="85"/>
+      <c r="Q37" s="65"/>
       <c r="R37" s="81"/>
       <c r="S37" s="3"/>
     </row>
@@ -26910,8 +27007,8 @@
       <c r="M38" s="82"/>
       <c r="N38" s="44"/>
       <c r="O38" s="62"/>
-      <c r="P38" s="64"/>
-      <c r="Q38" s="84"/>
+      <c r="P38" s="84"/>
+      <c r="Q38" s="64"/>
       <c r="R38" s="80"/>
       <c r="S38" s="3"/>
     </row>
@@ -26943,8 +27040,8 @@
       <c r="M39" s="83"/>
       <c r="N39" s="45"/>
       <c r="O39" s="63"/>
-      <c r="P39" s="65"/>
-      <c r="Q39" s="85"/>
+      <c r="P39" s="85"/>
+      <c r="Q39" s="65"/>
       <c r="R39" s="81"/>
       <c r="S39" s="3"/>
     </row>
@@ -26976,8 +27073,8 @@
       <c r="M40" s="82"/>
       <c r="N40" s="44"/>
       <c r="O40" s="62"/>
-      <c r="P40" s="64"/>
-      <c r="Q40" s="84"/>
+      <c r="P40" s="84"/>
+      <c r="Q40" s="64"/>
       <c r="R40" s="80"/>
       <c r="S40" s="3"/>
     </row>
@@ -27009,8 +27106,8 @@
       <c r="M41" s="83"/>
       <c r="N41" s="45"/>
       <c r="O41" s="63"/>
-      <c r="P41" s="65"/>
-      <c r="Q41" s="85"/>
+      <c r="P41" s="85"/>
+      <c r="Q41" s="65"/>
       <c r="R41" s="81"/>
       <c r="S41" s="3"/>
     </row>
@@ -27042,8 +27139,8 @@
       <c r="M42" s="82"/>
       <c r="N42" s="44"/>
       <c r="O42" s="62"/>
-      <c r="P42" s="64"/>
-      <c r="Q42" s="84"/>
+      <c r="P42" s="84"/>
+      <c r="Q42" s="64"/>
       <c r="R42" s="80"/>
       <c r="S42" s="3"/>
     </row>
@@ -27075,8 +27172,8 @@
       <c r="M43" s="83"/>
       <c r="N43" s="45"/>
       <c r="O43" s="63"/>
-      <c r="P43" s="65"/>
-      <c r="Q43" s="85"/>
+      <c r="P43" s="85"/>
+      <c r="Q43" s="65"/>
       <c r="R43" s="81"/>
       <c r="S43" s="3"/>
     </row>
@@ -27108,18 +27205,18 @@
       <c r="M44" s="82"/>
       <c r="N44" s="44"/>
       <c r="O44" s="62"/>
-      <c r="P44" s="64"/>
-      <c r="Q44" s="84"/>
+      <c r="P44" s="84"/>
+      <c r="Q44" s="64"/>
       <c r="R44" s="80"/>
       <c r="S44" s="3"/>
     </row>
     <row r="45" ht="27" customHeight="1">
       <c r="A45" s="3"/>
       <c r="B45" s="59" t="str">
-        <v>New Zealand</v>
+        <v>South Africa</v>
       </c>
       <c r="C45" s="59" t="str">
-        <v>Oceania</v>
+        <v>Africa</v>
       </c>
       <c r="D45" s="45" t="n">
         <v>5</v>
@@ -27134,19 +27231,17 @@
         <v>2.8</v>
       </c>
       <c r="H45" s="65" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" s="65" t="n">
-        <v>9</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="I45" s="65"/>
       <c r="J45" s="45"/>
       <c r="K45" s="81"/>
       <c r="L45" s="83"/>
       <c r="M45" s="83"/>
       <c r="N45" s="45"/>
       <c r="O45" s="63"/>
-      <c r="P45" s="65"/>
-      <c r="Q45" s="85"/>
+      <c r="P45" s="85"/>
+      <c r="Q45" s="65"/>
       <c r="R45" s="81"/>
       <c r="S45" s="3"/>
     </row>
@@ -27178,34 +27273,32 @@
       <c r="M46" s="82"/>
       <c r="N46" s="44"/>
       <c r="O46" s="62"/>
-      <c r="P46" s="64"/>
-      <c r="Q46" s="84"/>
+      <c r="P46" s="84"/>
+      <c r="Q46" s="64"/>
       <c r="R46" s="80"/>
       <c r="S46" s="3"/>
     </row>
     <row r="47" ht="27" customHeight="1">
       <c r="A47" s="3"/>
       <c r="B47" s="59" t="str">
-        <v>South Africa</v>
+        <v>Turkey</v>
       </c>
       <c r="C47" s="59" t="str">
-        <v>Africa</v>
+        <v>Asia</v>
       </c>
       <c r="D47" s="45" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E47" s="45" t="n">
         <v>14</v>
       </c>
       <c r="F47" s="45" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G47" s="63" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H47" s="65" t="n">
-        <v>0.9</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="H47" s="65"/>
       <c r="I47" s="65"/>
       <c r="J47" s="45"/>
       <c r="K47" s="81"/>
@@ -27213,30 +27306,30 @@
       <c r="M47" s="83"/>
       <c r="N47" s="45"/>
       <c r="O47" s="63"/>
-      <c r="P47" s="65"/>
-      <c r="Q47" s="85"/>
+      <c r="P47" s="85"/>
+      <c r="Q47" s="65"/>
       <c r="R47" s="81"/>
       <c r="S47" s="3"/>
     </row>
     <row r="48" ht="27" customHeight="1">
       <c r="A48" s="3"/>
       <c r="B48" s="58" t="str">
-        <v>Turkey</v>
+        <v>Luxembourg</v>
       </c>
       <c r="C48" s="58" t="str">
-        <v>Asia</v>
+        <v>Europe</v>
       </c>
       <c r="D48" s="44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E48" s="44" t="n">
         <v>14</v>
       </c>
       <c r="F48" s="44" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G48" s="62" t="n">
-        <v>14</v>
+        <v>3.5</v>
       </c>
       <c r="H48" s="64"/>
       <c r="I48" s="64"/>
@@ -27246,41 +27339,45 @@
       <c r="M48" s="82"/>
       <c r="N48" s="44"/>
       <c r="O48" s="62"/>
-      <c r="P48" s="64"/>
-      <c r="Q48" s="84"/>
+      <c r="P48" s="84"/>
+      <c r="Q48" s="64"/>
       <c r="R48" s="80"/>
       <c r="S48" s="3"/>
     </row>
     <row r="49" ht="27" customHeight="1">
       <c r="A49" s="3"/>
       <c r="B49" s="59" t="str">
-        <v>Luxembourg</v>
+        <v>New Zealand</v>
       </c>
       <c r="C49" s="59" t="str">
-        <v>Europe</v>
+        <v>Oceania</v>
       </c>
       <c r="D49" s="45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E49" s="45" t="n">
         <v>14</v>
       </c>
       <c r="F49" s="45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G49" s="63" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H49" s="65"/>
-      <c r="I49" s="65"/>
+        <v>2.8</v>
+      </c>
+      <c r="H49" s="65" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="65" t="n">
+        <v>9</v>
+      </c>
       <c r="J49" s="45"/>
       <c r="K49" s="81"/>
       <c r="L49" s="83"/>
       <c r="M49" s="83"/>
       <c r="N49" s="45"/>
       <c r="O49" s="63"/>
-      <c r="P49" s="65"/>
-      <c r="Q49" s="85"/>
+      <c r="P49" s="85"/>
+      <c r="Q49" s="65"/>
       <c r="R49" s="81"/>
       <c r="S49" s="3"/>
     </row>
@@ -27312,8 +27409,8 @@
       <c r="M50" s="82"/>
       <c r="N50" s="44"/>
       <c r="O50" s="62"/>
-      <c r="P50" s="64"/>
-      <c r="Q50" s="84"/>
+      <c r="P50" s="84"/>
+      <c r="Q50" s="64"/>
       <c r="R50" s="80"/>
       <c r="S50" s="3"/>
     </row>
@@ -27343,15 +27440,15 @@
       <c r="M51" s="83"/>
       <c r="N51" s="45"/>
       <c r="O51" s="63"/>
-      <c r="P51" s="65"/>
-      <c r="Q51" s="85"/>
+      <c r="P51" s="85"/>
+      <c r="Q51" s="65"/>
       <c r="R51" s="81"/>
       <c r="S51" s="3"/>
     </row>
     <row r="52" ht="27" customHeight="1">
       <c r="A52" s="3"/>
       <c r="B52" s="58" t="str">
-        <v>Hungary</v>
+        <v>Serbia</v>
       </c>
       <c r="C52" s="58" t="str">
         <v>Europe</v>
@@ -27374,8 +27471,8 @@
       <c r="M52" s="82"/>
       <c r="N52" s="44"/>
       <c r="O52" s="62"/>
-      <c r="P52" s="64"/>
-      <c r="Q52" s="84"/>
+      <c r="P52" s="84"/>
+      <c r="Q52" s="64"/>
       <c r="R52" s="80"/>
       <c r="S52" s="3"/>
     </row>
@@ -27407,15 +27504,15 @@
       <c r="M53" s="83"/>
       <c r="N53" s="45"/>
       <c r="O53" s="63"/>
-      <c r="P53" s="65"/>
-      <c r="Q53" s="85"/>
+      <c r="P53" s="85"/>
+      <c r="Q53" s="65"/>
       <c r="R53" s="81"/>
       <c r="S53" s="3"/>
     </row>
     <row r="54" ht="27" customHeight="1">
       <c r="A54" s="3"/>
       <c r="B54" s="58" t="str">
-        <v>Serbia</v>
+        <v>Hungary</v>
       </c>
       <c r="C54" s="58" t="str">
         <v>Europe</v>
@@ -27438,34 +27535,30 @@
       <c r="M54" s="82"/>
       <c r="N54" s="44"/>
       <c r="O54" s="62"/>
-      <c r="P54" s="64"/>
-      <c r="Q54" s="84"/>
+      <c r="P54" s="84"/>
+      <c r="Q54" s="64"/>
       <c r="R54" s="80"/>
       <c r="S54" s="3"/>
     </row>
-    <row r="55" ht="27" customHeight="1">
+    <row r="55" ht="39" customHeight="1">
       <c r="A55" s="3"/>
       <c r="B55" s="59" t="str">
-        <v>Slovenia</v>
+        <v>Puerto Rico</v>
       </c>
       <c r="C55" s="59" t="str">
-        <v>Europe</v>
+        <v>North America</v>
       </c>
       <c r="D55" s="45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E55" s="45" t="n">
         <v>7</v>
       </c>
       <c r="F55" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="G55" s="63" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="H55" s="65" t="n">
-        <v>0.3333</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="G55" s="63"/>
+      <c r="H55" s="65"/>
       <c r="I55" s="65"/>
       <c r="J55" s="45"/>
       <c r="K55" s="81"/>
@@ -27473,30 +27566,34 @@
       <c r="M55" s="83"/>
       <c r="N55" s="45"/>
       <c r="O55" s="63"/>
-      <c r="P55" s="65"/>
-      <c r="Q55" s="85"/>
+      <c r="P55" s="85"/>
+      <c r="Q55" s="65"/>
       <c r="R55" s="81"/>
       <c r="S55" s="3"/>
     </row>
-    <row r="56" ht="39" customHeight="1">
+    <row r="56" ht="27" customHeight="1">
       <c r="A56" s="3"/>
       <c r="B56" s="58" t="str">
-        <v>Puerto Rico</v>
+        <v>Slovenia</v>
       </c>
       <c r="C56" s="58" t="str">
-        <v>North America</v>
+        <v>Europe</v>
       </c>
       <c r="D56" s="44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E56" s="44" t="n">
         <v>7</v>
       </c>
       <c r="F56" s="44" t="n">
-        <v>7</v>
-      </c>
-      <c r="G56" s="62"/>
-      <c r="H56" s="64"/>
+        <v>2</v>
+      </c>
+      <c r="G56" s="62" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H56" s="64" t="n">
+        <v>0.3333</v>
+      </c>
       <c r="I56" s="64"/>
       <c r="J56" s="44"/>
       <c r="K56" s="80"/>
@@ -27504,30 +27601,30 @@
       <c r="M56" s="82"/>
       <c r="N56" s="44"/>
       <c r="O56" s="62"/>
-      <c r="P56" s="64"/>
-      <c r="Q56" s="84"/>
+      <c r="P56" s="84"/>
+      <c r="Q56" s="64"/>
       <c r="R56" s="80"/>
       <c r="S56" s="3"/>
     </row>
     <row r="57" ht="27" customHeight="1">
       <c r="A57" s="3"/>
       <c r="B57" s="59" t="str">
-        <v>Qatar</v>
+        <v>Romania</v>
       </c>
       <c r="C57" s="59" t="str">
-        <v>Asia</v>
+        <v>Europe</v>
       </c>
       <c r="D57" s="45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57" s="45" t="n">
         <v>5</v>
       </c>
       <c r="F57" s="45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G57" s="63" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="H57" s="65"/>
       <c r="I57" s="65"/>
@@ -27537,30 +27634,30 @@
       <c r="M57" s="83"/>
       <c r="N57" s="45"/>
       <c r="O57" s="63"/>
-      <c r="P57" s="65"/>
-      <c r="Q57" s="85"/>
+      <c r="P57" s="85"/>
+      <c r="Q57" s="65"/>
       <c r="R57" s="81"/>
       <c r="S57" s="3"/>
     </row>
     <row r="58" ht="27" customHeight="1">
       <c r="A58" s="3"/>
       <c r="B58" s="58" t="str">
-        <v>Romania</v>
+        <v>Qatar</v>
       </c>
       <c r="C58" s="58" t="str">
-        <v>Europe</v>
+        <v>Asia</v>
       </c>
       <c r="D58" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58" s="44" t="n">
         <v>5</v>
       </c>
       <c r="F58" s="44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G58" s="62" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="H58" s="64"/>
       <c r="I58" s="64"/>
@@ -27570,8 +27667,8 @@
       <c r="M58" s="82"/>
       <c r="N58" s="44"/>
       <c r="O58" s="62"/>
-      <c r="P58" s="64"/>
-      <c r="Q58" s="84"/>
+      <c r="P58" s="84"/>
+      <c r="Q58" s="64"/>
       <c r="R58" s="80"/>
       <c r="S58" s="3"/>
     </row>
@@ -27603,8 +27700,8 @@
       <c r="M59" s="83"/>
       <c r="N59" s="45"/>
       <c r="O59" s="63"/>
-      <c r="P59" s="65"/>
-      <c r="Q59" s="85"/>
+      <c r="P59" s="85"/>
+      <c r="Q59" s="65"/>
       <c r="R59" s="81"/>
       <c r="S59" s="3"/>
     </row>
@@ -27640,18 +27737,18 @@
       <c r="M60" s="82"/>
       <c r="N60" s="44"/>
       <c r="O60" s="62"/>
-      <c r="P60" s="64"/>
-      <c r="Q60" s="84"/>
+      <c r="P60" s="84"/>
+      <c r="Q60" s="64"/>
       <c r="R60" s="80"/>
       <c r="S60" s="3"/>
     </row>
     <row r="61" ht="27" customHeight="1">
       <c r="A61" s="3"/>
       <c r="B61" s="59" t="str">
-        <v>United Arab Emirates</v>
+        <v>Lithuania</v>
       </c>
       <c r="C61" s="59" t="str">
-        <v>Asia</v>
+        <v>Europe</v>
       </c>
       <c r="D61" s="45" t="n">
         <v>0</v>
@@ -27671,18 +27768,18 @@
       <c r="M61" s="83"/>
       <c r="N61" s="45"/>
       <c r="O61" s="63"/>
-      <c r="P61" s="65"/>
-      <c r="Q61" s="85"/>
+      <c r="P61" s="85"/>
+      <c r="Q61" s="65"/>
       <c r="R61" s="81"/>
       <c r="S61" s="3"/>
     </row>
     <row r="62" ht="27" customHeight="1">
       <c r="A62" s="3"/>
       <c r="B62" s="58" t="str">
-        <v>Lithuania</v>
+        <v>United Arab Emirates</v>
       </c>
       <c r="C62" s="58" t="str">
-        <v>Europe</v>
+        <v>Asia</v>
       </c>
       <c r="D62" s="44" t="n">
         <v>0</v>
@@ -27702,29 +27799,31 @@
       <c r="M62" s="82"/>
       <c r="N62" s="44"/>
       <c r="O62" s="62"/>
-      <c r="P62" s="64"/>
-      <c r="Q62" s="84"/>
+      <c r="P62" s="84"/>
+      <c r="Q62" s="64"/>
       <c r="R62" s="80"/>
       <c r="S62" s="3"/>
     </row>
     <row r="63" ht="27" customHeight="1">
       <c r="A63" s="3"/>
       <c r="B63" s="59" t="str">
-        <v>Jersey</v>
+        <v>Pakistan</v>
       </c>
       <c r="C63" s="59" t="str">
-        <v>Europe</v>
+        <v>Asia</v>
       </c>
       <c r="D63" s="45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E63" s="45" t="n">
         <v>2</v>
       </c>
       <c r="F63" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="G63" s="63"/>
+        <v>0</v>
+      </c>
+      <c r="G63" s="63" t="n">
+        <v>1</v>
+      </c>
       <c r="H63" s="65"/>
       <c r="I63" s="65"/>
       <c r="J63" s="45"/>
@@ -27733,31 +27832,29 @@
       <c r="M63" s="83"/>
       <c r="N63" s="45"/>
       <c r="O63" s="63"/>
-      <c r="P63" s="65"/>
-      <c r="Q63" s="85"/>
+      <c r="P63" s="85"/>
+      <c r="Q63" s="65"/>
       <c r="R63" s="81"/>
       <c r="S63" s="3"/>
     </row>
     <row r="64" ht="27" customHeight="1">
       <c r="A64" s="3"/>
       <c r="B64" s="58" t="str">
-        <v>Pakistan</v>
+        <v>Jersey</v>
       </c>
       <c r="C64" s="58" t="str">
-        <v>Asia</v>
+        <v>Europe</v>
       </c>
       <c r="D64" s="44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E64" s="44" t="n">
         <v>2</v>
       </c>
       <c r="F64" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="62" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G64" s="62"/>
       <c r="H64" s="64"/>
       <c r="I64" s="64"/>
       <c r="J64" s="44"/>
@@ -27766,18 +27863,18 @@
       <c r="M64" s="82"/>
       <c r="N64" s="44"/>
       <c r="O64" s="62"/>
-      <c r="P64" s="64"/>
-      <c r="Q64" s="84"/>
+      <c r="P64" s="84"/>
+      <c r="Q64" s="64"/>
       <c r="R64" s="80"/>
       <c r="S64" s="3"/>
     </row>
     <row r="65" ht="27" customHeight="1">
       <c r="A65" s="3"/>
       <c r="B65" s="59" t="str">
-        <v>Kenya</v>
+        <v>Cyprus</v>
       </c>
       <c r="C65" s="59" t="str">
-        <v>Africa</v>
+        <v>Asia</v>
       </c>
       <c r="D65" s="45" t="n">
         <v>0</v>
@@ -27797,18 +27894,18 @@
       <c r="M65" s="83"/>
       <c r="N65" s="45"/>
       <c r="O65" s="63"/>
-      <c r="P65" s="65"/>
-      <c r="Q65" s="85"/>
+      <c r="P65" s="85"/>
+      <c r="Q65" s="65"/>
       <c r="R65" s="81"/>
       <c r="S65" s="3"/>
     </row>
     <row r="66" ht="27" customHeight="1">
       <c r="A66" s="3"/>
       <c r="B66" s="58" t="str">
-        <v>Kuwait</v>
+        <v>Bulgaria</v>
       </c>
       <c r="C66" s="58" t="str">
-        <v>Asia</v>
+        <v>Europe</v>
       </c>
       <c r="D66" s="44" t="n">
         <v>0</v>
@@ -27828,31 +27925,29 @@
       <c r="M66" s="82"/>
       <c r="N66" s="44"/>
       <c r="O66" s="62"/>
-      <c r="P66" s="64"/>
-      <c r="Q66" s="84"/>
+      <c r="P66" s="84"/>
+      <c r="Q66" s="64"/>
       <c r="R66" s="80"/>
       <c r="S66" s="3"/>
     </row>
     <row r="67" ht="27" customHeight="1">
       <c r="A67" s="3"/>
       <c r="B67" s="59" t="str">
-        <v>Iran</v>
+        <v>Philippines</v>
       </c>
       <c r="C67" s="59" t="str">
         <v>Asia</v>
       </c>
       <c r="D67" s="45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E67" s="45" t="n">
         <v>1</v>
       </c>
       <c r="F67" s="45" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G67" s="63" t="n">
-        <v>0.5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G67" s="63"/>
       <c r="H67" s="65"/>
       <c r="I67" s="65"/>
       <c r="J67" s="45"/>
@@ -27861,8 +27956,8 @@
       <c r="M67" s="83"/>
       <c r="N67" s="45"/>
       <c r="O67" s="63"/>
-      <c r="P67" s="65"/>
-      <c r="Q67" s="85"/>
+      <c r="P67" s="85"/>
+      <c r="Q67" s="65"/>
       <c r="R67" s="81"/>
       <c r="S67" s="3"/>
     </row>
@@ -27892,29 +27987,31 @@
       <c r="M68" s="82"/>
       <c r="N68" s="44"/>
       <c r="O68" s="62"/>
-      <c r="P68" s="64"/>
-      <c r="Q68" s="84"/>
+      <c r="P68" s="84"/>
+      <c r="Q68" s="64"/>
       <c r="R68" s="80"/>
       <c r="S68" s="3"/>
     </row>
     <row r="69" ht="27" customHeight="1">
       <c r="A69" s="3"/>
       <c r="B69" s="59" t="str">
-        <v>Cyprus</v>
+        <v>Iran</v>
       </c>
       <c r="C69" s="59" t="str">
         <v>Asia</v>
       </c>
       <c r="D69" s="45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E69" s="45" t="n">
         <v>1</v>
       </c>
       <c r="F69" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" s="63"/>
+        <v>-1</v>
+      </c>
+      <c r="G69" s="63" t="n">
+        <v>0.5</v>
+      </c>
       <c r="H69" s="65"/>
       <c r="I69" s="65"/>
       <c r="J69" s="45"/>
@@ -27923,18 +28020,18 @@
       <c r="M69" s="83"/>
       <c r="N69" s="45"/>
       <c r="O69" s="63"/>
-      <c r="P69" s="65"/>
-      <c r="Q69" s="85"/>
+      <c r="P69" s="85"/>
+      <c r="Q69" s="65"/>
       <c r="R69" s="81"/>
       <c r="S69" s="3"/>
     </row>
     <row r="70" ht="27" customHeight="1">
       <c r="A70" s="3"/>
       <c r="B70" s="58" t="str">
-        <v>Bulgaria</v>
+        <v>Kenya</v>
       </c>
       <c r="C70" s="58" t="str">
-        <v>Europe</v>
+        <v>Africa</v>
       </c>
       <c r="D70" s="44" t="n">
         <v>0</v>
@@ -27954,29 +28051,31 @@
       <c r="M70" s="82"/>
       <c r="N70" s="44"/>
       <c r="O70" s="62"/>
-      <c r="P70" s="64"/>
-      <c r="Q70" s="84"/>
+      <c r="P70" s="84"/>
+      <c r="Q70" s="64"/>
       <c r="R70" s="80"/>
       <c r="S70" s="3"/>
     </row>
     <row r="71" ht="27" customHeight="1">
       <c r="A71" s="3"/>
       <c r="B71" s="59" t="str">
-        <v>Philippines</v>
+        <v>Macao</v>
       </c>
       <c r="C71" s="59" t="str">
         <v>Asia</v>
       </c>
       <c r="D71" s="45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71" s="45" t="n">
         <v>1</v>
       </c>
       <c r="F71" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="G71" s="63"/>
       <c r="H71" s="65"/>
       <c r="I71" s="65"/>
       <c r="J71" s="45"/>
@@ -27985,31 +28084,29 @@
       <c r="M71" s="83"/>
       <c r="N71" s="45"/>
       <c r="O71" s="63"/>
-      <c r="P71" s="65"/>
-      <c r="Q71" s="85"/>
+      <c r="P71" s="85"/>
+      <c r="Q71" s="65"/>
       <c r="R71" s="81"/>
       <c r="S71" s="3"/>
     </row>
     <row r="72" ht="27" customHeight="1">
       <c r="A72" s="3"/>
       <c r="B72" s="76" t="str">
-        <v>Macao</v>
+        <v>Kuwait</v>
       </c>
       <c r="C72" s="76" t="str">
         <v>Asia</v>
       </c>
       <c r="D72" s="51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72" s="51" t="n">
         <v>1</v>
       </c>
       <c r="F72" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" s="86" t="n">
         <v>1</v>
       </c>
+      <c r="G72" s="86"/>
       <c r="H72" s="87"/>
       <c r="I72" s="87"/>
       <c r="J72" s="51"/>
@@ -28018,8 +28115,8 @@
       <c r="M72" s="89"/>
       <c r="N72" s="51"/>
       <c r="O72" s="86"/>
-      <c r="P72" s="87"/>
-      <c r="Q72" s="90"/>
+      <c r="P72" s="90"/>
+      <c r="Q72" s="87"/>
       <c r="R72" s="88"/>
       <c r="S72" s="3"/>
     </row>
@@ -28588,7 +28685,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS6&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="Rc271a72809d2411c"/>
+    <tablePart ns1:id="R7b035b02cd9a40a6"/>
   </tableParts>
 </worksheet>
 </file>
@@ -28838,8 +28935,8 @@
       <c r="J8" s="80" t="n">
         <v>0.1067</v>
       </c>
-      <c r="K8" s="58" t="str">
-        <v>True</v>
+      <c r="K8" s="97" t="b">
+        <v>1</v>
       </c>
       <c r="L8" s="44" t="n">
         <v>6777</v>
@@ -28893,8 +28990,8 @@
       <c r="J9" s="81" t="n">
         <v>0.1559</v>
       </c>
-      <c r="K9" s="59" t="str">
-        <v>False</v>
+      <c r="K9" s="98" t="b">
+        <v>0</v>
       </c>
       <c r="L9" s="45" t="n">
         <v>4148</v>
@@ -28948,8 +29045,8 @@
       <c r="J10" s="80" t="n">
         <v>0.1545</v>
       </c>
-      <c r="K10" s="58" t="str">
-        <v>False</v>
+      <c r="K10" s="97" t="b">
+        <v>0</v>
       </c>
       <c r="L10" s="44" t="n">
         <v>3920</v>
@@ -29003,8 +29100,8 @@
       <c r="J11" s="81" t="n">
         <v>0.0707</v>
       </c>
-      <c r="K11" s="59" t="str">
-        <v>False</v>
+      <c r="K11" s="98" t="b">
+        <v>0</v>
       </c>
       <c r="L11" s="45" t="n">
         <v>2279</v>
@@ -29058,8 +29155,8 @@
       <c r="J12" s="80" t="n">
         <v>0.0191</v>
       </c>
-      <c r="K12" s="58" t="str">
-        <v>True</v>
+      <c r="K12" s="97" t="b">
+        <v>1</v>
       </c>
       <c r="L12" s="44" t="n">
         <v>2052</v>
@@ -29113,8 +29210,8 @@
       <c r="J13" s="81" t="n">
         <v>0.0187</v>
       </c>
-      <c r="K13" s="59" t="str">
-        <v>True</v>
+      <c r="K13" s="98" t="b">
+        <v>1</v>
       </c>
       <c r="L13" s="45" t="n">
         <v>1569</v>
@@ -29168,8 +29265,8 @@
       <c r="J14" s="80" t="n">
         <v>0.0268</v>
       </c>
-      <c r="K14" s="58" t="str">
-        <v>True</v>
+      <c r="K14" s="97" t="b">
+        <v>1</v>
       </c>
       <c r="L14" s="44" t="n">
         <v>1545</v>
@@ -29223,8 +29320,8 @@
       <c r="J15" s="81" t="n">
         <v>0.1306</v>
       </c>
-      <c r="K15" s="59" t="str">
-        <v>False</v>
+      <c r="K15" s="98" t="b">
+        <v>0</v>
       </c>
       <c r="L15" s="45" t="n">
         <v>1549</v>
@@ -29278,8 +29375,8 @@
       <c r="J16" s="80" t="n">
         <v>0.0175</v>
       </c>
-      <c r="K16" s="58" t="str">
-        <v>True</v>
+      <c r="K16" s="97" t="b">
+        <v>1</v>
       </c>
       <c r="L16" s="44" t="n">
         <v>969</v>
@@ -29333,8 +29430,8 @@
       <c r="J17" s="81" t="n">
         <v>0.0306</v>
       </c>
-      <c r="K17" s="59" t="str">
-        <v>False</v>
+      <c r="K17" s="98" t="b">
+        <v>0</v>
       </c>
       <c r="L17" s="45" t="n">
         <v>905</v>
@@ -29388,8 +29485,8 @@
       <c r="J18" s="80" t="n">
         <v>0.0638</v>
       </c>
-      <c r="K18" s="58" t="str">
-        <v>False</v>
+      <c r="K18" s="97" t="b">
+        <v>0</v>
       </c>
       <c r="L18" s="44" t="n">
         <v>692</v>
@@ -29443,8 +29540,8 @@
       <c r="J19" s="81" t="n">
         <v>0.0584</v>
       </c>
-      <c r="K19" s="59" t="str">
-        <v>False</v>
+      <c r="K19" s="98" t="b">
+        <v>0</v>
       </c>
       <c r="L19" s="45" t="n">
         <v>755</v>
@@ -29498,8 +29595,8 @@
       <c r="J20" s="80" t="n">
         <v>0.0268</v>
       </c>
-      <c r="K20" s="58" t="str">
-        <v>False</v>
+      <c r="K20" s="97" t="b">
+        <v>0</v>
       </c>
       <c r="L20" s="44" t="n">
         <v>564</v>
@@ -29553,8 +29650,8 @@
       <c r="J21" s="81" t="n">
         <v>0.0191</v>
       </c>
-      <c r="K21" s="59" t="str">
-        <v>True</v>
+      <c r="K21" s="98" t="b">
+        <v>1</v>
       </c>
       <c r="L21" s="45" t="n">
         <v>373</v>
@@ -29608,8 +29705,8 @@
       <c r="J22" s="80" t="n">
         <v>0.0039</v>
       </c>
-      <c r="K22" s="58" t="str">
-        <v>True</v>
+      <c r="K22" s="97" t="b">
+        <v>1</v>
       </c>
       <c r="L22" s="44" t="n">
         <v>213</v>
@@ -29663,8 +29760,8 @@
       <c r="J23" s="81" t="n">
         <v>0.0082</v>
       </c>
-      <c r="K23" s="59" t="str">
-        <v>False</v>
+      <c r="K23" s="98" t="b">
+        <v>0</v>
       </c>
       <c r="L23" s="45" t="n">
         <v>256</v>
@@ -29718,8 +29815,8 @@
       <c r="J24" s="80" t="n">
         <v>0.0286</v>
       </c>
-      <c r="K24" s="58" t="str">
-        <v>False</v>
+      <c r="K24" s="97" t="b">
+        <v>0</v>
       </c>
       <c r="L24" s="44" t="n">
         <v>209</v>
@@ -29773,8 +29870,8 @@
       <c r="J25" s="81" t="n">
         <v>0.0046</v>
       </c>
-      <c r="K25" s="59" t="str">
-        <v>False</v>
+      <c r="K25" s="98" t="b">
+        <v>0</v>
       </c>
       <c r="L25" s="45" t="n">
         <v>155</v>
@@ -29828,8 +29925,8 @@
       <c r="J26" s="80" t="n">
         <v>0.0021</v>
       </c>
-      <c r="K26" s="58" t="str">
-        <v>True</v>
+      <c r="K26" s="97" t="b">
+        <v>1</v>
       </c>
       <c r="L26" s="44" t="n">
         <v>163</v>
@@ -29883,8 +29980,8 @@
       <c r="J27" s="81" t="n">
         <v>0.0008</v>
       </c>
-      <c r="K27" s="59" t="str">
-        <v>False</v>
+      <c r="K27" s="98" t="b">
+        <v>0</v>
       </c>
       <c r="L27" s="45" t="n">
         <v>175</v>
@@ -29938,8 +30035,8 @@
       <c r="J28" s="80" t="n">
         <v>0.0254</v>
       </c>
-      <c r="K28" s="58" t="str">
-        <v>False</v>
+      <c r="K28" s="97" t="b">
+        <v>0</v>
       </c>
       <c r="L28" s="44" t="n">
         <v>131</v>
@@ -29993,8 +30090,8 @@
       <c r="J29" s="81" t="n">
         <v>0.0136</v>
       </c>
-      <c r="K29" s="59" t="str">
-        <v>False</v>
+      <c r="K29" s="98" t="b">
+        <v>0</v>
       </c>
       <c r="L29" s="45" t="n">
         <v>149</v>
@@ -30048,8 +30145,8 @@
       <c r="J30" s="80" t="n">
         <v>0.0021</v>
       </c>
-      <c r="K30" s="58" t="str">
-        <v>True</v>
+      <c r="K30" s="97" t="b">
+        <v>1</v>
       </c>
       <c r="L30" s="44" t="n">
         <v>92</v>
@@ -30103,8 +30200,8 @@
       <c r="J31" s="81" t="n">
         <v>0.0036</v>
       </c>
-      <c r="K31" s="59" t="str">
-        <v>True</v>
+      <c r="K31" s="98" t="b">
+        <v>1</v>
       </c>
       <c r="L31" s="45"/>
       <c r="M31" s="45"/>
@@ -30144,8 +30241,8 @@
       <c r="J32" s="80" t="n">
         <v>0.0018</v>
       </c>
-      <c r="K32" s="58" t="str">
-        <v>True</v>
+      <c r="K32" s="97" t="b">
+        <v>1</v>
       </c>
       <c r="L32" s="44"/>
       <c r="M32" s="44"/>
@@ -30185,8 +30282,8 @@
       <c r="J33" s="81" t="n">
         <v>0.0157</v>
       </c>
-      <c r="K33" s="59" t="str">
-        <v>False</v>
+      <c r="K33" s="98" t="b">
+        <v>0</v>
       </c>
       <c r="L33" s="45" t="n">
         <v>53</v>
@@ -30240,8 +30337,8 @@
       <c r="J34" s="80" t="n">
         <v>0.0018</v>
       </c>
-      <c r="K34" s="58" t="str">
-        <v>False</v>
+      <c r="K34" s="97" t="b">
+        <v>0</v>
       </c>
       <c r="L34" s="44" t="n">
         <v>64</v>
@@ -30295,8 +30392,8 @@
       <c r="J35" s="81" t="n">
         <v>0.0003</v>
       </c>
-      <c r="K35" s="59" t="str">
-        <v>True</v>
+      <c r="K35" s="98" t="b">
+        <v>1</v>
       </c>
       <c r="L35" s="45" t="n">
         <v>63</v>
@@ -30350,8 +30447,8 @@
       <c r="J36" s="80" t="n">
         <v>0.0043</v>
       </c>
-      <c r="K36" s="58" t="str">
-        <v>False</v>
+      <c r="K36" s="97" t="b">
+        <v>0</v>
       </c>
       <c r="L36" s="44"/>
       <c r="M36" s="44"/>
@@ -30391,8 +30488,8 @@
       <c r="J37" s="81" t="n">
         <v>0.0124</v>
       </c>
-      <c r="K37" s="59" t="str">
-        <v>False</v>
+      <c r="K37" s="98" t="b">
+        <v>0</v>
       </c>
       <c r="L37" s="45" t="n">
         <v>63</v>
@@ -30446,8 +30543,8 @@
       <c r="J38" s="80" t="n">
         <v>0.0015</v>
       </c>
-      <c r="K38" s="58" t="str">
-        <v>True</v>
+      <c r="K38" s="97" t="b">
+        <v>1</v>
       </c>
       <c r="L38" s="44"/>
       <c r="M38" s="44"/>
@@ -30487,8 +30584,8 @@
       <c r="J39" s="81" t="n">
         <v>0.0047</v>
       </c>
-      <c r="K39" s="59" t="str">
-        <v>False</v>
+      <c r="K39" s="98" t="b">
+        <v>0</v>
       </c>
       <c r="L39" s="45"/>
       <c r="M39" s="45"/>
@@ -30528,8 +30625,8 @@
       <c r="J40" s="80" t="n">
         <v>0.0034</v>
       </c>
-      <c r="K40" s="58" t="str">
-        <v>False</v>
+      <c r="K40" s="97" t="b">
+        <v>0</v>
       </c>
       <c r="L40" s="44"/>
       <c r="M40" s="44"/>
@@ -30569,8 +30666,8 @@
       <c r="J41" s="81" t="n">
         <v>0.0021</v>
       </c>
-      <c r="K41" s="59" t="str">
-        <v>False</v>
+      <c r="K41" s="98" t="b">
+        <v>0</v>
       </c>
       <c r="L41" s="45"/>
       <c r="M41" s="45"/>
@@ -30610,8 +30707,8 @@
       <c r="J42" s="80" t="n">
         <v>0.002</v>
       </c>
-      <c r="K42" s="58" t="str">
-        <v>True</v>
+      <c r="K42" s="97" t="b">
+        <v>1</v>
       </c>
       <c r="L42" s="44"/>
       <c r="M42" s="44"/>
@@ -30651,8 +30748,8 @@
       <c r="J43" s="81" t="n">
         <v>0.0051</v>
       </c>
-      <c r="K43" s="59" t="str">
-        <v>False</v>
+      <c r="K43" s="98" t="b">
+        <v>0</v>
       </c>
       <c r="L43" s="45"/>
       <c r="M43" s="45"/>
@@ -30692,8 +30789,8 @@
       <c r="J44" s="88" t="n">
         <v>0.0011</v>
       </c>
-      <c r="K44" s="76" t="str">
-        <v>False</v>
+      <c r="K44" s="99" t="b">
+        <v>0</v>
       </c>
       <c r="L44" s="51"/>
       <c r="M44" s="51"/>
@@ -31269,7 +31366,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS7&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="R7ceb4bfcf0f045ab"/>
+    <tablePart ns1:id="R4b434d0cf46840e8"/>
   </tableParts>
 </worksheet>
 </file>
@@ -31648,13 +31745,13 @@
       <c r="W8" s="82" t="n">
         <v>0.0974</v>
       </c>
-      <c r="X8" s="93" t="n">
+      <c r="X8" s="102" t="n">
         <v>-0.1079</v>
       </c>
-      <c r="Y8" s="95" t="n">
+      <c r="Y8" s="104" t="n">
         <v>-0.1365</v>
       </c>
-      <c r="Z8" s="95" t="n">
+      <c r="Z8" s="104" t="n">
         <v>-0.0837</v>
       </c>
       <c r="AA8" s="58"/>
@@ -31728,13 +31825,13 @@
       <c r="W9" s="83" t="n">
         <v>0.1024</v>
       </c>
-      <c r="X9" s="94" t="n">
+      <c r="X9" s="103" t="n">
         <v>-0.1147</v>
       </c>
-      <c r="Y9" s="96" t="n">
+      <c r="Y9" s="105" t="n">
         <v>-0.1436</v>
       </c>
-      <c r="Z9" s="96" t="n">
+      <c r="Z9" s="105" t="n">
         <v>-0.0888</v>
       </c>
       <c r="AA9" s="59"/>
@@ -31808,13 +31905,13 @@
       <c r="W10" s="82" t="n">
         <v>0.0974</v>
       </c>
-      <c r="X10" s="93" t="n">
+      <c r="X10" s="102" t="n">
         <v>-0.1079</v>
       </c>
-      <c r="Y10" s="95" t="n">
+      <c r="Y10" s="104" t="n">
         <v>-0.1365</v>
       </c>
-      <c r="Z10" s="95" t="n">
+      <c r="Z10" s="104" t="n">
         <v>-0.0837</v>
       </c>
       <c r="AA10" s="58"/>
@@ -31888,13 +31985,13 @@
       <c r="W11" s="83" t="n">
         <v>0.1027</v>
       </c>
-      <c r="X11" s="94" t="n">
+      <c r="X11" s="103" t="n">
         <v>-0.1063</v>
       </c>
-      <c r="Y11" s="96" t="n">
+      <c r="Y11" s="105" t="n">
         <v>-0.134</v>
       </c>
-      <c r="Z11" s="96" t="n">
+      <c r="Z11" s="105" t="n">
         <v>-0.082</v>
       </c>
       <c r="AA11" s="59"/>
@@ -31968,13 +32065,13 @@
       <c r="W12" s="82" t="n">
         <v>0.1246</v>
       </c>
-      <c r="X12" s="93" t="n">
+      <c r="X12" s="102" t="n">
         <v>-0.1119</v>
       </c>
-      <c r="Y12" s="95" t="n">
+      <c r="Y12" s="104" t="n">
         <v>-0.1363</v>
       </c>
-      <c r="Z12" s="95" t="n">
+      <c r="Z12" s="104" t="n">
         <v>-0.0897</v>
       </c>
       <c r="AA12" s="58"/>
@@ -32048,13 +32145,13 @@
       <c r="W13" s="83" t="n">
         <v>0.1288</v>
       </c>
-      <c r="X13" s="94" t="n">
+      <c r="X13" s="103" t="n">
         <v>-0.1278</v>
       </c>
-      <c r="Y13" s="96" t="n">
+      <c r="Y13" s="105" t="n">
         <v>-0.1497</v>
       </c>
-      <c r="Z13" s="96" t="n">
+      <c r="Z13" s="105" t="n">
         <v>-0.1045</v>
       </c>
       <c r="AA13" s="59"/>
@@ -32128,13 +32225,13 @@
       <c r="W14" s="82" t="n">
         <v>0.1664</v>
       </c>
-      <c r="X14" s="93" t="n">
+      <c r="X14" s="102" t="n">
         <v>-0.1169</v>
       </c>
-      <c r="Y14" s="95" t="n">
+      <c r="Y14" s="104" t="n">
         <v>-0.1417</v>
       </c>
-      <c r="Z14" s="95" t="n">
+      <c r="Z14" s="104" t="n">
         <v>-0.0931</v>
       </c>
       <c r="AA14" s="58"/>
@@ -32208,13 +32305,13 @@
       <c r="W15" s="83" t="n">
         <v>0.084</v>
       </c>
-      <c r="X15" s="94" t="n">
+      <c r="X15" s="103" t="n">
         <v>-0.0821</v>
       </c>
-      <c r="Y15" s="96" t="n">
+      <c r="Y15" s="105" t="n">
         <v>-0.1048</v>
       </c>
-      <c r="Z15" s="96" t="n">
+      <c r="Z15" s="105" t="n">
         <v>-0.0607</v>
       </c>
       <c r="AA15" s="59"/>
@@ -32288,13 +32385,13 @@
       <c r="W16" s="82" t="n">
         <v>0.0841</v>
       </c>
-      <c r="X16" s="93" t="n">
+      <c r="X16" s="102" t="n">
         <v>-0.0793</v>
       </c>
-      <c r="Y16" s="95" t="n">
+      <c r="Y16" s="104" t="n">
         <v>-0.1011</v>
       </c>
-      <c r="Z16" s="95" t="n">
+      <c r="Z16" s="104" t="n">
         <v>-0.0587</v>
       </c>
       <c r="AA16" s="58"/>
@@ -32368,13 +32465,13 @@
       <c r="W17" s="83" t="n">
         <v>0.1001</v>
       </c>
-      <c r="X17" s="94" t="n">
+      <c r="X17" s="103" t="n">
         <v>-0.1271</v>
       </c>
-      <c r="Y17" s="96" t="n">
+      <c r="Y17" s="105" t="n">
         <v>-0.1592</v>
       </c>
-      <c r="Z17" s="96" t="n">
+      <c r="Z17" s="105" t="n">
         <v>-0.0974</v>
       </c>
       <c r="AA17" s="59"/>
@@ -32448,13 +32545,13 @@
       <c r="W18" s="82" t="n">
         <v>0.0974</v>
       </c>
-      <c r="X18" s="93" t="n">
+      <c r="X18" s="102" t="n">
         <v>-0.1079</v>
       </c>
-      <c r="Y18" s="95" t="n">
+      <c r="Y18" s="104" t="n">
         <v>-0.1365</v>
       </c>
-      <c r="Z18" s="95" t="n">
+      <c r="Z18" s="104" t="n">
         <v>-0.0837</v>
       </c>
       <c r="AA18" s="58"/>
@@ -32528,13 +32625,13 @@
       <c r="W19" s="83" t="n">
         <v>0.1323</v>
       </c>
-      <c r="X19" s="94" t="n">
+      <c r="X19" s="103" t="n">
         <v>-0.1045</v>
       </c>
-      <c r="Y19" s="96" t="n">
+      <c r="Y19" s="105" t="n">
         <v>-0.1463</v>
       </c>
-      <c r="Z19" s="96" t="n">
+      <c r="Z19" s="105" t="n">
         <v>-0.0654</v>
       </c>
       <c r="AA19" s="59" t="str">
@@ -32610,13 +32707,13 @@
       <c r="W20" s="82" t="n">
         <v>0.066</v>
       </c>
-      <c r="X20" s="93" t="n">
+      <c r="X20" s="102" t="n">
         <v>-0.1186</v>
       </c>
-      <c r="Y20" s="95" t="n">
+      <c r="Y20" s="104" t="n">
         <v>-0.1491</v>
       </c>
-      <c r="Z20" s="95" t="n">
+      <c r="Z20" s="104" t="n">
         <v>-0.0887</v>
       </c>
       <c r="AA20" s="58" t="str">
@@ -32654,9 +32751,9 @@
       <c r="U21" s="81"/>
       <c r="V21" s="83"/>
       <c r="W21" s="83"/>
-      <c r="X21" s="94"/>
-      <c r="Y21" s="96"/>
-      <c r="Z21" s="96"/>
+      <c r="X21" s="103"/>
+      <c r="Y21" s="105"/>
+      <c r="Z21" s="105"/>
       <c r="AA21" s="59" t="str">
         <v>human_s</v>
       </c>
@@ -32730,13 +32827,13 @@
       <c r="W22" s="82" t="n">
         <v>0.1664</v>
       </c>
-      <c r="X22" s="93" t="n">
+      <c r="X22" s="102" t="n">
         <v>0.0276</v>
       </c>
-      <c r="Y22" s="95" t="n">
+      <c r="Y22" s="104" t="n">
         <v>-0.0619</v>
       </c>
-      <c r="Z22" s="95" t="n">
+      <c r="Z22" s="104" t="n">
         <v>0.1253</v>
       </c>
       <c r="AA22" s="58" t="str">
@@ -32812,13 +32909,13 @@
       <c r="W23" s="83" t="n">
         <v>0.0866</v>
       </c>
-      <c r="X23" s="94" t="n">
+      <c r="X23" s="103" t="n">
         <v>-0.1197</v>
       </c>
-      <c r="Y23" s="96" t="n">
+      <c r="Y23" s="105" t="n">
         <v>-0.1439</v>
       </c>
-      <c r="Z23" s="96" t="n">
+      <c r="Z23" s="105" t="n">
         <v>-0.0961</v>
       </c>
       <c r="AA23" s="59" t="str">
@@ -32894,13 +32991,13 @@
       <c r="W24" s="82" t="n">
         <v>0.126</v>
       </c>
-      <c r="X24" s="93" t="n">
+      <c r="X24" s="102" t="n">
         <v>-0.0879</v>
       </c>
-      <c r="Y24" s="95" t="n">
+      <c r="Y24" s="104" t="n">
         <v>-0.1817</v>
       </c>
-      <c r="Z24" s="95" t="n">
+      <c r="Z24" s="104" t="n">
         <v>-0.014</v>
       </c>
       <c r="AA24" s="58" t="str">
@@ -32976,13 +33073,13 @@
       <c r="W25" s="83" t="n">
         <v>0.0939</v>
       </c>
-      <c r="X25" s="94" t="n">
+      <c r="X25" s="103" t="n">
         <v>-0.1112</v>
       </c>
-      <c r="Y25" s="96" t="n">
+      <c r="Y25" s="105" t="n">
         <v>-0.1364</v>
       </c>
-      <c r="Z25" s="96" t="n">
+      <c r="Z25" s="105" t="n">
         <v>-0.0852</v>
       </c>
       <c r="AA25" s="59" t="str">
@@ -33058,13 +33155,13 @@
       <c r="W26" s="82" t="n">
         <v>0.0655</v>
       </c>
-      <c r="X26" s="93" t="n">
+      <c r="X26" s="102" t="n">
         <v>-0.1069</v>
       </c>
-      <c r="Y26" s="95" t="n">
+      <c r="Y26" s="104" t="n">
         <v>-0.1673</v>
       </c>
-      <c r="Z26" s="95" t="n">
+      <c r="Z26" s="104" t="n">
         <v>-0.0629</v>
       </c>
       <c r="AA26" s="58" t="str">
@@ -33140,13 +33237,13 @@
       <c r="W27" s="83" t="n">
         <v>0.1047</v>
       </c>
-      <c r="X27" s="94" t="n">
+      <c r="X27" s="103" t="n">
         <v>-0.1173</v>
       </c>
-      <c r="Y27" s="96" t="n">
+      <c r="Y27" s="105" t="n">
         <v>-0.1482</v>
       </c>
-      <c r="Z27" s="96" t="n">
+      <c r="Z27" s="105" t="n">
         <v>-0.093</v>
       </c>
       <c r="AA27" s="59" t="str">
@@ -33222,13 +33319,13 @@
       <c r="W28" s="82" t="n">
         <v>0.0815</v>
       </c>
-      <c r="X28" s="93" t="n">
+      <c r="X28" s="102" t="n">
         <v>-0.0948</v>
       </c>
-      <c r="Y28" s="95" t="n">
+      <c r="Y28" s="104" t="n">
         <v>-0.1916</v>
       </c>
-      <c r="Z28" s="95" t="n">
+      <c r="Z28" s="104" t="n">
         <v>-0.0065</v>
       </c>
       <c r="AA28" s="58" t="str">
@@ -33304,13 +33401,13 @@
       <c r="W29" s="83" t="n">
         <v>0.1969</v>
       </c>
-      <c r="X29" s="94" t="n">
+      <c r="X29" s="103" t="n">
         <v>0.0405</v>
       </c>
-      <c r="Y29" s="96" t="n">
+      <c r="Y29" s="105" t="n">
         <v>-0.0181</v>
       </c>
-      <c r="Z29" s="96" t="n">
+      <c r="Z29" s="105" t="n">
         <v>0.0971</v>
       </c>
       <c r="AA29" s="59" t="str">
@@ -33386,13 +33483,13 @@
       <c r="W30" s="82" t="n">
         <v>0.0966</v>
       </c>
-      <c r="X30" s="93" t="n">
+      <c r="X30" s="102" t="n">
         <v>-0.1219</v>
       </c>
-      <c r="Y30" s="95" t="n">
+      <c r="Y30" s="104" t="n">
         <v>-0.1553</v>
       </c>
-      <c r="Z30" s="95" t="n">
+      <c r="Z30" s="104" t="n">
         <v>-0.0961</v>
       </c>
       <c r="AA30" s="58" t="str">
@@ -33468,13 +33565,13 @@
       <c r="W31" s="83" t="n">
         <v>0.1516</v>
       </c>
-      <c r="X31" s="94" t="n">
+      <c r="X31" s="103" t="n">
         <v>-0.023</v>
       </c>
-      <c r="Y31" s="96" t="n">
+      <c r="Y31" s="105" t="n">
         <v>-0.1409</v>
       </c>
-      <c r="Z31" s="96" t="n">
+      <c r="Z31" s="105" t="n">
         <v>0.0854</v>
       </c>
       <c r="AA31" s="59" t="str">
@@ -33550,13 +33647,13 @@
       <c r="W32" s="82" t="n">
         <v>0.1404</v>
       </c>
-      <c r="X32" s="93" t="n">
+      <c r="X32" s="102" t="n">
         <v>-0.0296</v>
       </c>
-      <c r="Y32" s="95" t="n">
+      <c r="Y32" s="104" t="n">
         <v>-0.0994</v>
       </c>
-      <c r="Z32" s="95" t="n">
+      <c r="Z32" s="104" t="n">
         <v>0.0433</v>
       </c>
       <c r="AA32" s="58" t="str">
@@ -33632,13 +33729,13 @@
       <c r="W33" s="83" t="n">
         <v>0.0913</v>
       </c>
-      <c r="X33" s="94" t="n">
+      <c r="X33" s="103" t="n">
         <v>-0.0761</v>
       </c>
-      <c r="Y33" s="96" t="n">
+      <c r="Y33" s="105" t="n">
         <v>-0.1288</v>
       </c>
-      <c r="Z33" s="96" t="n">
+      <c r="Z33" s="105" t="n">
         <v>-0.0233</v>
       </c>
       <c r="AA33" s="59" t="str">
@@ -33714,13 +33811,13 @@
       <c r="W34" s="82" t="n">
         <v>0.1022</v>
       </c>
-      <c r="X34" s="93" t="n">
+      <c r="X34" s="102" t="n">
         <v>-0.1063</v>
       </c>
-      <c r="Y34" s="95" t="n">
+      <c r="Y34" s="104" t="n">
         <v>-0.1329</v>
       </c>
-      <c r="Z34" s="95" t="n">
+      <c r="Z34" s="104" t="n">
         <v>-0.0816</v>
       </c>
       <c r="AA34" s="58" t="str">
@@ -33758,9 +33855,9 @@
       <c r="U35" s="81"/>
       <c r="V35" s="83"/>
       <c r="W35" s="83"/>
-      <c r="X35" s="94"/>
-      <c r="Y35" s="96"/>
-      <c r="Z35" s="96"/>
+      <c r="X35" s="103"/>
+      <c r="Y35" s="105"/>
+      <c r="Z35" s="105"/>
       <c r="AA35" s="59" t="str">
         <v>cont_s</v>
       </c>
@@ -33834,13 +33931,13 @@
       <c r="W36" s="82" t="n">
         <v>0.0654</v>
       </c>
-      <c r="X36" s="93" t="n">
+      <c r="X36" s="102" t="n">
         <v>-0.0584</v>
       </c>
-      <c r="Y36" s="95" t="n">
+      <c r="Y36" s="104" t="n">
         <v>-0.1084</v>
       </c>
-      <c r="Z36" s="95" t="n">
+      <c r="Z36" s="104" t="n">
         <v>-0.0087</v>
       </c>
       <c r="AA36" s="58" t="str">
@@ -33916,13 +34013,13 @@
       <c r="W37" s="83" t="n">
         <v>0.1171</v>
       </c>
-      <c r="X37" s="94" t="n">
+      <c r="X37" s="103" t="n">
         <v>-0.0985</v>
       </c>
-      <c r="Y37" s="96" t="n">
+      <c r="Y37" s="105" t="n">
         <v>-0.1381</v>
       </c>
-      <c r="Z37" s="96" t="n">
+      <c r="Z37" s="105" t="n">
         <v>-0.065</v>
       </c>
       <c r="AA37" s="59" t="str">
@@ -33998,13 +34095,13 @@
       <c r="W38" s="82" t="n">
         <v>0.1166</v>
       </c>
-      <c r="X38" s="93" t="n">
+      <c r="X38" s="102" t="n">
         <v>-0.1229</v>
       </c>
-      <c r="Y38" s="95" t="n">
+      <c r="Y38" s="104" t="n">
         <v>-0.2155</v>
       </c>
-      <c r="Z38" s="95" t="n">
+      <c r="Z38" s="104" t="n">
         <v>-0.0346</v>
       </c>
       <c r="AA38" s="58" t="str">
@@ -34080,13 +34177,13 @@
       <c r="W39" s="83" t="n">
         <v>0.1567</v>
       </c>
-      <c r="X39" s="94" t="n">
+      <c r="X39" s="103" t="n">
         <v>-0.0495</v>
       </c>
-      <c r="Y39" s="96" t="n">
+      <c r="Y39" s="105" t="n">
         <v>-0.1593</v>
       </c>
-      <c r="Z39" s="96" t="n">
+      <c r="Z39" s="105" t="n">
         <v>0.0452</v>
       </c>
       <c r="AA39" s="59" t="str">
@@ -34162,13 +34259,13 @@
       <c r="W40" s="82" t="n">
         <v>0.0608</v>
       </c>
-      <c r="X40" s="93" t="n">
+      <c r="X40" s="102" t="n">
         <v>-0.0516</v>
       </c>
-      <c r="Y40" s="95" t="n">
+      <c r="Y40" s="104" t="n">
         <v>-0.2201</v>
       </c>
-      <c r="Z40" s="95" t="n">
+      <c r="Z40" s="104" t="n">
         <v>0.0528</v>
       </c>
       <c r="AA40" s="58" t="str">
@@ -34244,13 +34341,13 @@
       <c r="W41" s="83" t="n">
         <v>0.0915</v>
       </c>
-      <c r="X41" s="94" t="n">
+      <c r="X41" s="103" t="n">
         <v>-0.131</v>
       </c>
-      <c r="Y41" s="96" t="n">
+      <c r="Y41" s="105" t="n">
         <v>-0.1706</v>
       </c>
-      <c r="Z41" s="96" t="n">
+      <c r="Z41" s="105" t="n">
         <v>-0.0955</v>
       </c>
       <c r="AA41" s="59" t="str">
@@ -34326,13 +34423,13 @@
       <c r="W42" s="82" t="n">
         <v>0</v>
       </c>
-      <c r="X42" s="93" t="n">
+      <c r="X42" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="Y42" s="95" t="n">
+      <c r="Y42" s="104" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" s="95" t="n">
+      <c r="Z42" s="104" t="n">
         <v>0</v>
       </c>
       <c r="AA42" s="58" t="str">
@@ -34408,13 +34505,13 @@
       <c r="W43" s="83" t="n">
         <v>0.1125</v>
       </c>
-      <c r="X43" s="94" t="n">
+      <c r="X43" s="103" t="n">
         <v>-0.1117</v>
       </c>
-      <c r="Y43" s="96" t="n">
+      <c r="Y43" s="105" t="n">
         <v>-0.1375</v>
       </c>
-      <c r="Z43" s="96" t="n">
+      <c r="Z43" s="105" t="n">
         <v>-0.0837</v>
       </c>
       <c r="AA43" s="59" t="str">
@@ -34490,13 +34587,13 @@
       <c r="W44" s="82" t="n">
         <v>0.0942</v>
       </c>
-      <c r="X44" s="93" t="n">
+      <c r="X44" s="102" t="n">
         <v>-0.1042</v>
       </c>
-      <c r="Y44" s="95" t="n">
+      <c r="Y44" s="104" t="n">
         <v>-0.1414</v>
       </c>
-      <c r="Z44" s="95" t="n">
+      <c r="Z44" s="104" t="n">
         <v>-0.0678</v>
       </c>
       <c r="AA44" s="58" t="str">
@@ -34572,13 +34669,13 @@
       <c r="W45" s="83" t="n">
         <v>0.3041</v>
       </c>
-      <c r="X45" s="94" t="n">
+      <c r="X45" s="103" t="n">
         <v>-0.0522</v>
       </c>
-      <c r="Y45" s="96" t="n">
+      <c r="Y45" s="105" t="n">
         <v>-0.133</v>
       </c>
-      <c r="Z45" s="96" t="n">
+      <c r="Z45" s="105" t="n">
         <v>0.0321</v>
       </c>
       <c r="AA45" s="59" t="str">
@@ -34654,13 +34751,13 @@
       <c r="W46" s="82" t="n">
         <v>0.0933</v>
       </c>
-      <c r="X46" s="93" t="n">
+      <c r="X46" s="102" t="n">
         <v>-0.1245</v>
       </c>
-      <c r="Y46" s="95" t="n">
+      <c r="Y46" s="104" t="n">
         <v>-0.2385</v>
       </c>
-      <c r="Z46" s="95" t="n">
+      <c r="Z46" s="104" t="n">
         <v>-0.0364</v>
       </c>
       <c r="AA46" s="58" t="str">
@@ -34736,13 +34833,13 @@
       <c r="W47" s="83" t="n">
         <v>0.078</v>
       </c>
-      <c r="X47" s="94" t="n">
+      <c r="X47" s="103" t="n">
         <v>-0.0442</v>
       </c>
-      <c r="Y47" s="96" t="n">
+      <c r="Y47" s="105" t="n">
         <v>-0.1094</v>
       </c>
-      <c r="Z47" s="96" t="n">
+      <c r="Z47" s="105" t="n">
         <v>0.0172</v>
       </c>
       <c r="AA47" s="59" t="str">
@@ -34818,13 +34915,13 @@
       <c r="W48" s="82" t="n">
         <v>0.098</v>
       </c>
-      <c r="X48" s="93" t="n">
+      <c r="X48" s="102" t="n">
         <v>-0.1163</v>
       </c>
-      <c r="Y48" s="95" t="n">
+      <c r="Y48" s="104" t="n">
         <v>-0.3048</v>
       </c>
-      <c r="Z48" s="95" t="n">
+      <c r="Z48" s="104" t="n">
         <v>-0.0089</v>
       </c>
       <c r="AA48" s="58" t="str">
@@ -34900,13 +34997,13 @@
       <c r="W49" s="83" t="n">
         <v>0.1195</v>
       </c>
-      <c r="X49" s="94" t="n">
+      <c r="X49" s="103" t="n">
         <v>-0.0765</v>
       </c>
-      <c r="Y49" s="96" t="n">
+      <c r="Y49" s="105" t="n">
         <v>-0.1887</v>
       </c>
-      <c r="Z49" s="96" t="n">
+      <c r="Z49" s="105" t="n">
         <v>0.019</v>
       </c>
       <c r="AA49" s="59" t="str">
@@ -34982,13 +35079,13 @@
       <c r="W50" s="82" t="n">
         <v>0.1345</v>
       </c>
-      <c r="X50" s="93" t="n">
+      <c r="X50" s="102" t="n">
         <v>-0.1366</v>
       </c>
-      <c r="Y50" s="95" t="n">
+      <c r="Y50" s="104" t="n">
         <v>-0.284</v>
       </c>
-      <c r="Z50" s="95" t="n">
+      <c r="Z50" s="104" t="n">
         <v>-0.0287</v>
       </c>
       <c r="AA50" s="58" t="str">
@@ -35064,13 +35161,13 @@
       <c r="W51" s="83" t="n">
         <v>0.176</v>
       </c>
-      <c r="X51" s="94" t="n">
+      <c r="X51" s="103" t="n">
         <v>-0.0946</v>
       </c>
-      <c r="Y51" s="96" t="n">
+      <c r="Y51" s="105" t="n">
         <v>-0.1991</v>
       </c>
-      <c r="Z51" s="96" t="n">
+      <c r="Z51" s="105" t="n">
         <v>0.0029</v>
       </c>
       <c r="AA51" s="59" t="str">
@@ -35146,13 +35243,13 @@
       <c r="W52" s="82" t="n">
         <v>0.1155</v>
       </c>
-      <c r="X52" s="93" t="n">
+      <c r="X52" s="102" t="n">
         <v>-0.1471</v>
       </c>
-      <c r="Y52" s="95" t="n">
+      <c r="Y52" s="104" t="n">
         <v>-0.2034</v>
       </c>
-      <c r="Z52" s="95" t="n">
+      <c r="Z52" s="104" t="n">
         <v>-0.0952</v>
       </c>
       <c r="AA52" s="58" t="str">
@@ -35228,13 +35325,13 @@
       <c r="W53" s="83" t="n">
         <v>0.062</v>
       </c>
-      <c r="X53" s="94" t="n">
+      <c r="X53" s="103" t="n">
         <v>-0.1348</v>
       </c>
-      <c r="Y53" s="96" t="n">
+      <c r="Y53" s="105" t="n">
         <v>-0.1686</v>
       </c>
-      <c r="Z53" s="96" t="n">
+      <c r="Z53" s="105" t="n">
         <v>-0.1068</v>
       </c>
       <c r="AA53" s="59" t="str">
@@ -35310,13 +35407,13 @@
       <c r="W54" s="82" t="n">
         <v>0.0943</v>
       </c>
-      <c r="X54" s="93" t="n">
+      <c r="X54" s="102" t="n">
         <v>-0.0962</v>
       </c>
-      <c r="Y54" s="95" t="n">
+      <c r="Y54" s="104" t="n">
         <v>-0.1231</v>
       </c>
-      <c r="Z54" s="95" t="n">
+      <c r="Z54" s="104" t="n">
         <v>-0.0713</v>
       </c>
       <c r="AA54" s="58" t="str">
@@ -35392,13 +35489,13 @@
       <c r="W55" s="83" t="n">
         <v>0.0915</v>
       </c>
-      <c r="X55" s="94" t="n">
+      <c r="X55" s="103" t="n">
         <v>-0.131</v>
       </c>
-      <c r="Y55" s="96" t="n">
+      <c r="Y55" s="105" t="n">
         <v>-0.1706</v>
       </c>
-      <c r="Z55" s="96" t="n">
+      <c r="Z55" s="105" t="n">
         <v>-0.0955</v>
       </c>
       <c r="AA55" s="59" t="str">
@@ -35474,13 +35571,13 @@
       <c r="W56" s="82" t="n">
         <v>0.1206</v>
       </c>
-      <c r="X56" s="93" t="n">
+      <c r="X56" s="102" t="n">
         <v>-0.1071</v>
       </c>
-      <c r="Y56" s="95" t="n">
+      <c r="Y56" s="104" t="n">
         <v>-0.2135</v>
       </c>
-      <c r="Z56" s="95" t="n">
+      <c r="Z56" s="104" t="n">
         <v>-0.0256</v>
       </c>
       <c r="AA56" s="58" t="str">
@@ -35556,13 +35653,13 @@
       <c r="W57" s="83" t="n">
         <v>0.1398</v>
       </c>
-      <c r="X57" s="94" t="n">
+      <c r="X57" s="103" t="n">
         <v>-0.1334</v>
       </c>
-      <c r="Y57" s="96" t="n">
+      <c r="Y57" s="105" t="n">
         <v>-0.2228</v>
       </c>
-      <c r="Z57" s="96" t="n">
+      <c r="Z57" s="105" t="n">
         <v>-0.0565</v>
       </c>
       <c r="AA57" s="59" t="str">
@@ -35638,13 +35735,13 @@
       <c r="W58" s="82" t="n">
         <v>0.1173</v>
       </c>
-      <c r="X58" s="93" t="n">
+      <c r="X58" s="102" t="n">
         <v>-0.0861</v>
       </c>
-      <c r="Y58" s="95" t="n">
+      <c r="Y58" s="104" t="n">
         <v>-0.1724</v>
       </c>
-      <c r="Z58" s="95" t="n">
+      <c r="Z58" s="104" t="n">
         <v>-0.0062</v>
       </c>
       <c r="AA58" s="58" t="str">
@@ -35720,13 +35817,13 @@
       <c r="W59" s="83" t="n">
         <v>0.1164</v>
       </c>
-      <c r="X59" s="94" t="n">
+      <c r="X59" s="103" t="n">
         <v>-0.0707</v>
       </c>
-      <c r="Y59" s="96" t="n">
+      <c r="Y59" s="105" t="n">
         <v>-0.1547</v>
       </c>
-      <c r="Z59" s="96" t="n">
+      <c r="Z59" s="105" t="n">
         <v>-0.0075</v>
       </c>
       <c r="AA59" s="59" t="str">
@@ -35802,13 +35899,13 @@
       <c r="W60" s="82" t="n">
         <v>0.0423</v>
       </c>
-      <c r="X60" s="93" t="n">
+      <c r="X60" s="102" t="n">
         <v>-0.0295</v>
       </c>
-      <c r="Y60" s="95" t="n">
+      <c r="Y60" s="104" t="n">
         <v>-0.0972</v>
       </c>
-      <c r="Z60" s="95" t="n">
+      <c r="Z60" s="104" t="n">
         <v>0.0214</v>
       </c>
       <c r="AA60" s="58" t="str">
@@ -35884,13 +35981,13 @@
       <c r="W61" s="83" t="n">
         <v>0.2018</v>
       </c>
-      <c r="X61" s="94" t="n">
+      <c r="X61" s="103" t="n">
         <v>-0.1173</v>
       </c>
-      <c r="Y61" s="96" t="n">
+      <c r="Y61" s="105" t="n">
         <v>-0.2354</v>
       </c>
-      <c r="Z61" s="96" t="n">
+      <c r="Z61" s="105" t="n">
         <v>0.0189</v>
       </c>
       <c r="AA61" s="59" t="str">
@@ -35966,13 +36063,13 @@
       <c r="W62" s="82" t="n">
         <v>0.1193</v>
       </c>
-      <c r="X62" s="93" t="n">
+      <c r="X62" s="102" t="n">
         <v>-0.1838</v>
       </c>
-      <c r="Y62" s="95" t="n">
+      <c r="Y62" s="104" t="n">
         <v>-0.3417</v>
       </c>
-      <c r="Z62" s="95" t="n">
+      <c r="Z62" s="104" t="n">
         <v>-0.0599</v>
       </c>
       <c r="AA62" s="58" t="str">
@@ -36048,13 +36145,13 @@
       <c r="W63" s="83" t="n">
         <v>0.2893</v>
       </c>
-      <c r="X63" s="94" t="n">
+      <c r="X63" s="103" t="n">
         <v>0.0222</v>
       </c>
-      <c r="Y63" s="96" t="n">
+      <c r="Y63" s="105" t="n">
         <v>-0.1189</v>
       </c>
-      <c r="Z63" s="96" t="n">
+      <c r="Z63" s="105" t="n">
         <v>0.1414</v>
       </c>
       <c r="AA63" s="59" t="str">
@@ -36130,13 +36227,13 @@
       <c r="W64" s="82" t="n">
         <v>0.1536</v>
       </c>
-      <c r="X64" s="93" t="n">
+      <c r="X64" s="102" t="n">
         <v>-0.2103</v>
       </c>
-      <c r="Y64" s="95" t="n">
+      <c r="Y64" s="104" t="n">
         <v>-0.4324</v>
       </c>
-      <c r="Z64" s="95" t="n">
+      <c r="Z64" s="104" t="n">
         <v>0.0393</v>
       </c>
       <c r="AA64" s="58" t="str">
@@ -36212,13 +36309,13 @@
       <c r="W65" s="83" t="n">
         <v>0.0952</v>
       </c>
-      <c r="X65" s="94" t="n">
+      <c r="X65" s="103" t="n">
         <v>-0.0863</v>
       </c>
-      <c r="Y65" s="96" t="n">
+      <c r="Y65" s="105" t="n">
         <v>-0.1925</v>
       </c>
-      <c r="Z65" s="96" t="n">
+      <c r="Z65" s="105" t="n">
         <v>0.0021</v>
       </c>
       <c r="AA65" s="59" t="str">
@@ -36294,13 +36391,13 @@
       <c r="W66" s="82" t="n">
         <v>0.117</v>
       </c>
-      <c r="X66" s="93" t="n">
+      <c r="X66" s="102" t="n">
         <v>-0.0229</v>
       </c>
-      <c r="Y66" s="95" t="n">
+      <c r="Y66" s="104" t="n">
         <v>-0.3254</v>
       </c>
-      <c r="Z66" s="95" t="n">
+      <c r="Z66" s="104" t="n">
         <v>0.061</v>
       </c>
       <c r="AA66" s="58" t="str">
@@ -36376,13 +36473,13 @@
       <c r="W67" s="83" t="n">
         <v>0.1588</v>
       </c>
-      <c r="X67" s="94" t="n">
+      <c r="X67" s="103" t="n">
         <v>-0.0546</v>
       </c>
-      <c r="Y67" s="96" t="n">
+      <c r="Y67" s="105" t="n">
         <v>-0.1717</v>
       </c>
-      <c r="Z67" s="96" t="n">
+      <c r="Z67" s="105" t="n">
         <v>0.0401</v>
       </c>
       <c r="AA67" s="59" t="str">
@@ -36458,13 +36555,13 @@
       <c r="W68" s="82" t="n">
         <v>0.2078</v>
       </c>
-      <c r="X68" s="93" t="n">
+      <c r="X68" s="102" t="n">
         <v>-0.0013</v>
       </c>
-      <c r="Y68" s="95" t="n">
+      <c r="Y68" s="104" t="n">
         <v>-0.173</v>
       </c>
-      <c r="Z68" s="95" t="n">
+      <c r="Z68" s="104" t="n">
         <v>0.1183</v>
       </c>
       <c r="AA68" s="58" t="str">
@@ -36540,13 +36637,13 @@
       <c r="W69" s="83" t="n">
         <v>0.2516</v>
       </c>
-      <c r="X69" s="94" t="n">
+      <c r="X69" s="103" t="n">
         <v>-0.1154</v>
       </c>
-      <c r="Y69" s="96" t="n">
+      <c r="Y69" s="105" t="n">
         <v>-0.2495</v>
       </c>
-      <c r="Z69" s="96" t="n">
+      <c r="Z69" s="105" t="n">
         <v>0.0514</v>
       </c>
       <c r="AA69" s="59" t="str">
@@ -36622,13 +36719,13 @@
       <c r="W70" s="82" t="n">
         <v>0.1246</v>
       </c>
-      <c r="X70" s="93" t="n">
+      <c r="X70" s="102" t="n">
         <v>-0.2549</v>
       </c>
-      <c r="Y70" s="95" t="n">
+      <c r="Y70" s="104" t="n">
         <v>-0.4988</v>
       </c>
-      <c r="Z70" s="95" t="n">
+      <c r="Z70" s="104" t="n">
         <v>-0.0705</v>
       </c>
       <c r="AA70" s="58" t="str">
@@ -36704,13 +36801,13 @@
       <c r="W71" s="83" t="n">
         <v>0.117</v>
       </c>
-      <c r="X71" s="94" t="n">
+      <c r="X71" s="103" t="n">
         <v>-0.1305</v>
       </c>
-      <c r="Y71" s="96" t="n">
+      <c r="Y71" s="105" t="n">
         <v>-0.3574</v>
       </c>
-      <c r="Z71" s="96" t="n">
+      <c r="Z71" s="105" t="n">
         <v>0.0265</v>
       </c>
       <c r="AA71" s="59" t="str">
@@ -36786,13 +36883,13 @@
       <c r="W72" s="82" t="n">
         <v>0.105</v>
       </c>
-      <c r="X72" s="93" t="n">
+      <c r="X72" s="102" t="n">
         <v>-0.107</v>
       </c>
-      <c r="Y72" s="95" t="n">
+      <c r="Y72" s="104" t="n">
         <v>-0.1357</v>
       </c>
-      <c r="Z72" s="95" t="n">
+      <c r="Z72" s="104" t="n">
         <v>-0.0809</v>
       </c>
       <c r="AA72" s="58" t="str">
@@ -36868,13 +36965,13 @@
       <c r="W73" s="83" t="n">
         <v>0.0989</v>
       </c>
-      <c r="X73" s="94" t="n">
+      <c r="X73" s="103" t="n">
         <v>-0.1092</v>
       </c>
-      <c r="Y73" s="96" t="n">
+      <c r="Y73" s="105" t="n">
         <v>-0.137</v>
       </c>
-      <c r="Z73" s="96" t="n">
+      <c r="Z73" s="105" t="n">
         <v>-0.0818</v>
       </c>
       <c r="AA73" s="59" t="str">
@@ -36950,13 +37047,13 @@
       <c r="W74" s="82" t="n">
         <v>0.1004</v>
       </c>
-      <c r="X74" s="93" t="n">
+      <c r="X74" s="102" t="n">
         <v>-0.1014</v>
       </c>
-      <c r="Y74" s="95" t="n">
+      <c r="Y74" s="104" t="n">
         <v>-0.135</v>
       </c>
-      <c r="Z74" s="95" t="n">
+      <c r="Z74" s="104" t="n">
         <v>-0.0736</v>
       </c>
       <c r="AA74" s="58" t="str">
@@ -37032,13 +37129,13 @@
       <c r="W75" s="83" t="n">
         <v>0.1498</v>
       </c>
-      <c r="X75" s="94" t="n">
+      <c r="X75" s="103" t="n">
         <v>-0.0422</v>
       </c>
-      <c r="Y75" s="96" t="n">
+      <c r="Y75" s="105" t="n">
         <v>-0.068</v>
       </c>
-      <c r="Z75" s="96" t="n">
+      <c r="Z75" s="105" t="n">
         <v>-0.0185</v>
       </c>
       <c r="AA75" s="59" t="str">
@@ -37114,13 +37211,13 @@
       <c r="W76" s="82" t="n">
         <v>0.0969</v>
       </c>
-      <c r="X76" s="93" t="n">
+      <c r="X76" s="102" t="n">
         <v>-0.0659</v>
       </c>
-      <c r="Y76" s="95" t="n">
+      <c r="Y76" s="104" t="n">
         <v>-0.0823</v>
       </c>
-      <c r="Z76" s="95" t="n">
+      <c r="Z76" s="104" t="n">
         <v>-0.049</v>
       </c>
       <c r="AA76" s="58" t="str">
@@ -37196,13 +37293,13 @@
       <c r="W77" s="83" t="n">
         <v>0.1255</v>
       </c>
-      <c r="X77" s="94" t="n">
+      <c r="X77" s="103" t="n">
         <v>-0.1151</v>
       </c>
-      <c r="Y77" s="96" t="n">
+      <c r="Y77" s="105" t="n">
         <v>-0.1753</v>
       </c>
-      <c r="Z77" s="96" t="n">
+      <c r="Z77" s="105" t="n">
         <v>-0.0584</v>
       </c>
       <c r="AA77" s="59" t="str">
@@ -37278,13 +37375,13 @@
       <c r="W78" s="89" t="n">
         <v>0.0651</v>
       </c>
-      <c r="X78" s="97" t="n">
+      <c r="X78" s="106" t="n">
         <v>-0.1264</v>
       </c>
-      <c r="Y78" s="98" t="n">
+      <c r="Y78" s="107" t="n">
         <v>-0.1529</v>
       </c>
-      <c r="Z78" s="98" t="n">
+      <c r="Z78" s="107" t="n">
         <v>-0.103</v>
       </c>
       <c r="AA78" s="76" t="str">
@@ -38082,7 +38179,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS8&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="Rb62ff5980e7c4dca"/>
+    <tablePart ns1:id="R39126c0ed6f94ee1"/>
   </tableParts>
 </worksheet>
 </file>
--- a/outputs/Stack-and-reuse/Supplementary-Tables/Supplementary-Tables.xlsx
+++ b/outputs/Stack-and-reuse/Supplementary-Tables/Supplementary-Tables.xlsx
@@ -2,28 +2,29 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Contents" sheetId="1" ns1:id="R6faf48ee4f364b35"/>
-    <sheet name="S1" sheetId="2" ns1:id="Rcd735eb6b43c4442"/>
-    <sheet name="S2" sheetId="3" ns1:id="R882e083dbfe14dcf"/>
-    <sheet name="S3" sheetId="4" ns1:id="R28603e94d4b34147"/>
-    <sheet name="S4" sheetId="5" ns1:id="R668eaa974e3847b8"/>
-    <sheet name="S5" sheetId="6" ns1:id="R2464c7afd8814c49"/>
-    <sheet name="S6" sheetId="7" ns1:id="Rccc85357321e47e6"/>
-    <sheet name="S7" sheetId="8" ns1:id="R2f4e0b8dc1664135"/>
-    <sheet name="S8" sheetId="9" ns1:id="R4019d84ede8e4df4"/>
-    <sheet name="S9" sheetId="10" ns1:id="R16576041fed145ad"/>
-    <sheet name="S10" sheetId="11" ns1:id="Rf4abb955d2fb4ff2"/>
-    <sheet name="S11" sheetId="12" ns1:id="Readd855356344af7"/>
-    <sheet name="S12" sheetId="13" ns1:id="Rfbcdc0595a414ca5"/>
-    <sheet name="S13" sheetId="14" ns1:id="R332fe6b4352f4ae7"/>
-    <sheet name="S14" sheetId="15" ns1:id="R688aec16cc6d4268"/>
-    <sheet name="S15" sheetId="16" ns1:id="R393e235bfd4c4d58"/>
-    <sheet name="S16" sheetId="17" ns1:id="R2ac501d5f0404483"/>
-    <sheet name="S17" sheetId="18" ns1:id="Rc82c2ce9784e444a"/>
-    <sheet name="S18" sheetId="19" ns1:id="R8e7840fc83d1460e"/>
-    <sheet name="S19" sheetId="20" ns1:id="R75d9ab5c37614f48"/>
-    <sheet name="S20" sheetId="21" ns1:id="Ra14b4444d04f4586"/>
-    <sheet name="S21" sheetId="22" ns1:id="R65d4599f1e8443b0"/>
+    <sheet name="Contents" sheetId="1" ns1:id="Rab75b308679f4a33"/>
+    <sheet name="S1" sheetId="2" ns1:id="Rf40c8566242e4e07"/>
+    <sheet name="S2" sheetId="3" ns1:id="Rc76692ae990f4a15"/>
+    <sheet name="S3" sheetId="4" ns1:id="Rcaa81fd2f32446ed"/>
+    <sheet name="S4" sheetId="5" ns1:id="R3859053b867b455f"/>
+    <sheet name="S5" sheetId="6" ns1:id="Rb1d02a3701034aa5"/>
+    <sheet name="S6" sheetId="7" ns1:id="Rbed157908ce14110"/>
+    <sheet name="S7" sheetId="8" ns1:id="Rc561f7f573bc4b97"/>
+    <sheet name="S8" sheetId="9" ns1:id="R00e9148d09374cc2"/>
+    <sheet name="S9" sheetId="10" ns1:id="R40ff1988a2504ec6"/>
+    <sheet name="S10" sheetId="11" ns1:id="R5f11d49826ca40d4"/>
+    <sheet name="S11" sheetId="12" ns1:id="R4077b5bd649f4c38"/>
+    <sheet name="S12" sheetId="13" ns1:id="R41174f8cac674343"/>
+    <sheet name="S13" sheetId="14" ns1:id="R21a0262c146d402c"/>
+    <sheet name="S14" sheetId="15" ns1:id="Rfe904dae251a4268"/>
+    <sheet name="S15" sheetId="16" ns1:id="Rec7fe9f259fb4683"/>
+    <sheet name="S16" sheetId="17" ns1:id="Rb9ad0b636f4a42ac"/>
+    <sheet name="S17" sheetId="18" ns1:id="R7d6e75ea737246db"/>
+    <sheet name="S18" sheetId="19" ns1:id="Re46c724494d6433a"/>
+    <sheet name="S19" sheetId="20" ns1:id="R22d79e6faba14693"/>
+    <sheet name="S20" sheetId="21" ns1:id="R5fe92315e1d04983"/>
+    <sheet name="S21" sheetId="22" ns1:id="R2a757c58164d4563"/>
+    <sheet name="S22" sheetId="23" ns1:id="Rba2ad32a51004f51"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Contents'!$B$2:$E$35</definedName>
@@ -69,6 +70,8 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="20">'S20'!$7:$7,'S20'!$B:$C</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="21">'S21'!$B$2:$F$128</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="21">'S21'!$7:$7,'S21'!$B:$B</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="22">'S22'!$B$2:$K$105</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="22">'S22'!$7:$7</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -79,7 +82,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="9">
+  <x:numFmts count="10">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0"/>
     <x:numFmt numFmtId="202" formatCode="0.0&quot;%&quot;"/>
@@ -89,6 +92,7 @@
     <x:numFmt numFmtId="206" formatCode="0.0%"/>
     <x:numFmt numFmtId="207" formatCode="0.000"/>
     <x:numFmt numFmtId="208" formatCode="0.00&quot;%&quot;"/>
+    <x:numFmt numFmtId="209" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="8">
     <x:font>
@@ -133,7 +137,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -148,6 +152,21 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF2E6F9E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F6F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2E6F9E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -224,7 +243,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="120">
+  <x:cellXfs count="150">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -629,6 +648,94 @@
     <x:xf numFmtId="202" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="209" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="209" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="209" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="209" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -640,7 +747,7 @@
         <x:color rgb="FFD1495B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFBECEF"/>
         </x:patternFill>
       </x:fill>
@@ -651,7 +758,7 @@
         <x:color rgb="FF986416"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4DF"/>
         </x:patternFill>
       </x:fill>
@@ -662,7 +769,7 @@
         <x:color rgb="FF74716C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF6F4EF"/>
         </x:patternFill>
       </x:fill>
@@ -949,6 +1056,25 @@
     <x:tableColumn id="3" name="Status"/>
     <x:tableColumn id="4" name="Robustness verdict"/>
     <x:tableColumn id="5" name="Wording after review"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="PRIDE_S22" displayName="PRIDE_S22" ref="B7:K101" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="B7:K101"/>
+  <x:tableColumns count="10">
+    <x:tableColumn id="1" name="Comparison"/>
+    <x:tableColumn id="2" name="Population"/>
+    <x:tableColumn id="3" name="Period or comparison"/>
+    <x:tableColumn id="4" name="Estimate"/>
+    <x:tableColumn id="5" name="Lower bound"/>
+    <x:tableColumn id="6" name="Upper bound"/>
+    <x:tableColumn id="7" name="Meaning of bounds"/>
+    <x:tableColumn id="8" name="Unit"/>
+    <x:tableColumn id="9" name="Definition or qualification"/>
+    <x:tableColumn id="10" name="Source"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -1351,7 +1477,7 @@
     <row r="4" ht="23" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="9" t="str">
-        <v>Supplementary tables S1–S21</v>
+        <v>Supplementary tables S1–S22</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -1754,12 +1880,20 @@
       </c>
       <c r="F31" s="3"/>
     </row>
-    <row r="32" ht="23" customHeight="1">
+    <row r="32" ht="32" customHeight="1">
       <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
+      <c r="B32" s="16" t="str">
+        <v>S22</v>
+      </c>
+      <c r="C32" s="26" t="str">
+        <v>Supporting numerical comparisons</v>
+      </c>
+      <c r="D32" s="12" t="str">
+        <v>Supporting comparisons</v>
+      </c>
+      <c r="E32" s="27" t="n">
+        <v>94</v>
+      </c>
       <c r="F32" s="3"/>
     </row>
     <row r="33" ht="23" customHeight="1">
@@ -1841,27 +1975,28 @@
     <mergeCell ref="B35:E35"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B11" location="'S1'!B2" display="S1" tooltip="Open supplementary table S1"/>
-    <hyperlink ref="B12" location="'S2'!B2" display="S2" tooltip="Open supplementary table S2"/>
-    <hyperlink ref="B13" location="'S3'!B2" display="S3" tooltip="Open supplementary table S3"/>
-    <hyperlink ref="B14" location="'S4'!B2" display="S4" tooltip="Open supplementary table S4"/>
-    <hyperlink ref="B15" location="'S5'!B2" display="S5" tooltip="Open supplementary table S5"/>
-    <hyperlink ref="B16" location="'S6'!B2" display="S6" tooltip="Open supplementary table S6"/>
-    <hyperlink ref="B17" location="'S7'!B2" display="S7" tooltip="Open supplementary table S7"/>
-    <hyperlink ref="B18" location="'S8'!B2" display="S8" tooltip="Open supplementary table S8"/>
-    <hyperlink ref="B19" location="'S9'!B2" display="S9" tooltip="Open supplementary table S9"/>
-    <hyperlink ref="B20" location="'S10'!B2" display="S10" tooltip="Open supplementary table S10"/>
-    <hyperlink ref="B21" location="'S11'!B2" display="S11" tooltip="Open supplementary table S11"/>
-    <hyperlink ref="B22" location="'S12'!B2" display="S12" tooltip="Open supplementary table S12"/>
-    <hyperlink ref="B23" location="'S13'!B2" display="S13" tooltip="Open supplementary table S13"/>
-    <hyperlink ref="B24" location="'S14'!B2" display="S14" tooltip="Open supplementary table S14"/>
-    <hyperlink ref="B25" location="'S15'!B2" display="S15" tooltip="Open supplementary table S15"/>
-    <hyperlink ref="B26" location="'S16'!B2" display="S16" tooltip="Open supplementary table S16"/>
-    <hyperlink ref="B27" location="'S17'!B2" display="S17" tooltip="Open supplementary table S17"/>
-    <hyperlink ref="B28" location="'S18'!B2" display="S18" tooltip="Open supplementary table S18"/>
-    <hyperlink ref="B29" location="'S19'!B2" display="S19" tooltip="Open supplementary table S19"/>
-    <hyperlink ref="B30" location="'S20'!B2" display="S20" tooltip="Open supplementary table S20"/>
-    <hyperlink ref="B31" location="'S21'!B2" display="S21" tooltip="Open supplementary table S21"/>
+    <hyperlink ref="B11" location="'S1'!B2"/>
+    <hyperlink ref="B12" location="'S2'!B2"/>
+    <hyperlink ref="B13" location="'S3'!B2"/>
+    <hyperlink ref="B14" location="'S4'!B2"/>
+    <hyperlink ref="B15" location="'S5'!B2"/>
+    <hyperlink ref="B16" location="'S6'!B2"/>
+    <hyperlink ref="B17" location="'S7'!B2"/>
+    <hyperlink ref="B18" location="'S8'!B2"/>
+    <hyperlink ref="B19" location="'S9'!B2"/>
+    <hyperlink ref="B20" location="'S10'!B2"/>
+    <hyperlink ref="B21" location="'S11'!B2"/>
+    <hyperlink ref="B22" location="'S12'!B2"/>
+    <hyperlink ref="B23" location="'S13'!B2"/>
+    <hyperlink ref="B24" location="'S14'!B2"/>
+    <hyperlink ref="B25" location="'S15'!B2"/>
+    <hyperlink ref="B26" location="'S16'!B2"/>
+    <hyperlink ref="B27" location="'S17'!B2"/>
+    <hyperlink ref="B28" location="'S18'!B2"/>
+    <hyperlink ref="B29" location="'S19'!B2"/>
+    <hyperlink ref="B30" location="'S20'!B2"/>
+    <hyperlink ref="B31" location="'S21'!B2"/>
+    <hyperlink ref="B32" location="'S22'!B2"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0" horizontalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.15" footer="0.2"/>
@@ -2699,7 +2834,7 @@
     <mergeCell ref="B45:E45"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B6" location="'Contents'!B2" display="Contents" tooltip="Return to contents"/>
+    <hyperlink ref="B6" location="'Contents'!B2"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0" horizontalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.15" footer="0.2"/>
@@ -2708,7 +2843,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS9&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="R951ee0b987804f2c"/>
+    <tablePart ns1:id="R66d6be05a1cd4e79"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3323,7 +3458,7 @@
     <mergeCell ref="B21:E21"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B6" location="'Contents'!B2" display="Contents" tooltip="Return to contents"/>
+    <hyperlink ref="B6" location="'Contents'!B2"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0" horizontalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.15" footer="0.2"/>
@@ -3332,7 +3467,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS10&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="R93310e9a8fda4149"/>
+    <tablePart ns1:id="Rb8f37c396c544d80"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4484,7 +4619,7 @@
     <mergeCell ref="B25:G25"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B6" location="'Contents'!B2" display="Contents" tooltip="Return to contents"/>
+    <hyperlink ref="B6" location="'Contents'!B2"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0" horizontalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.15" footer="0.2"/>
@@ -4493,7 +4628,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS11&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="Rc6a145580d09437a"/>
+    <tablePart ns1:id="R1c5fed60687147ca"/>
   </tableParts>
 </worksheet>
 </file>
@@ -5045,7 +5180,7 @@
     <mergeCell ref="B25:G25"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B6" location="'Contents'!B2" display="Contents" tooltip="Return to contents"/>
+    <hyperlink ref="B6" location="'Contents'!B2"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0" horizontalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.15" footer="0.2"/>
@@ -5054,7 +5189,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS12&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="R2e185cff09a148d6"/>
+    <tablePart ns1:id="R7ddeb504eec349da"/>
   </tableParts>
 </worksheet>
 </file>
@@ -6398,7 +6533,7 @@
     <mergeCell ref="B33:G33"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B6" location="'Contents'!B2" display="Contents" tooltip="Return to contents"/>
+    <hyperlink ref="B6" location="'Contents'!B2"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0" horizontalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.15" footer="0.2"/>
@@ -6407,7 +6542,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS13&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="Rfbc29a51654c47ce"/>
+    <tablePart ns1:id="Re791832050fd4336"/>
   </tableParts>
 </worksheet>
 </file>
@@ -6975,7 +7110,7 @@
     <mergeCell ref="B28:E28"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B6" location="'Contents'!B2" display="Contents" tooltip="Return to contents"/>
+    <hyperlink ref="B6" location="'Contents'!B2"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0" horizontalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.15" footer="0.2"/>
@@ -6984,7 +7119,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS14&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="R5f4e38ca00d9404d"/>
+    <tablePart ns1:id="Rd418388cc8bc42e1"/>
   </tableParts>
 </worksheet>
 </file>
@@ -7698,7 +7833,7 @@
     <mergeCell ref="B29:G29"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B6" location="'Contents'!B2" display="Contents" tooltip="Return to contents"/>
+    <hyperlink ref="B6" location="'Contents'!B2"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0" horizontalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.15" footer="0.2"/>
@@ -7707,7 +7842,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS15&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="R30feec6dd44842c1"/>
+    <tablePart ns1:id="Ra4a5b576152c4c34"/>
   </tableParts>
 </worksheet>
 </file>
@@ -8423,7 +8558,7 @@
     <mergeCell ref="B20:G20"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B6" location="'Contents'!B2" display="Contents" tooltip="Return to contents"/>
+    <hyperlink ref="B6" location="'Contents'!B2"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0" horizontalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.15" footer="0.2"/>
@@ -8432,7 +8567,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS16&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="Rf4e5108588c742ff"/>
+    <tablePart ns1:id="R599a8289fa3f4e8e"/>
   </tableParts>
 </worksheet>
 </file>
@@ -10034,7 +10169,7 @@
     <mergeCell ref="B35:G35"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B6" location="'Contents'!B2" display="Contents" tooltip="Return to contents"/>
+    <hyperlink ref="B6" location="'Contents'!B2"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0" horizontalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.15" footer="0.2"/>
@@ -10043,7 +10178,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS17&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="R3e1f851e96244e95"/>
+    <tablePart ns1:id="R60520cd5c44a4706"/>
   </tableParts>
 </worksheet>
 </file>
@@ -11011,7 +11146,7 @@
     <mergeCell ref="B30:G30"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B6" location="'Contents'!B2" display="Contents" tooltip="Return to contents"/>
+    <hyperlink ref="B6" location="'Contents'!B2"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0" horizontalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.15" footer="0.2"/>
@@ -11020,7 +11155,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS18&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="Rbb122c67b0d34abc"/>
+    <tablePart ns1:id="R2ab19edbda1a458a"/>
   </tableParts>
 </worksheet>
 </file>
@@ -11816,7 +11951,7 @@
     <row r="27" ht="57" customHeight="1">
       <c r="A27" s="3"/>
       <c r="B27" s="12" t="str">
-        <v>All 36,249 PRIDE datasets released 2013–2025. Standard result files = corrected non-generated expanded mzIdentML/mzTab definition. Identifiable results = file names, archive members and table headers (lower bound). Contributor group = hashed PI contact.</v>
+        <v>All 36,249 PRIDE datasets released 2013–2025. Standard result files = corrected non-generated expanded mzIdentML/mzTab definition. Identifiable results = file names, archive members and table headers; rule-based detection with unmeasured sensitivity and false-positive rates. Contributor group = hashed PI contact.</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
@@ -12142,7 +12277,7 @@
     <mergeCell ref="B33:G33"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B6" location="'Contents'!B2" display="Contents" tooltip="Return to contents"/>
+    <hyperlink ref="B6" location="'Contents'!B2"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0" horizontalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.15" footer="0.2"/>
@@ -12151,7 +12286,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS1&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="Rbd7f472a9ec94ed9"/>
+    <tablePart ns1:id="Rc6e98756ec9648d6"/>
   </tableParts>
 </worksheet>
 </file>
@@ -17317,7 +17452,7 @@
     <mergeCell ref="B188:G188"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B6" location="'Contents'!B2" display="Contents" tooltip="Return to contents"/>
+    <hyperlink ref="B6" location="'Contents'!B2"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0" horizontalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.15" footer="0.2"/>
@@ -17326,7 +17461,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS19&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="R52443122152f4039"/>
+    <tablePart ns1:id="Rca6caec3cd2f46d1"/>
   </tableParts>
 </worksheet>
 </file>
@@ -17442,7 +17577,7 @@
         <v>0.66</v>
       </c>
       <c r="F8" s="64" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="G8" s="3"/>
     </row>
@@ -17458,10 +17593,10 @@
         <v>1.71</v>
       </c>
       <c r="E9" s="65" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="F9" s="65" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="G9" s="3"/>
     </row>
@@ -17477,10 +17612,10 @@
         <v>4.08</v>
       </c>
       <c r="E10" s="64" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="F10" s="64" t="n">
-        <v>7.26</v>
+        <v>6.65</v>
       </c>
       <c r="G10" s="3"/>
     </row>
@@ -17496,10 +17631,10 @@
         <v>1.39</v>
       </c>
       <c r="E11" s="65" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="F11" s="65" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G11" s="3"/>
     </row>
@@ -17515,10 +17650,10 @@
         <v>1.28</v>
       </c>
       <c r="E12" s="64" t="n">
-        <v>1.04</v>
+        <v>0.99</v>
       </c>
       <c r="F12" s="64" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G12" s="3"/>
     </row>
@@ -17534,10 +17669,10 @@
         <v>1.35</v>
       </c>
       <c r="E13" s="65" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="F13" s="65" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="G13" s="3"/>
     </row>
@@ -17648,10 +17783,10 @@
         <v>1.04</v>
       </c>
       <c r="E19" s="65" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="F19" s="65" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="G19" s="3"/>
     </row>
@@ -17667,10 +17802,10 @@
         <v>1.76</v>
       </c>
       <c r="E20" s="64" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="F20" s="64" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="G20" s="3"/>
     </row>
@@ -17686,10 +17821,10 @@
         <v>8.37</v>
       </c>
       <c r="E21" s="65" t="n">
-        <v>5.97</v>
+        <v>5.73</v>
       </c>
       <c r="F21" s="65" t="n">
-        <v>11.56</v>
+        <v>11.53</v>
       </c>
       <c r="G21" s="3"/>
     </row>
@@ -17705,10 +17840,10 @@
         <v>2</v>
       </c>
       <c r="E22" s="64" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="F22" s="64" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="G22" s="3"/>
     </row>
@@ -17724,10 +17859,10 @@
         <v>1.69</v>
       </c>
       <c r="E23" s="65" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="F23" s="65" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="G23" s="3"/>
     </row>
@@ -17743,10 +17878,10 @@
         <v>0.74</v>
       </c>
       <c r="E24" s="87" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="F24" s="87" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="G24" s="3"/>
     </row>
@@ -17813,7 +17948,7 @@
     <row r="31" ht="87" customHeight="1">
       <c r="A31" s="3"/>
       <c r="B31" s="12" t="str">
-        <v>Ridge binomial logit GLM with alpha 1e-4 and L1_wt 0; 200 contributor-group bootstrap draws. Predictors: standard files, detected DIA, SDRF, human and Thermo Fisher-only vendor assignment. Adjustment: release year, pooled field/software categories, log10 bytes floored at 1e6, log(1+citations) and missing-citation indicator. See Supplementary Methods for missingness and category reference levels. A4/A5 report crude rate ratios with 1000 group-bootstrap draws. A5 uses release year plus five calendar years among 2013-2020 releases. SDRF direction is not interpretable because files may be added after release.</v>
+        <v>Ridge binomial logit GLM with alpha 1e-4 and L1_wt 0; 2000 contributor-group bootstrap draws. Predictors: standard files, detected DIA, SDRF, human and Thermo Fisher-only vendor assignment. Adjustment: release year, pooled field/software categories, log10 bytes floored at 1e6, log(1+citations) and missing-citation indicator. See Supplementary Methods for missingness and category reference levels. A4/A5 report crude rate ratios with 1000 group-bootstrap draws. A5 uses release year plus five calendar years among 2013-2020 releases. SDRF direction is not interpretable because files may be added after release.</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
@@ -18006,7 +18141,7 @@
     <mergeCell ref="B37:F37"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B6" location="'Contents'!B2" display="Contents" tooltip="Return to contents"/>
+    <hyperlink ref="B6" location="'Contents'!B2"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0" horizontalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.15" footer="0.2"/>
@@ -18015,7 +18150,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS20&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="Ref800e8f925946d3"/>
+    <tablePart ns1:id="Rb6c95b097f144113"/>
   </tableParts>
 </worksheet>
 </file>
@@ -18152,13 +18287,15 @@
         <v>A3</v>
       </c>
       <c r="C10" s="58" t="str">
-        <v>The file classification matches independent references</v>
+        <v>Rule-based file classifications were checked against format references; sensitivity and false-positive rates were not independently measured.</v>
       </c>
       <c r="D10" s="58" t="str">
         <v>V</v>
       </c>
       <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
+      <c r="F10" s="58" t="str">
+        <v>Rule-based file classifications were checked against format references; sensitivity and false-positive rates were not independently measured.</v>
+      </c>
       <c r="G10" s="3"/>
     </row>
     <row r="11" ht="27" customHeight="1">
@@ -18227,16 +18364,16 @@
         <v>B2</v>
       </c>
       <c r="C15" s="59" t="str">
-        <v>Results identifiable only by their header (renamed or re-saved tool output)</v>
+        <v>Table headers identify additional candidate tool outputs. Model-assisted rule review is not independent validation; detected shares are not established lower bounds.</v>
       </c>
       <c r="D15" s="59" t="str">
         <v>S</v>
       </c>
       <c r="E15" s="59" t="str">
-        <v>survives (lower bound)</v>
+        <v>Detection finding retained; independent accuracy validation not performed</v>
       </c>
       <c r="F15" s="59" t="str">
-        <v>382/389 identified tables correctly attributed. Dataset shares under strict signatures: 42.7% and 71.7%. About half of the tables left unidentified are also tool outputs.</v>
+        <v>Table headers identify additional candidate tool outputs. Model-assisted rule review is not independent validation; detected shares are not established lower bounds.</v>
       </c>
       <c r="G15" s="3"/>
     </row>
@@ -18599,14 +18736,14 @@
         <v>G7</v>
       </c>
       <c r="C39" s="59" t="str">
-        <v>Detected DIA, human samples and Thermo Fisher-only vendor assignments associated with qualifying mentions; mentions do not establish reanalysis.</v>
+        <v>DIA and human datasets had higher adjusted odds of qualifying mentions. The Thermo Fisher-only interval included one with 2000 bootstrap draws. Mentions do not establish reanalysis.</v>
       </c>
       <c r="D39" s="59" t="str">
         <v>V</v>
       </c>
       <c r="E39" s="59"/>
       <c r="F39" s="59" t="str">
-        <v>Detected DIA, human samples and Thermo Fisher-only vendor assignments associated with qualifying mentions; mentions do not establish reanalysis.</v>
+        <v>DIA and human datasets had higher adjusted odds of qualifying mentions. The Thermo Fisher-only interval included one with 2000 bootstrap draws. Mentions do not establish reanalysis.</v>
       </c>
       <c r="G39" s="3"/>
     </row>
@@ -19826,7 +19963,7 @@
     <row r="121" ht="42" customHeight="1">
       <c r="A121" s="3"/>
       <c r="B121" s="12" t="str">
-        <v>Status: V verified; W weakened; S single analysis, not yet attacked; X dropped. attack_verdict and corrected_wording come from the robustness attacks and override status where present. Full numbers, denominators and caveats in Findings-ledger.md.</v>
+        <v>Historical review ledger: V verified in the original review; W weakened; S single analysis; X dropped. These labels are not independent validation. Corrected wording includes later reporting qualifications and supersedes historical claims. The 107 rows are not 107 freshly rerun tests. Source: Findings-ledger.md.</v>
       </c>
       <c r="C121" s="12"/>
       <c r="D121" s="12"/>
@@ -20030,7 +20167,7 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="B6" location="'Contents'!B2" display="Contents" tooltip="Return to contents"/>
+    <hyperlink ref="B6" location="'Contents'!B2"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0" horizontalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.15" footer="0.2"/>
@@ -20039,7 +20176,2955 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS21&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="Re6a747c84e6048eb"/>
+    <tablePart ns1:id="R632cee017eb349f8"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FF2E6F9E"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="3" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="43" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="49" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="32" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="25" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="25" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="66" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="56" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="121"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+    </row>
+    <row r="2" ht="25" customHeight="1">
+      <c r="A2" s="121"/>
+      <c r="B2" s="123" t="str">
+        <v>SUPPLEMENTARY TABLE S22</v>
+      </c>
+      <c r="C2" s="123"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="121"/>
+      <c r="G2" s="121"/>
+      <c r="H2" s="121"/>
+      <c r="I2" s="121"/>
+      <c r="J2" s="121"/>
+      <c r="K2" s="121"/>
+      <c r="L2" s="121"/>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="121"/>
+      <c r="B3" s="125" t="str">
+        <v>Supporting numerical comparisons</v>
+      </c>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="121"/>
+      <c r="F3" s="121"/>
+      <c r="G3" s="121"/>
+      <c r="H3" s="121"/>
+      <c r="I3" s="121"/>
+      <c r="J3" s="121"/>
+      <c r="K3" s="121"/>
+      <c r="L3" s="121"/>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="121"/>
+      <c r="B4" s="127" t="str">
+        <v>Supporting comparisons at manuscript reporting precision. Population, period and units accompany every estimate.</v>
+      </c>
+      <c r="C4" s="127"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121"/>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="121"/>
+      <c r="B5" s="128"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="128"/>
+      <c r="E5" s="121"/>
+      <c r="F5" s="121"/>
+      <c r="G5" s="121"/>
+      <c r="H5" s="121"/>
+      <c r="I5" s="121"/>
+      <c r="J5" s="121"/>
+      <c r="K5" s="121"/>
+      <c r="L5" s="121"/>
+    </row>
+    <row r="6" ht="25" customHeight="1">
+      <c r="A6" s="121"/>
+      <c r="B6" s="122" t="str">
+        <v>Contents</v>
+      </c>
+      <c r="C6" s="121"/>
+      <c r="D6" s="121"/>
+      <c r="E6" s="121"/>
+      <c r="F6" s="121"/>
+      <c r="G6" s="121"/>
+      <c r="H6" s="121"/>
+      <c r="I6" s="121"/>
+      <c r="J6" s="121"/>
+      <c r="K6" s="121"/>
+      <c r="L6" s="121"/>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="121"/>
+      <c r="B7" s="132" t="str">
+        <v>Comparison</v>
+      </c>
+      <c r="C7" s="132" t="str">
+        <v>Population</v>
+      </c>
+      <c r="D7" s="132" t="str">
+        <v>Period or comparison</v>
+      </c>
+      <c r="E7" s="132" t="str">
+        <v>Estimate</v>
+      </c>
+      <c r="F7" s="132" t="str">
+        <v>Lower bound</v>
+      </c>
+      <c r="G7" s="132" t="str">
+        <v>Upper bound</v>
+      </c>
+      <c r="H7" s="132" t="str">
+        <v>Meaning of bounds</v>
+      </c>
+      <c r="I7" s="132" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="J7" s="132" t="str">
+        <v>Definition or qualification</v>
+      </c>
+      <c r="K7" s="132" t="str">
+        <v>Source</v>
+      </c>
+      <c r="L7" s="121"/>
+    </row>
+    <row r="8" ht="43" customHeight="1">
+      <c r="A8" s="121"/>
+      <c r="B8" s="134" t="str">
+        <v>Distinct journals</v>
+      </c>
+      <c r="C8" s="134" t="str">
+        <v>Linked papers with known journal</v>
+      </c>
+      <c r="D8" s="134" t="str">
+        <v>2013</v>
+      </c>
+      <c r="E8" s="138" t="n">
+        <v>78</v>
+      </c>
+      <c r="F8" s="142"/>
+      <c r="G8" s="142"/>
+      <c r="H8" s="143" t="str"/>
+      <c r="I8" s="134" t="str">
+        <v>journals</v>
+      </c>
+      <c r="J8" s="134" t="str"/>
+      <c r="K8" s="134" t="str">
+        <v>Table S18</v>
+      </c>
+      <c r="L8" s="121"/>
+    </row>
+    <row r="9" ht="43" customHeight="1">
+      <c r="A9" s="121"/>
+      <c r="B9" s="135" t="str">
+        <v>Distinct journals</v>
+      </c>
+      <c r="C9" s="135" t="str">
+        <v>Linked papers with known journal</v>
+      </c>
+      <c r="D9" s="135" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E9" s="139" t="n">
+        <v>627</v>
+      </c>
+      <c r="F9" s="144"/>
+      <c r="G9" s="144"/>
+      <c r="H9" s="145" t="str"/>
+      <c r="I9" s="135" t="str">
+        <v>journals</v>
+      </c>
+      <c r="J9" s="135" t="str"/>
+      <c r="K9" s="135" t="str">
+        <v>Table S18</v>
+      </c>
+      <c r="L9" s="121"/>
+    </row>
+    <row r="10" ht="43" customHeight="1">
+      <c r="A10" s="121"/>
+      <c r="B10" s="134" t="str">
+        <v>Rarefied instrument richness</v>
+      </c>
+      <c r="C10" s="134" t="str">
+        <v>Equal-sized samples of 1,500 datasets</v>
+      </c>
+      <c r="D10" s="134" t="str">
+        <v>2013–2015</v>
+      </c>
+      <c r="E10" s="138" t="n">
+        <v>66</v>
+      </c>
+      <c r="F10" s="142"/>
+      <c r="G10" s="142"/>
+      <c r="H10" s="143" t="str"/>
+      <c r="I10" s="134" t="str">
+        <v>models</v>
+      </c>
+      <c r="J10" s="134" t="str">
+        <v>Richness did not increase despite more even model representation.</v>
+      </c>
+      <c r="K10" s="134" t="str">
+        <v>Table S3; Fig. 1b</v>
+      </c>
+      <c r="L10" s="121"/>
+    </row>
+    <row r="11" ht="43" customHeight="1">
+      <c r="A11" s="121"/>
+      <c r="B11" s="135" t="str">
+        <v>Rarefied instrument richness</v>
+      </c>
+      <c r="C11" s="135" t="str">
+        <v>Equal-sized samples of 1,500 datasets</v>
+      </c>
+      <c r="D11" s="135" t="str">
+        <v>2023–2025</v>
+      </c>
+      <c r="E11" s="139" t="n">
+        <v>62</v>
+      </c>
+      <c r="F11" s="144"/>
+      <c r="G11" s="144"/>
+      <c r="H11" s="145" t="str"/>
+      <c r="I11" s="135" t="str">
+        <v>models</v>
+      </c>
+      <c r="J11" s="135" t="str">
+        <v>Richness did not increase despite more even model representation.</v>
+      </c>
+      <c r="K11" s="135" t="str">
+        <v>Table S3; Fig. 1b</v>
+      </c>
+      <c r="L11" s="121"/>
+    </row>
+    <row r="12" ht="57" customHeight="1">
+      <c r="A12" s="121"/>
+      <c r="B12" s="134" t="str">
+        <v>Diversity comparisons</v>
+      </c>
+      <c r="C12" s="134" t="str">
+        <v>Contributor groups, journals, instrument models and species</v>
+      </c>
+      <c r="D12" s="134" t="str">
+        <v>2023–2025 versus 2013–2015</v>
+      </c>
+      <c r="E12" s="136"/>
+      <c r="F12" s="142"/>
+      <c r="G12" s="142"/>
+      <c r="H12" s="143" t="str"/>
+      <c r="I12" s="134" t="str"/>
+      <c r="J12" s="134" t="str">
+        <v>Direction agreed at orders 1 and 2. At order 2, tools, research subfields, countries and instrument vendors showed no detectable change.</v>
+      </c>
+      <c r="K12" s="134" t="str">
+        <v>Table S3</v>
+      </c>
+      <c r="L12" s="121"/>
+    </row>
+    <row r="13" ht="43" customHeight="1">
+      <c r="A13" s="121"/>
+      <c r="B13" s="135" t="str">
+        <v>Timing of effective-number increases</v>
+      </c>
+      <c r="C13" s="135" t="str">
+        <v>Instrument models, journals and tools</v>
+      </c>
+      <c r="D13" s="135" t="str">
+        <v>2013–2025</v>
+      </c>
+      <c r="E13" s="137"/>
+      <c r="F13" s="144"/>
+      <c r="G13" s="144"/>
+      <c r="H13" s="145" t="str"/>
+      <c r="I13" s="135" t="str"/>
+      <c r="J13" s="135" t="str">
+        <v>Instrument models mainly from 2020; journals until 2022; tools only in 2024 and 2025.</v>
+      </c>
+      <c r="K13" s="135" t="str">
+        <v>Table S2; Fig. 1a</v>
+      </c>
+      <c r="L13" s="121"/>
+    </row>
+    <row r="14" ht="43" customHeight="1">
+      <c r="A14" s="121"/>
+      <c r="B14" s="134" t="str">
+        <v>Human samples named</v>
+      </c>
+      <c r="C14" s="134" t="str">
+        <v>All released datasets</v>
+      </c>
+      <c r="D14" s="134" t="str">
+        <v>2013</v>
+      </c>
+      <c r="E14" s="138" t="n">
+        <v>41</v>
+      </c>
+      <c r="F14" s="142"/>
+      <c r="G14" s="142"/>
+      <c r="H14" s="143" t="str"/>
+      <c r="I14" s="134" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J14" s="134" t="str"/>
+      <c r="K14" s="134" t="str">
+        <v>Supplementary Fig. 9; Gallery/data/29-species.csv</v>
+      </c>
+      <c r="L14" s="121"/>
+    </row>
+    <row r="15" ht="43" customHeight="1">
+      <c r="A15" s="121"/>
+      <c r="B15" s="135" t="str">
+        <v>Human samples named</v>
+      </c>
+      <c r="C15" s="135" t="str">
+        <v>All released datasets</v>
+      </c>
+      <c r="D15" s="135" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E15" s="139" t="n">
+        <v>52</v>
+      </c>
+      <c r="F15" s="144"/>
+      <c r="G15" s="144"/>
+      <c r="H15" s="145" t="str"/>
+      <c r="I15" s="135" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J15" s="135" t="str"/>
+      <c r="K15" s="135" t="str">
+        <v>Supplementary Fig. 9; Gallery/data/29-species.csv</v>
+      </c>
+      <c r="L15" s="121"/>
+    </row>
+    <row r="16" ht="43" customHeight="1">
+      <c r="A16" s="121"/>
+      <c r="B16" s="134" t="str">
+        <v>Mouse samples named</v>
+      </c>
+      <c r="C16" s="134" t="str">
+        <v>All released datasets</v>
+      </c>
+      <c r="D16" s="134" t="str">
+        <v>2013</v>
+      </c>
+      <c r="E16" s="138" t="n">
+        <v>11</v>
+      </c>
+      <c r="F16" s="142"/>
+      <c r="G16" s="142"/>
+      <c r="H16" s="143" t="str"/>
+      <c r="I16" s="134" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J16" s="134" t="str"/>
+      <c r="K16" s="134" t="str">
+        <v>Supplementary Fig. 9; Gallery/data/29-species.csv</v>
+      </c>
+      <c r="L16" s="121"/>
+    </row>
+    <row r="17" ht="43" customHeight="1">
+      <c r="A17" s="121"/>
+      <c r="B17" s="135" t="str">
+        <v>Mouse samples named</v>
+      </c>
+      <c r="C17" s="135" t="str">
+        <v>All released datasets</v>
+      </c>
+      <c r="D17" s="135" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E17" s="139" t="n">
+        <v>19</v>
+      </c>
+      <c r="F17" s="144"/>
+      <c r="G17" s="144"/>
+      <c r="H17" s="145" t="str"/>
+      <c r="I17" s="135" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J17" s="135" t="str"/>
+      <c r="K17" s="135" t="str">
+        <v>Supplementary Fig. 9; Gallery/data/29-species.csv</v>
+      </c>
+      <c r="L17" s="121"/>
+    </row>
+    <row r="18" ht="43" customHeight="1">
+      <c r="A18" s="121"/>
+      <c r="B18" s="134" t="str">
+        <v>Neither human nor mouse named</v>
+      </c>
+      <c r="C18" s="134" t="str">
+        <v>354 contributor groups present in both periods</v>
+      </c>
+      <c r="D18" s="134" t="str">
+        <v>2013–2016</v>
+      </c>
+      <c r="E18" s="138" t="n">
+        <v>40</v>
+      </c>
+      <c r="F18" s="142"/>
+      <c r="G18" s="142"/>
+      <c r="H18" s="143" t="str"/>
+      <c r="I18" s="134" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J18" s="134" t="str"/>
+      <c r="K18" s="134" t="str">
+        <v>Findings-ledger.md; Supplementary Fig. 9</v>
+      </c>
+      <c r="L18" s="121"/>
+    </row>
+    <row r="19" ht="43" customHeight="1">
+      <c r="A19" s="121"/>
+      <c r="B19" s="135" t="str">
+        <v>Neither human nor mouse named</v>
+      </c>
+      <c r="C19" s="135" t="str">
+        <v>354 contributor groups present in both periods</v>
+      </c>
+      <c r="D19" s="135" t="str">
+        <v>2023–2025</v>
+      </c>
+      <c r="E19" s="139" t="n">
+        <v>32</v>
+      </c>
+      <c r="F19" s="144"/>
+      <c r="G19" s="144"/>
+      <c r="H19" s="145" t="str"/>
+      <c r="I19" s="135" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J19" s="135" t="str"/>
+      <c r="K19" s="135" t="str">
+        <v>Findings-ledger.md; Supplementary Fig. 9</v>
+      </c>
+      <c r="L19" s="121"/>
+    </row>
+    <row r="20" ht="43" customHeight="1">
+      <c r="A20" s="121"/>
+      <c r="B20" s="134" t="str">
+        <v>First-time contributor share</v>
+      </c>
+      <c r="C20" s="134" t="str">
+        <v>Groups with no earlier PRIDE release since 2013</v>
+      </c>
+      <c r="D20" s="134" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E20" s="138" t="n">
+        <v>44</v>
+      </c>
+      <c r="F20" s="142"/>
+      <c r="G20" s="142"/>
+      <c r="H20" s="143" t="str"/>
+      <c r="I20" s="134" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J20" s="134" t="str"/>
+      <c r="K20" s="134" t="str">
+        <v>Table S1; Fig. 1c,d</v>
+      </c>
+      <c r="L20" s="121"/>
+    </row>
+    <row r="21" ht="43" customHeight="1">
+      <c r="A21" s="121"/>
+      <c r="B21" s="135" t="str">
+        <v>Growth in country-resolved deposits</v>
+      </c>
+      <c r="C21" s="135" t="str">
+        <v>Datasets from groups with resolved country</v>
+      </c>
+      <c r="D21" s="135" t="str">
+        <v>2023–2025 versus 2016–2018</v>
+      </c>
+      <c r="E21" s="140" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F21" s="144"/>
+      <c r="G21" s="144"/>
+      <c r="H21" s="145" t="str"/>
+      <c r="I21" s="135" t="str">
+        <v>fold</v>
+      </c>
+      <c r="J21" s="135" t="str"/>
+      <c r="K21" s="135" t="str">
+        <v>Table S6; Fig. 1e–g</v>
+      </c>
+      <c r="L21" s="121"/>
+    </row>
+    <row r="22" ht="43" customHeight="1">
+      <c r="A22" s="121"/>
+      <c r="B22" s="134" t="str">
+        <v>Growth in deposits from China</v>
+      </c>
+      <c r="C22" s="134" t="str">
+        <v>Datasets from groups assigned to China</v>
+      </c>
+      <c r="D22" s="134" t="str">
+        <v>2023–2025 versus 2016–2018</v>
+      </c>
+      <c r="E22" s="141" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F22" s="142"/>
+      <c r="G22" s="142"/>
+      <c r="H22" s="143" t="str"/>
+      <c r="I22" s="134" t="str">
+        <v>fold</v>
+      </c>
+      <c r="J22" s="134" t="str">
+        <v>See S6 for the bootstrap bounds at source precision.</v>
+      </c>
+      <c r="K22" s="134" t="str">
+        <v>Table S6; Fig. 1e–g</v>
+      </c>
+      <c r="L22" s="121"/>
+    </row>
+    <row r="23" ht="43" customHeight="1">
+      <c r="A23" s="121"/>
+      <c r="B23" s="135" t="str">
+        <v>Growth in deposits from Germany</v>
+      </c>
+      <c r="C23" s="135" t="str">
+        <v>Datasets from groups assigned to Germany</v>
+      </c>
+      <c r="D23" s="135" t="str">
+        <v>2023–2025 versus 2016–2018</v>
+      </c>
+      <c r="E23" s="140" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F23" s="144"/>
+      <c r="G23" s="144"/>
+      <c r="H23" s="145" t="str"/>
+      <c r="I23" s="135" t="str">
+        <v>fold</v>
+      </c>
+      <c r="J23" s="135" t="str">
+        <v>See S6 for the bootstrap bounds at source precision.</v>
+      </c>
+      <c r="K23" s="135" t="str">
+        <v>Table S6; Fig. 1e–g</v>
+      </c>
+      <c r="L23" s="121"/>
+    </row>
+    <row r="24" ht="43" customHeight="1">
+      <c r="A24" s="121"/>
+      <c r="B24" s="134" t="str">
+        <v>China share of deposits</v>
+      </c>
+      <c r="C24" s="134" t="str">
+        <v>Country-resolved datasets</v>
+      </c>
+      <c r="D24" s="134" t="str">
+        <v>2013</v>
+      </c>
+      <c r="E24" s="138" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" s="142"/>
+      <c r="G24" s="142"/>
+      <c r="H24" s="143" t="str"/>
+      <c r="I24" s="134" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J24" s="134" t="str"/>
+      <c r="K24" s="134" t="str">
+        <v>Fig. 1e–g; Table S6</v>
+      </c>
+      <c r="L24" s="121"/>
+    </row>
+    <row r="25" ht="43" customHeight="1">
+      <c r="A25" s="121"/>
+      <c r="B25" s="135" t="str">
+        <v>China share of deposits</v>
+      </c>
+      <c r="C25" s="135" t="str">
+        <v>Country-resolved datasets</v>
+      </c>
+      <c r="D25" s="135" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E25" s="139" t="n">
+        <v>15</v>
+      </c>
+      <c r="F25" s="144"/>
+      <c r="G25" s="144"/>
+      <c r="H25" s="145" t="str"/>
+      <c r="I25" s="135" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J25" s="135" t="str"/>
+      <c r="K25" s="135" t="str">
+        <v>Fig. 1e–g; Table S6</v>
+      </c>
+      <c r="L25" s="121"/>
+    </row>
+    <row r="26" ht="43" customHeight="1">
+      <c r="A26" s="121"/>
+      <c r="B26" s="134" t="str">
+        <v>Eligible raw-run datasets</v>
+      </c>
+      <c r="C26" s="134" t="str">
+        <v>Datasets with run counts</v>
+      </c>
+      <c r="D26" s="134" t="str">
+        <v>2013–2016</v>
+      </c>
+      <c r="E26" s="138" t="n">
+        <v>2498</v>
+      </c>
+      <c r="F26" s="142"/>
+      <c r="G26" s="142"/>
+      <c r="H26" s="143" t="str"/>
+      <c r="I26" s="134" t="str">
+        <v>datasets</v>
+      </c>
+      <c r="J26" s="134" t="str"/>
+      <c r="K26" s="134" t="str">
+        <v>Table S8; Fig. 2a</v>
+      </c>
+      <c r="L26" s="121"/>
+    </row>
+    <row r="27" ht="43" customHeight="1">
+      <c r="A27" s="121"/>
+      <c r="B27" s="135" t="str">
+        <v>Eligible raw-run datasets</v>
+      </c>
+      <c r="C27" s="135" t="str">
+        <v>Datasets with run counts</v>
+      </c>
+      <c r="D27" s="135" t="str">
+        <v>2023–2025</v>
+      </c>
+      <c r="E27" s="139" t="n">
+        <v>15248</v>
+      </c>
+      <c r="F27" s="144"/>
+      <c r="G27" s="144"/>
+      <c r="H27" s="145" t="str"/>
+      <c r="I27" s="135" t="str">
+        <v>datasets</v>
+      </c>
+      <c r="J27" s="135" t="str"/>
+      <c r="K27" s="135" t="str">
+        <v>Table S8; Fig. 2a</v>
+      </c>
+      <c r="L27" s="121"/>
+    </row>
+    <row r="28" ht="43" customHeight="1">
+      <c r="A28" s="121"/>
+      <c r="B28" s="134" t="str">
+        <v>Share with at least 100 runs</v>
+      </c>
+      <c r="C28" s="134" t="str">
+        <v>Datasets with run counts</v>
+      </c>
+      <c r="D28" s="134" t="str">
+        <v>2013–2016</v>
+      </c>
+      <c r="E28" s="141" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F28" s="142"/>
+      <c r="G28" s="142"/>
+      <c r="H28" s="143" t="str"/>
+      <c r="I28" s="134" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J28" s="134" t="str"/>
+      <c r="K28" s="134" t="str">
+        <v>Table S8; Fig. 2b</v>
+      </c>
+      <c r="L28" s="121"/>
+    </row>
+    <row r="29" ht="43" customHeight="1">
+      <c r="A29" s="121"/>
+      <c r="B29" s="135" t="str">
+        <v>Share with at least 100 runs</v>
+      </c>
+      <c r="C29" s="135" t="str">
+        <v>Datasets with run counts</v>
+      </c>
+      <c r="D29" s="135" t="str">
+        <v>2023–2025</v>
+      </c>
+      <c r="E29" s="139" t="n">
+        <v>9</v>
+      </c>
+      <c r="F29" s="144"/>
+      <c r="G29" s="144"/>
+      <c r="H29" s="145" t="str"/>
+      <c r="I29" s="135" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J29" s="135" t="str"/>
+      <c r="K29" s="135" t="str">
+        <v>Table S8; Fig. 2b</v>
+      </c>
+      <c r="L29" s="121"/>
+    </row>
+    <row r="30" ht="43" customHeight="1">
+      <c r="A30" s="121"/>
+      <c r="B30" s="134" t="str">
+        <v>Mean channels per labelled dataset</v>
+      </c>
+      <c r="C30" s="134" t="str">
+        <v>Datasets using isobaric labelling</v>
+      </c>
+      <c r="D30" s="134" t="str">
+        <v>2014</v>
+      </c>
+      <c r="E30" s="138" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" s="142"/>
+      <c r="G30" s="142"/>
+      <c r="H30" s="143" t="str"/>
+      <c r="I30" s="134" t="str">
+        <v>channels</v>
+      </c>
+      <c r="J30" s="134" t="str">
+        <v>TMTpro replaced iTRAQ; channels distinguish samples measured together in a run.</v>
+      </c>
+      <c r="K30" s="134" t="str">
+        <v>Supplementary Fig. 8; Gallery/data/27-isobaric-plex.csv</v>
+      </c>
+      <c r="L30" s="121"/>
+    </row>
+    <row r="31" ht="43" customHeight="1">
+      <c r="A31" s="121"/>
+      <c r="B31" s="135" t="str">
+        <v>Mean channels per labelled dataset</v>
+      </c>
+      <c r="C31" s="135" t="str">
+        <v>Datasets using isobaric labelling</v>
+      </c>
+      <c r="D31" s="135" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E31" s="139" t="n">
+        <v>13</v>
+      </c>
+      <c r="F31" s="144"/>
+      <c r="G31" s="144"/>
+      <c r="H31" s="145" t="str"/>
+      <c r="I31" s="135" t="str">
+        <v>channels</v>
+      </c>
+      <c r="J31" s="135" t="str">
+        <v>TMTpro replaced iTRAQ; channels distinguish samples measured together in a run.</v>
+      </c>
+      <c r="K31" s="135" t="str">
+        <v>Supplementary Fig. 8; Gallery/data/27-isobaric-plex.csv</v>
+      </c>
+      <c r="L31" s="121"/>
+    </row>
+    <row r="32" ht="87" customHeight="1">
+      <c r="A32" s="121"/>
+      <c r="B32" s="134" t="str">
+        <v>Run-count sensitivity analyses</v>
+      </c>
+      <c r="C32" s="134" t="str">
+        <v>Alternative units, counts, composition and strata</v>
+      </c>
+      <c r="D32" s="134" t="str">
+        <v>2013–2016 versus 2023–2025</v>
+      </c>
+      <c r="E32" s="138" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" s="142"/>
+      <c r="G32" s="142"/>
+      <c r="H32" s="143" t="str"/>
+      <c r="I32" s="134" t="str">
+        <v>analyses</v>
+      </c>
+      <c r="J32" s="134" t="str">
+        <v>Combine datasets from the same paper; exact counts only; collapse fraction-numbered runs; reweight vendor, acquisition mode, labelling, species and submission type to the early composition; stratify by country. The overall median decline persisted.</v>
+      </c>
+      <c r="K32" s="134" t="str">
+        <v>Table S8; Fig. 2c</v>
+      </c>
+      <c r="L32" s="121"/>
+    </row>
+    <row r="33" ht="43" customHeight="1">
+      <c r="A33" s="121"/>
+      <c r="B33" s="135" t="str">
+        <v>Early Bruker subset</v>
+      </c>
+      <c r="C33" s="135" t="str">
+        <v>Datasets naming Bruker instruments in the run-count comparison</v>
+      </c>
+      <c r="D33" s="135" t="str">
+        <v>2013–2016</v>
+      </c>
+      <c r="E33" s="139" t="n">
+        <v>56</v>
+      </c>
+      <c r="F33" s="144"/>
+      <c r="G33" s="144"/>
+      <c r="H33" s="145" t="str"/>
+      <c r="I33" s="135" t="str">
+        <v>datasets</v>
+      </c>
+      <c r="J33" s="135" t="str">
+        <v>No detectable decrease for this subset, TMT-labelled datasets or SCIEX-labelled datasets.</v>
+      </c>
+      <c r="K33" s="135" t="str">
+        <v>Table S8</v>
+      </c>
+      <c r="L33" s="121"/>
+    </row>
+    <row r="34" ht="57" customHeight="1">
+      <c r="A34" s="121"/>
+      <c r="B34" s="134" t="str">
+        <v>Within-group versus pooled slope</v>
+      </c>
+      <c r="C34" s="134" t="str">
+        <v>3,456 groups contributing in multiple years; 23,486 datasets</v>
+      </c>
+      <c r="D34" s="134" t="str">
+        <v>Across the study years</v>
+      </c>
+      <c r="E34" s="138" t="n">
+        <v>38</v>
+      </c>
+      <c r="F34" s="142"/>
+      <c r="G34" s="142"/>
+      <c r="H34" s="143" t="str"/>
+      <c r="I34" s="134" t="str">
+        <v>% of pooled slope</v>
+      </c>
+      <c r="J34" s="134" t="str">
+        <v>Slopes of log2 raw-run counts on time, compared on the same datasets. This is not a decomposition of the median decline.</v>
+      </c>
+      <c r="K34" s="134" t="str">
+        <v>Findings-ledger.md; within-group analysis</v>
+      </c>
+      <c r="L34" s="121"/>
+    </row>
+    <row r="35" ht="43" customHeight="1">
+      <c r="A35" s="121"/>
+      <c r="B35" s="135" t="str">
+        <v>Median raw-run size by model</v>
+      </c>
+      <c r="C35" s="135" t="str">
+        <v>Eligible single-model datasets with exact run counts</v>
+      </c>
+      <c r="D35" s="135" t="str">
+        <v>LTQ Orbitrap</v>
+      </c>
+      <c r="E35" s="140" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F35" s="144"/>
+      <c r="G35" s="144"/>
+      <c r="H35" s="145" t="str"/>
+      <c r="I35" s="135" t="str">
+        <v>GB per run</v>
+      </c>
+      <c r="J35" s="135" t="str">
+        <v>Model references: Makarov2006 and Stewart2023. GB = 10^9 bytes.</v>
+      </c>
+      <c r="K35" s="135" t="str">
+        <v>Table S7; Fig. 2d</v>
+      </c>
+      <c r="L35" s="121"/>
+    </row>
+    <row r="36" ht="43" customHeight="1">
+      <c r="A36" s="121"/>
+      <c r="B36" s="134" t="str">
+        <v>Median raw-run size by model</v>
+      </c>
+      <c r="C36" s="134" t="str">
+        <v>Eligible single-model datasets with exact run counts</v>
+      </c>
+      <c r="D36" s="134" t="str">
+        <v>Orbitrap Astral</v>
+      </c>
+      <c r="E36" s="141" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="F36" s="142"/>
+      <c r="G36" s="142"/>
+      <c r="H36" s="143" t="str"/>
+      <c r="I36" s="134" t="str">
+        <v>GB per run</v>
+      </c>
+      <c r="J36" s="134" t="str">
+        <v>Model references: Makarov2006 and Stewart2023. GB = 10^9 bytes.</v>
+      </c>
+      <c r="K36" s="134" t="str">
+        <v>Table S7; Fig. 2d</v>
+      </c>
+      <c r="L36" s="121"/>
+    </row>
+    <row r="37" ht="43" customHeight="1">
+      <c r="A37" s="121"/>
+      <c r="B37" s="135" t="str">
+        <v>Instrument-mix component of run-size change</v>
+      </c>
+      <c r="C37" s="135" t="str">
+        <v>Single identified model and exact raw-run count</v>
+      </c>
+      <c r="D37" s="135" t="str">
+        <v>2023–2025 versus 2014–2016</v>
+      </c>
+      <c r="E37" s="140" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F37" s="144"/>
+      <c r="G37" s="144"/>
+      <c r="H37" s="145" t="str"/>
+      <c r="I37" s="135" t="str">
+        <v>fold</v>
+      </c>
+      <c r="J37" s="135" t="str">
+        <v>Decomposition of change in mean log10 bytes per run. No interval reported for this component in the manuscript.</v>
+      </c>
+      <c r="K37" s="135" t="str">
+        <v>Table S21, H1.4; Fig. 2d</v>
+      </c>
+      <c r="L37" s="121"/>
+    </row>
+    <row r="38" ht="43" customHeight="1">
+      <c r="A38" s="121"/>
+      <c r="B38" s="134" t="str">
+        <v>Within-model component of run-size change</v>
+      </c>
+      <c r="C38" s="134" t="str">
+        <v>Single identified model and exact raw-run count</v>
+      </c>
+      <c r="D38" s="134" t="str">
+        <v>2023–2025 versus 2014–2016</v>
+      </c>
+      <c r="E38" s="141" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F38" s="146" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G38" s="146" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H38" s="143" t="str">
+        <v>95% interval</v>
+      </c>
+      <c r="I38" s="134" t="str">
+        <v>fold</v>
+      </c>
+      <c r="J38" s="134" t="str">
+        <v>Decomposition of change in mean log10 bytes per run.</v>
+      </c>
+      <c r="K38" s="134" t="str">
+        <v>Table S21, H1.4; Fig. 2d</v>
+      </c>
+      <c r="L38" s="121"/>
+    </row>
+    <row r="39" ht="43" customHeight="1">
+      <c r="A39" s="121"/>
+      <c r="B39" s="135" t="str">
+        <v>Bytes held by largest 1% of deposits</v>
+      </c>
+      <c r="C39" s="135" t="str">
+        <v>All listed dataset bytes</v>
+      </c>
+      <c r="D39" s="135" t="str">
+        <v>2013–2025 releases</v>
+      </c>
+      <c r="E39" s="139" t="n">
+        <v>24</v>
+      </c>
+      <c r="F39" s="144"/>
+      <c r="G39" s="144"/>
+      <c r="H39" s="145" t="str"/>
+      <c r="I39" s="135" t="str">
+        <v>% of bytes</v>
+      </c>
+      <c r="J39" s="135" t="str"/>
+      <c r="K39" s="135" t="str">
+        <v>Fig. 2e; Findings-ledger.md</v>
+      </c>
+      <c r="L39" s="121"/>
+    </row>
+    <row r="40" ht="43" customHeight="1">
+      <c r="A40" s="121"/>
+      <c r="B40" s="134" t="str">
+        <v>Raw vendor-format files</v>
+      </c>
+      <c r="C40" s="134" t="str">
+        <v>All listed file bytes</v>
+      </c>
+      <c r="D40" s="134" t="str">
+        <v>2013–2025 releases</v>
+      </c>
+      <c r="E40" s="138" t="n">
+        <v>84</v>
+      </c>
+      <c r="F40" s="142"/>
+      <c r="G40" s="142"/>
+      <c r="H40" s="143" t="str"/>
+      <c r="I40" s="134" t="str">
+        <v>% of bytes</v>
+      </c>
+      <c r="J40" s="134" t="str"/>
+      <c r="K40" s="134" t="str">
+        <v>Fig. 2f; Supplementary Fig. 6</v>
+      </c>
+      <c r="L40" s="121"/>
+    </row>
+    <row r="41" ht="43" customHeight="1">
+      <c r="A41" s="121"/>
+      <c r="B41" s="135" t="str">
+        <v>Thermo Fisher share of instrument assignments</v>
+      </c>
+      <c r="C41" s="135" t="str">
+        <v>One count per identified dataset, split among named models</v>
+      </c>
+      <c r="D41" s="135" t="str">
+        <v>Annual values, 2013–2025</v>
+      </c>
+      <c r="E41" s="137"/>
+      <c r="F41" s="147" t="n">
+        <v>79</v>
+      </c>
+      <c r="G41" s="147" t="n">
+        <v>89</v>
+      </c>
+      <c r="H41" s="145" t="str">
+        <v>Observed annual range</v>
+      </c>
+      <c r="I41" s="135" t="str">
+        <v>% of fractional counts</v>
+      </c>
+      <c r="J41" s="135" t="str">
+        <v>Different from unweighted model shares in S7.</v>
+      </c>
+      <c r="K41" s="135" t="str">
+        <v>Fig. 3a; Gallery/data/14-fleet-history.csv</v>
+      </c>
+      <c r="L41" s="121"/>
+    </row>
+    <row r="42" ht="43" customHeight="1">
+      <c r="A42" s="121"/>
+      <c r="B42" s="134" t="str">
+        <v>Fractional instrument share: LTQ Orbitrap</v>
+      </c>
+      <c r="C42" s="134" t="str">
+        <v>One count per identified dataset, split among named models</v>
+      </c>
+      <c r="D42" s="134" t="str">
+        <v>2013; first year of series</v>
+      </c>
+      <c r="E42" s="138" t="n">
+        <v>40</v>
+      </c>
+      <c r="F42" s="142"/>
+      <c r="G42" s="142"/>
+      <c r="H42" s="143" t="str"/>
+      <c r="I42" s="134" t="str">
+        <v>% of fractional counts</v>
+      </c>
+      <c r="J42" s="134" t="str">
+        <v>The first-year LTQ Orbitrap value is left-censored.</v>
+      </c>
+      <c r="K42" s="134" t="str">
+        <v>Fig. 3a; Supplementary Fig. 2</v>
+      </c>
+      <c r="L42" s="121"/>
+    </row>
+    <row r="43" ht="43" customHeight="1">
+      <c r="A43" s="121"/>
+      <c r="B43" s="135" t="str">
+        <v>Fractional instrument share: Q Exactive</v>
+      </c>
+      <c r="C43" s="135" t="str">
+        <v>One count per identified dataset, split among named models</v>
+      </c>
+      <c r="D43" s="135" t="str">
+        <v>Peak year</v>
+      </c>
+      <c r="E43" s="139" t="n">
+        <v>38</v>
+      </c>
+      <c r="F43" s="144"/>
+      <c r="G43" s="144"/>
+      <c r="H43" s="145" t="str"/>
+      <c r="I43" s="135" t="str">
+        <v>% of fractional counts</v>
+      </c>
+      <c r="J43" s="135" t="str">
+        <v>The first-year LTQ Orbitrap value is left-censored.</v>
+      </c>
+      <c r="K43" s="135" t="str">
+        <v>Fig. 3a; Supplementary Fig. 2</v>
+      </c>
+      <c r="L43" s="121"/>
+    </row>
+    <row r="44" ht="43" customHeight="1">
+      <c r="A44" s="121"/>
+      <c r="B44" s="134" t="str">
+        <v>Fractional instrument share: Q Exactive HF</v>
+      </c>
+      <c r="C44" s="134" t="str">
+        <v>One count per identified dataset, split among named models</v>
+      </c>
+      <c r="D44" s="134" t="str">
+        <v>Peak year</v>
+      </c>
+      <c r="E44" s="138" t="n">
+        <v>19</v>
+      </c>
+      <c r="F44" s="142"/>
+      <c r="G44" s="142"/>
+      <c r="H44" s="143" t="str"/>
+      <c r="I44" s="134" t="str">
+        <v>% of fractional counts</v>
+      </c>
+      <c r="J44" s="134" t="str">
+        <v>The first-year LTQ Orbitrap value is left-censored.</v>
+      </c>
+      <c r="K44" s="134" t="str">
+        <v>Fig. 3a; Supplementary Fig. 2</v>
+      </c>
+      <c r="L44" s="121"/>
+    </row>
+    <row r="45" ht="43" customHeight="1">
+      <c r="A45" s="121"/>
+      <c r="B45" s="135" t="str">
+        <v>timsTOF-labelled datasets</v>
+      </c>
+      <c r="C45" s="135" t="str">
+        <v>Datasets in instrument-share analysis</v>
+      </c>
+      <c r="D45" s="135" t="str">
+        <v>2021</v>
+      </c>
+      <c r="E45" s="140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F45" s="144"/>
+      <c r="G45" s="144"/>
+      <c r="H45" s="145" t="str"/>
+      <c r="I45" s="135" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J45" s="135" t="str">
+        <v>Meier2021 described increasing use in 2021; deposits are not ownership records.</v>
+      </c>
+      <c r="K45" s="135" t="str">
+        <v>Fig. 3a; Gallery/data/14-fleet-history.csv</v>
+      </c>
+      <c r="L45" s="121"/>
+    </row>
+    <row r="46" ht="43" customHeight="1">
+      <c r="A46" s="121"/>
+      <c r="B46" s="134" t="str">
+        <v>timsTOF-labelled datasets</v>
+      </c>
+      <c r="C46" s="134" t="str">
+        <v>Datasets in instrument-share analysis</v>
+      </c>
+      <c r="D46" s="134" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E46" s="138" t="n">
+        <v>13</v>
+      </c>
+      <c r="F46" s="142"/>
+      <c r="G46" s="142"/>
+      <c r="H46" s="143" t="str"/>
+      <c r="I46" s="134" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J46" s="134" t="str">
+        <v>Meier2021 described increasing use in 2021; deposits are not ownership records.</v>
+      </c>
+      <c r="K46" s="134" t="str">
+        <v>Fig. 3a; Gallery/data/14-fleet-history.csv</v>
+      </c>
+      <c r="L46" s="121"/>
+    </row>
+    <row r="47" ht="43" customHeight="1">
+      <c r="A47" s="121"/>
+      <c r="B47" s="135" t="str">
+        <v>Software named: MaxQuant</v>
+      </c>
+      <c r="C47" s="135" t="str">
+        <v>All released datasets</v>
+      </c>
+      <c r="D47" s="135" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E47" s="139" t="n">
+        <v>28</v>
+      </c>
+      <c r="F47" s="144"/>
+      <c r="G47" s="144"/>
+      <c r="H47" s="145" t="str"/>
+      <c r="I47" s="135" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J47" s="135" t="str"/>
+      <c r="K47" s="135" t="str">
+        <v>Fig. 3c; Figure-data/Tool-year.csv</v>
+      </c>
+      <c r="L47" s="121"/>
+    </row>
+    <row r="48" ht="43" customHeight="1">
+      <c r="A48" s="121"/>
+      <c r="B48" s="134" t="str">
+        <v>Software named: Proteome Discoverer</v>
+      </c>
+      <c r="C48" s="134" t="str">
+        <v>All released datasets</v>
+      </c>
+      <c r="D48" s="134" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E48" s="138" t="n">
+        <v>20</v>
+      </c>
+      <c r="F48" s="142"/>
+      <c r="G48" s="142"/>
+      <c r="H48" s="143" t="str"/>
+      <c r="I48" s="134" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J48" s="134" t="str"/>
+      <c r="K48" s="134" t="str">
+        <v>Fig. 3c; Figure-data/Tool-year.csv</v>
+      </c>
+      <c r="L48" s="121"/>
+    </row>
+    <row r="49" ht="43" customHeight="1">
+      <c r="A49" s="121"/>
+      <c r="B49" s="135" t="str">
+        <v>Tool-country pairs with interval excluding 1</v>
+      </c>
+      <c r="C49" s="135" t="str">
+        <v>20 pairs of a tool and its developers’ country</v>
+      </c>
+      <c r="D49" s="135" t="str">
+        <v>Study cohort</v>
+      </c>
+      <c r="E49" s="139" t="n">
+        <v>11</v>
+      </c>
+      <c r="F49" s="144"/>
+      <c r="G49" s="144"/>
+      <c r="H49" s="145" t="str"/>
+      <c r="I49" s="135" t="str">
+        <v>pairs</v>
+      </c>
+      <c r="J49" s="135" t="str">
+        <v>95% interval excludes equal naming rates. Developers’ own laboratories included.</v>
+      </c>
+      <c r="K49" s="135" t="str">
+        <v>Fig. 3d; software-geography analysis</v>
+      </c>
+      <c r="L49" s="121"/>
+    </row>
+    <row r="50" ht="43" customHeight="1">
+      <c r="A50" s="121"/>
+      <c r="B50" s="134" t="str">
+        <v>Developer-country naming ratio: Spectronaut</v>
+      </c>
+      <c r="C50" s="134" t="str">
+        <v>Groups in Switzerland versus groups in all countries combined</v>
+      </c>
+      <c r="D50" s="134" t="str">
+        <v>Study cohort</v>
+      </c>
+      <c r="E50" s="141" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F50" s="142"/>
+      <c r="G50" s="142"/>
+      <c r="H50" s="143" t="str"/>
+      <c r="I50" s="134" t="str">
+        <v>fold</v>
+      </c>
+      <c r="J50" s="134" t="str">
+        <v>Examples from the reported tool-country comparison. Full intervals remain in Fig. 3d/source data.</v>
+      </c>
+      <c r="K50" s="134" t="str">
+        <v>Fig. 3d; software-geography analysis</v>
+      </c>
+      <c r="L50" s="121"/>
+    </row>
+    <row r="51" ht="43" customHeight="1">
+      <c r="A51" s="121"/>
+      <c r="B51" s="135" t="str">
+        <v>Developer-country naming ratio: Comet</v>
+      </c>
+      <c r="C51" s="135" t="str">
+        <v>Groups in United States versus groups in all countries combined</v>
+      </c>
+      <c r="D51" s="135" t="str">
+        <v>Study cohort</v>
+      </c>
+      <c r="E51" s="140" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F51" s="144"/>
+      <c r="G51" s="144"/>
+      <c r="H51" s="145" t="str"/>
+      <c r="I51" s="135" t="str">
+        <v>fold</v>
+      </c>
+      <c r="J51" s="135" t="str">
+        <v>Examples from the reported tool-country comparison. Full intervals remain in Fig. 3d/source data.</v>
+      </c>
+      <c r="K51" s="135" t="str">
+        <v>Fig. 3d; software-geography analysis</v>
+      </c>
+      <c r="L51" s="121"/>
+    </row>
+    <row r="52" ht="43" customHeight="1">
+      <c r="A52" s="121"/>
+      <c r="B52" s="134" t="str">
+        <v>Developer-country naming ratio: MaxQuant</v>
+      </c>
+      <c r="C52" s="134" t="str">
+        <v>Groups in Germany versus groups in all countries combined</v>
+      </c>
+      <c r="D52" s="134" t="str">
+        <v>Study cohort</v>
+      </c>
+      <c r="E52" s="141" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F52" s="142"/>
+      <c r="G52" s="142"/>
+      <c r="H52" s="143" t="str"/>
+      <c r="I52" s="134" t="str">
+        <v>fold</v>
+      </c>
+      <c r="J52" s="134" t="str">
+        <v>Examples from the reported tool-country comparison. Full intervals remain in Fig. 3d/source data.</v>
+      </c>
+      <c r="K52" s="134" t="str">
+        <v>Fig. 3d; software-geography analysis</v>
+      </c>
+      <c r="L52" s="121"/>
+    </row>
+    <row r="53" ht="43" customHeight="1">
+      <c r="A53" s="121"/>
+      <c r="B53" s="135" t="str">
+        <v>MaxQuant 1.6-series share by release year</v>
+      </c>
+      <c r="C53" s="135" t="str">
+        <v>MaxQuant datasets released in 2025 with recovered version</v>
+      </c>
+      <c r="D53" s="135" t="str">
+        <v>Release year 2025</v>
+      </c>
+      <c r="E53" s="139" t="n">
+        <v>47</v>
+      </c>
+      <c r="F53" s="144"/>
+      <c r="G53" s="144"/>
+      <c r="H53" s="145" t="str"/>
+      <c r="I53" s="135" t="str">
+        <v>% of versioned datasets</v>
+      </c>
+      <c r="J53" s="135" t="str">
+        <v>First recorded in PRIDE in 2017; a different denominator from submission-year shares.</v>
+      </c>
+      <c r="K53" s="135" t="str">
+        <v>Supplementary Fig. 4; Gallery/data/31-version-streams.csv</v>
+      </c>
+      <c r="L53" s="121"/>
+    </row>
+    <row r="54" ht="43" customHeight="1">
+      <c r="A54" s="121"/>
+      <c r="B54" s="134" t="str">
+        <v>MaxQuant 1.6-series share by submission year</v>
+      </c>
+      <c r="C54" s="134" t="str">
+        <v>361 versioned datasets among 576 submissions naming MaxQuant</v>
+      </c>
+      <c r="D54" s="134" t="str">
+        <v>Submission year 2025</v>
+      </c>
+      <c r="E54" s="138" t="n">
+        <v>40</v>
+      </c>
+      <c r="F54" s="146" t="n">
+        <v>34.27</v>
+      </c>
+      <c r="G54" s="146" t="n">
+        <v>46.58</v>
+      </c>
+      <c r="H54" s="143" t="str">
+        <v>95% interval</v>
+      </c>
+      <c r="I54" s="134" t="str">
+        <v>% of versioned datasets</v>
+      </c>
+      <c r="J54" s="134" t="str">
+        <v>Point estimate rounded as in prose; Table S12 gives 40.17%.</v>
+      </c>
+      <c r="K54" s="134" t="str">
+        <v>Table S12; Supplementary Fig. 4</v>
+      </c>
+      <c r="L54" s="121"/>
+    </row>
+    <row r="55" ht="43" customHeight="1">
+      <c r="A55" s="121"/>
+      <c r="B55" s="135" t="str">
+        <v>DIA-NN 1.8-series share by submission year</v>
+      </c>
+      <c r="C55" s="135" t="str">
+        <v>110 versioned datasets among 331 submissions naming DIA-NN</v>
+      </c>
+      <c r="D55" s="135" t="str">
+        <v>Submission year 2025</v>
+      </c>
+      <c r="E55" s="139" t="n">
+        <v>61</v>
+      </c>
+      <c r="F55" s="147" t="n">
+        <v>48</v>
+      </c>
+      <c r="G55" s="147" t="n">
+        <v>74</v>
+      </c>
+      <c r="H55" s="145" t="str">
+        <v>95% interval</v>
+      </c>
+      <c r="I55" s="135" t="str">
+        <v>% of versioned datasets</v>
+      </c>
+      <c r="J55" s="135" t="str">
+        <v>Rounded as in prose; Table S12 gives estimates and bounds at source precision.</v>
+      </c>
+      <c r="K55" s="135" t="str">
+        <v>Table S12; Supplementary Fig. 4</v>
+      </c>
+      <c r="L55" s="121"/>
+    </row>
+    <row r="56" ht="43" customHeight="1">
+      <c r="A56" s="121"/>
+      <c r="B56" s="134" t="str">
+        <v>Eligible identification-result datasets</v>
+      </c>
+      <c r="C56" s="134" t="str">
+        <v>All released datasets</v>
+      </c>
+      <c r="D56" s="134" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E56" s="138" t="n">
+        <v>6231</v>
+      </c>
+      <c r="F56" s="142"/>
+      <c r="G56" s="142"/>
+      <c r="H56" s="143" t="str"/>
+      <c r="I56" s="134" t="str">
+        <v>datasets</v>
+      </c>
+      <c r="J56" s="134" t="str"/>
+      <c r="K56" s="134" t="str">
+        <v>Table S1; Table S13</v>
+      </c>
+      <c r="L56" s="121"/>
+    </row>
+    <row r="57" ht="43" customHeight="1">
+      <c r="A57" s="121"/>
+      <c r="B57" s="135" t="str">
+        <v>Identifiable results: Top-level file names</v>
+      </c>
+      <c r="C57" s="135" t="str">
+        <v>All released datasets</v>
+      </c>
+      <c r="D57" s="135" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E57" s="139" t="n">
+        <v>59</v>
+      </c>
+      <c r="F57" s="144"/>
+      <c r="G57" s="144"/>
+      <c r="H57" s="145" t="str"/>
+      <c r="I57" s="135" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J57" s="135" t="str">
+        <v>Lower-bound detection, not validity or usability.</v>
+      </c>
+      <c r="K57" s="135" t="str">
+        <v>Table S13; Fig. 4c</v>
+      </c>
+      <c r="L57" s="121"/>
+    </row>
+    <row r="58" ht="43" customHeight="1">
+      <c r="A58" s="121"/>
+      <c r="B58" s="134" t="str">
+        <v>Identifiable results: Adding archive contents</v>
+      </c>
+      <c r="C58" s="134" t="str">
+        <v>All released datasets</v>
+      </c>
+      <c r="D58" s="134" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E58" s="138" t="n">
+        <v>68</v>
+      </c>
+      <c r="F58" s="142"/>
+      <c r="G58" s="142"/>
+      <c r="H58" s="143" t="str"/>
+      <c r="I58" s="134" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J58" s="134" t="str">
+        <v>Lower-bound detection, not validity or usability.</v>
+      </c>
+      <c r="K58" s="134" t="str">
+        <v>Table S13; Fig. 4c</v>
+      </c>
+      <c r="L58" s="121"/>
+    </row>
+    <row r="59" ht="43" customHeight="1">
+      <c r="A59" s="121"/>
+      <c r="B59" s="135" t="str">
+        <v>Identifiable results: Adding table headers</v>
+      </c>
+      <c r="C59" s="135" t="str">
+        <v>All released datasets</v>
+      </c>
+      <c r="D59" s="135" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E59" s="139" t="n">
+        <v>80</v>
+      </c>
+      <c r="F59" s="144"/>
+      <c r="G59" s="144"/>
+      <c r="H59" s="145" t="str"/>
+      <c r="I59" s="135" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J59" s="135" t="str">
+        <v>Lower-bound detection, not validity or usability.</v>
+      </c>
+      <c r="K59" s="135" t="str">
+        <v>Table S13; Fig. 4c</v>
+      </c>
+      <c r="L59" s="121"/>
+    </row>
+    <row r="60" ht="43" customHeight="1">
+      <c r="A60" s="121"/>
+      <c r="B60" s="134" t="str">
+        <v>Identifiable results at all search depths</v>
+      </c>
+      <c r="C60" s="134" t="str">
+        <v>All released datasets</v>
+      </c>
+      <c r="D60" s="134" t="str">
+        <v>2015</v>
+      </c>
+      <c r="E60" s="138" t="n">
+        <v>92</v>
+      </c>
+      <c r="F60" s="142"/>
+      <c r="G60" s="142"/>
+      <c r="H60" s="143" t="str"/>
+      <c r="I60" s="134" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J60" s="134" t="str">
+        <v>Compared with 80% in 2025.</v>
+      </c>
+      <c r="K60" s="134" t="str">
+        <v>Table S13; Fig. 4d</v>
+      </c>
+      <c r="L60" s="121"/>
+    </row>
+    <row r="61" ht="43" customHeight="1">
+      <c r="A61" s="121"/>
+      <c r="B61" s="135" t="str">
+        <v>Standard-result-file prevalence</v>
+      </c>
+      <c r="C61" s="135" t="str">
+        <v>All released datasets</v>
+      </c>
+      <c r="D61" s="135" t="str">
+        <v>Annual values since 2015</v>
+      </c>
+      <c r="E61" s="137"/>
+      <c r="F61" s="147" t="n">
+        <v>16</v>
+      </c>
+      <c r="G61" s="147" t="n">
+        <v>20</v>
+      </c>
+      <c r="H61" s="145" t="str">
+        <v>Observed annual range</v>
+      </c>
+      <c r="I61" s="135" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J61" s="135" t="str">
+        <v>Submitter-deposited mzIdentML or mzTab; repository-generated files excluded.</v>
+      </c>
+      <c r="K61" s="135" t="str">
+        <v>Table S13</v>
+      </c>
+      <c r="L61" s="121"/>
+    </row>
+    <row r="62" ht="43" customHeight="1">
+      <c r="A62" s="121"/>
+      <c r="B62" s="134" t="str">
+        <v>Standard result files: DIA-NN</v>
+      </c>
+      <c r="C62" s="134" t="str">
+        <v>Datasets naming a single analysis tool</v>
+      </c>
+      <c r="D62" s="134" t="str">
+        <v>Study cohort</v>
+      </c>
+      <c r="E62" s="141" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F62" s="142"/>
+      <c r="G62" s="142"/>
+      <c r="H62" s="143" t="str"/>
+      <c r="I62" s="134" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J62" s="134" t="str">
+        <v>Lowest and highest observed tool-specific rates, respectively.</v>
+      </c>
+      <c r="K62" s="134" t="str">
+        <v>Table S9; Fig. 4a</v>
+      </c>
+      <c r="L62" s="121"/>
+    </row>
+    <row r="63" ht="43" customHeight="1">
+      <c r="A63" s="121"/>
+      <c r="B63" s="135" t="str">
+        <v>Standard result files: MS-GF+</v>
+      </c>
+      <c r="C63" s="135" t="str">
+        <v>Datasets naming a single analysis tool</v>
+      </c>
+      <c r="D63" s="135" t="str">
+        <v>Study cohort</v>
+      </c>
+      <c r="E63" s="139" t="n">
+        <v>76</v>
+      </c>
+      <c r="F63" s="144"/>
+      <c r="G63" s="144"/>
+      <c r="H63" s="145" t="str"/>
+      <c r="I63" s="135" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J63" s="135" t="str">
+        <v>Lowest and highest observed tool-specific rates, respectively.</v>
+      </c>
+      <c r="K63" s="135" t="str">
+        <v>Table S9; Fig. 4a</v>
+      </c>
+      <c r="L63" s="121"/>
+    </row>
+    <row r="64" ht="43" customHeight="1">
+      <c r="A64" s="121"/>
+      <c r="B64" s="134" t="str">
+        <v>Standard files when export is optional</v>
+      </c>
+      <c r="C64" s="134" t="str">
+        <v>Datasets naming tools offering standard output as an option</v>
+      </c>
+      <c r="D64" s="134" t="str">
+        <v>Study cohort</v>
+      </c>
+      <c r="E64" s="138" t="n">
+        <v>15</v>
+      </c>
+      <c r="F64" s="148" t="n">
+        <v>14</v>
+      </c>
+      <c r="G64" s="148" t="n">
+        <v>18</v>
+      </c>
+      <c r="H64" s="143" t="str">
+        <v>95% interval</v>
+      </c>
+      <c r="I64" s="134" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J64" s="134" t="str"/>
+      <c r="K64" s="134" t="str">
+        <v>Table S10; Fig. 4b</v>
+      </c>
+      <c r="L64" s="121"/>
+    </row>
+    <row r="65" ht="43" customHeight="1">
+      <c r="A65" s="121"/>
+      <c r="B65" s="135" t="str">
+        <v>Default-export group size</v>
+      </c>
+      <c r="C65" s="135" t="str">
+        <v>MS-GF+ and MetaMorpheus only</v>
+      </c>
+      <c r="D65" s="135" t="str">
+        <v>Study cohort</v>
+      </c>
+      <c r="E65" s="139" t="n">
+        <v>144</v>
+      </c>
+      <c r="F65" s="144"/>
+      <c r="G65" s="144"/>
+      <c r="H65" s="145" t="str"/>
+      <c r="I65" s="135" t="str">
+        <v>datasets</v>
+      </c>
+      <c r="J65" s="135" t="str"/>
+      <c r="K65" s="135" t="str">
+        <v>Table S10; Fig. 4b</v>
+      </c>
+      <c r="L65" s="121"/>
+    </row>
+    <row r="66" ht="43" customHeight="1">
+      <c r="A66" s="121"/>
+      <c r="B66" s="134" t="str">
+        <v>MetaMorpheus deposits with standard files</v>
+      </c>
+      <c r="C66" s="134" t="str">
+        <v>Single-tool MetaMorpheus datasets</v>
+      </c>
+      <c r="D66" s="134" t="str">
+        <v>Study cohort</v>
+      </c>
+      <c r="E66" s="138" t="n">
+        <v>23</v>
+      </c>
+      <c r="F66" s="142"/>
+      <c r="G66" s="142"/>
+      <c r="H66" s="143" t="str"/>
+      <c r="I66" s="134" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J66" s="134" t="str">
+        <v>The tool writes standard files by default.</v>
+      </c>
+      <c r="K66" s="134" t="str">
+        <v>Table S9; Fig. 4a</v>
+      </c>
+      <c r="L66" s="121"/>
+    </row>
+    <row r="67" ht="43" customHeight="1">
+      <c r="A67" s="121"/>
+      <c r="B67" s="135" t="str">
+        <v>Software-mix component of standard-file change</v>
+      </c>
+      <c r="C67" s="135" t="str">
+        <v>Software families</v>
+      </c>
+      <c r="D67" s="135" t="str">
+        <v>2023–2025 versus 2019–2021</v>
+      </c>
+      <c r="E67" s="139" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F67" s="149" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="G67" s="149" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H67" s="145" t="str">
+        <v>95% interval</v>
+      </c>
+      <c r="I67" s="135" t="str">
+        <v>percentage points</v>
+      </c>
+      <c r="J67" s="135" t="str">
+        <v>Mainly growth of DIA-NN and Spectronaut and decline of Mascot.</v>
+      </c>
+      <c r="K67" s="135" t="str">
+        <v>Findings-ledger.md; standards-by-stack analysis</v>
+      </c>
+      <c r="L67" s="121"/>
+    </row>
+    <row r="68" ht="43" customHeight="1">
+      <c r="A68" s="121"/>
+      <c r="B68" s="134" t="str">
+        <v>Within-family component of standard-file change</v>
+      </c>
+      <c r="C68" s="134" t="str">
+        <v>Software families</v>
+      </c>
+      <c r="D68" s="134" t="str">
+        <v>2023–2025 versus 2019–2021</v>
+      </c>
+      <c r="E68" s="141" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F68" s="146" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G68" s="146" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H68" s="143" t="str">
+        <v>95% interval</v>
+      </c>
+      <c r="I68" s="134" t="str">
+        <v>percentage points</v>
+      </c>
+      <c r="J68" s="134" t="str"/>
+      <c r="K68" s="134" t="str">
+        <v>Findings-ledger.md; standards-by-stack analysis</v>
+      </c>
+      <c r="L68" s="121"/>
+    </row>
+    <row r="69" ht="43" customHeight="1">
+      <c r="A69" s="121"/>
+      <c r="B69" s="135" t="str">
+        <v>Standard-file prevalence without detected DIA</v>
+      </c>
+      <c r="C69" s="135" t="str">
+        <v>Datasets with no DIA detected</v>
+      </c>
+      <c r="D69" s="135" t="str">
+        <v>Annual values since 2020</v>
+      </c>
+      <c r="E69" s="137"/>
+      <c r="F69" s="147" t="n">
+        <v>19</v>
+      </c>
+      <c r="G69" s="147" t="n">
+        <v>21</v>
+      </c>
+      <c r="H69" s="145" t="str">
+        <v>Observed annual range</v>
+      </c>
+      <c r="I69" s="135" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J69" s="135" t="str"/>
+      <c r="K69" s="135" t="str">
+        <v>Findings-ledger.md; standards-by-stack analysis</v>
+      </c>
+      <c r="L69" s="121"/>
+    </row>
+    <row r="70" ht="43" customHeight="1">
+      <c r="A70" s="121"/>
+      <c r="B70" s="134" t="str">
+        <v>Detected DIA prevalence</v>
+      </c>
+      <c r="C70" s="134" t="str">
+        <v>All released datasets</v>
+      </c>
+      <c r="D70" s="134" t="str">
+        <v>2015</v>
+      </c>
+      <c r="E70" s="141" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F70" s="142"/>
+      <c r="G70" s="142"/>
+      <c r="H70" s="143" t="str"/>
+      <c r="I70" s="134" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J70" s="134" t="str"/>
+      <c r="K70" s="134" t="str">
+        <v>Table S1; standards-by-stack analysis</v>
+      </c>
+      <c r="L70" s="121"/>
+    </row>
+    <row r="71" ht="43" customHeight="1">
+      <c r="A71" s="121"/>
+      <c r="B71" s="135" t="str">
+        <v>Detected DIA prevalence</v>
+      </c>
+      <c r="C71" s="135" t="str">
+        <v>All released datasets</v>
+      </c>
+      <c r="D71" s="135" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E71" s="140" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F71" s="144"/>
+      <c r="G71" s="144"/>
+      <c r="H71" s="145" t="str"/>
+      <c r="I71" s="135" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J71" s="135" t="str"/>
+      <c r="K71" s="135" t="str">
+        <v>Table S1; standards-by-stack analysis</v>
+      </c>
+      <c r="L71" s="121"/>
+    </row>
+    <row r="72" ht="43" customHeight="1">
+      <c r="A72" s="121"/>
+      <c r="B72" s="134" t="str">
+        <v>Standard-file prevalence with detected DIA</v>
+      </c>
+      <c r="C72" s="134" t="str">
+        <v>Datasets with DIA detected</v>
+      </c>
+      <c r="D72" s="134" t="str">
+        <v>2023–2025</v>
+      </c>
+      <c r="E72" s="138" t="n">
+        <v>3</v>
+      </c>
+      <c r="F72" s="142"/>
+      <c r="G72" s="142"/>
+      <c r="H72" s="143" t="str"/>
+      <c r="I72" s="134" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J72" s="134" t="str">
+        <v>Approximately 3%, as reported in prose.</v>
+      </c>
+      <c r="K72" s="134" t="str">
+        <v>Findings-ledger.md; standards-by-stack analysis</v>
+      </c>
+      <c r="L72" s="121"/>
+    </row>
+    <row r="73" ht="57" customHeight="1">
+      <c r="A73" s="121"/>
+      <c r="B73" s="135" t="str">
+        <v>Uncompressed results-archive storage: Scan-level and intermediate search outputs</v>
+      </c>
+      <c r="C73" s="135" t="str">
+        <v>Bytes in uncompressed results archives</v>
+      </c>
+      <c r="D73" s="135" t="str">
+        <v>Study cohort</v>
+      </c>
+      <c r="E73" s="139" t="n">
+        <v>66</v>
+      </c>
+      <c r="F73" s="144"/>
+      <c r="G73" s="144"/>
+      <c r="H73" s="145" t="str"/>
+      <c r="I73" s="135" t="str">
+        <v>% of bytes</v>
+      </c>
+      <c r="J73" s="135" t="str"/>
+      <c r="K73" s="135" t="str">
+        <v>Supplementary Fig. 6</v>
+      </c>
+      <c r="L73" s="121"/>
+    </row>
+    <row r="74" ht="43" customHeight="1">
+      <c r="A74" s="121"/>
+      <c r="B74" s="134" t="str">
+        <v>Uncompressed results-archive storage: Final result tables</v>
+      </c>
+      <c r="C74" s="134" t="str">
+        <v>Bytes in uncompressed results archives</v>
+      </c>
+      <c r="D74" s="134" t="str">
+        <v>Study cohort</v>
+      </c>
+      <c r="E74" s="141" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F74" s="142"/>
+      <c r="G74" s="142"/>
+      <c r="H74" s="143" t="str"/>
+      <c r="I74" s="134" t="str">
+        <v>% of bytes</v>
+      </c>
+      <c r="J74" s="134" t="str"/>
+      <c r="K74" s="134" t="str">
+        <v>Supplementary Fig. 6</v>
+      </c>
+      <c r="L74" s="121"/>
+    </row>
+    <row r="75" ht="43" customHeight="1">
+      <c r="A75" s="121"/>
+      <c r="B75" s="135" t="str">
+        <v>Spectra in open formats present</v>
+      </c>
+      <c r="C75" s="135" t="str">
+        <v>All released datasets</v>
+      </c>
+      <c r="D75" s="135" t="str">
+        <v>2013–2016</v>
+      </c>
+      <c r="E75" s="139" t="n">
+        <v>34</v>
+      </c>
+      <c r="F75" s="144"/>
+      <c r="G75" s="144"/>
+      <c r="H75" s="145" t="str"/>
+      <c r="I75" s="135" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J75" s="135" t="str"/>
+      <c r="K75" s="135" t="str">
+        <v>Supplementary Fig. 7; Gallery/data/30-file-formats-periods.csv</v>
+      </c>
+      <c r="L75" s="121"/>
+    </row>
+    <row r="76" ht="43" customHeight="1">
+      <c r="A76" s="121"/>
+      <c r="B76" s="134" t="str">
+        <v>Spectra in open formats present</v>
+      </c>
+      <c r="C76" s="134" t="str">
+        <v>All released datasets</v>
+      </c>
+      <c r="D76" s="134" t="str">
+        <v>2023–2025</v>
+      </c>
+      <c r="E76" s="138" t="n">
+        <v>21</v>
+      </c>
+      <c r="F76" s="142"/>
+      <c r="G76" s="142"/>
+      <c r="H76" s="143" t="str"/>
+      <c r="I76" s="134" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J76" s="134" t="str"/>
+      <c r="K76" s="134" t="str">
+        <v>Supplementary Fig. 7; Gallery/data/30-file-formats-periods.csv</v>
+      </c>
+      <c r="L76" s="121"/>
+    </row>
+    <row r="77" ht="43" customHeight="1">
+      <c r="A77" s="121"/>
+      <c r="B77" s="135" t="str">
+        <v>Contribution of complete-submission decline</v>
+      </c>
+      <c r="C77" s="135" t="str">
+        <v>Submissions classified as complete require peak lists</v>
+      </c>
+      <c r="D77" s="135" t="str">
+        <v>2013–2016 versus 2023–2025</v>
+      </c>
+      <c r="E77" s="137"/>
+      <c r="F77" s="147" t="n">
+        <v>5</v>
+      </c>
+      <c r="G77" s="147" t="n">
+        <v>10</v>
+      </c>
+      <c r="H77" s="145" t="str">
+        <v>Estimated contribution range</v>
+      </c>
+      <c r="I77" s="135" t="str">
+        <v>percentage points</v>
+      </c>
+      <c r="J77" s="135" t="str">
+        <v>Complete-submission share halved; contribution to the 13 percentage-point open-spectra decline.</v>
+      </c>
+      <c r="K77" s="135" t="str">
+        <v>Supplementary Fig. 7</v>
+      </c>
+      <c r="L77" s="121"/>
+    </row>
+    <row r="78" ht="43" customHeight="1">
+      <c r="A78" s="121"/>
+      <c r="B78" s="134" t="str">
+        <v>SDRF recurrence</v>
+      </c>
+      <c r="C78" s="134" t="str">
+        <v>Next dataset of a group whose previous dataset had SDRF</v>
+      </c>
+      <c r="D78" s="134" t="str">
+        <v>Study cohort</v>
+      </c>
+      <c r="E78" s="138" t="n">
+        <v>44</v>
+      </c>
+      <c r="F78" s="142"/>
+      <c r="G78" s="142"/>
+      <c r="H78" s="143" t="str"/>
+      <c r="I78" s="134" t="str">
+        <v>% of next datasets</v>
+      </c>
+      <c r="J78" s="134" t="str">
+        <v>Unadjusted for pairs submitted on the same day or linked to the same paper; includes retrospective additions.</v>
+      </c>
+      <c r="K78" s="134" t="str">
+        <v>Table S14; Fig. 4e</v>
+      </c>
+      <c r="L78" s="121"/>
+    </row>
+    <row r="79" ht="43" customHeight="1">
+      <c r="A79" s="121"/>
+      <c r="B79" s="135" t="str">
+        <v>Expected SDRF recurrence</v>
+      </c>
+      <c r="C79" s="135" t="str">
+        <v>Release-year-matched expectation</v>
+      </c>
+      <c r="D79" s="135" t="str">
+        <v>Study cohort</v>
+      </c>
+      <c r="E79" s="140" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F79" s="144"/>
+      <c r="G79" s="144"/>
+      <c r="H79" s="145" t="str"/>
+      <c r="I79" s="135" t="str">
+        <v>% of next datasets</v>
+      </c>
+      <c r="J79" s="135" t="str"/>
+      <c r="K79" s="135" t="str">
+        <v>Table S14; Fig. 4e</v>
+      </c>
+      <c r="L79" s="121"/>
+    </row>
+    <row r="80" ht="43" customHeight="1">
+      <c r="A80" s="121"/>
+      <c r="B80" s="134" t="str">
+        <v>SDRF presence</v>
+      </c>
+      <c r="C80" s="134" t="str">
+        <v>All released datasets</v>
+      </c>
+      <c r="D80" s="134" t="str">
+        <v>2020–2022</v>
+      </c>
+      <c r="E80" s="141" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F80" s="142"/>
+      <c r="G80" s="142"/>
+      <c r="H80" s="143" t="str"/>
+      <c r="I80" s="134" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J80" s="134" t="str"/>
+      <c r="K80" s="134" t="str">
+        <v>Findings-ledger.md; Fig. 4e</v>
+      </c>
+      <c r="L80" s="121"/>
+    </row>
+    <row r="81" ht="43" customHeight="1">
+      <c r="A81" s="121"/>
+      <c r="B81" s="135" t="str">
+        <v>SDRF presence</v>
+      </c>
+      <c r="C81" s="135" t="str">
+        <v>All released datasets</v>
+      </c>
+      <c r="D81" s="135" t="str">
+        <v>2023–2025</v>
+      </c>
+      <c r="E81" s="140" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F81" s="144"/>
+      <c r="G81" s="144"/>
+      <c r="H81" s="145" t="str"/>
+      <c r="I81" s="135" t="str">
+        <v>% of datasets</v>
+      </c>
+      <c r="J81" s="135" t="str"/>
+      <c r="K81" s="135" t="str">
+        <v>Findings-ledger.md; Fig. 4e</v>
+      </c>
+      <c r="L81" s="121"/>
+    </row>
+    <row r="82" ht="43" customHeight="1">
+      <c r="A82" s="121"/>
+      <c r="B82" s="134" t="str">
+        <v>Raw-file measurement-date coverage</v>
+      </c>
+      <c r="C82" s="134" t="str">
+        <v>11,868 dated datasets among 35,364 datasets with raw files</v>
+      </c>
+      <c r="D82" s="134" t="str">
+        <v>2013–2025 releases</v>
+      </c>
+      <c r="E82" s="138" t="n">
+        <v>34</v>
+      </c>
+      <c r="F82" s="142"/>
+      <c r="G82" s="142"/>
+      <c r="H82" s="143" t="str"/>
+      <c r="I82" s="134" t="str">
+        <v>% of raw-file datasets</v>
+      </c>
+      <c r="J82" s="134" t="str"/>
+      <c r="K82" s="134" t="str">
+        <v>Table S15; Fig. 5a</v>
+      </c>
+      <c r="L82" s="121"/>
+    </row>
+    <row r="83" ht="43" customHeight="1">
+      <c r="A83" s="121"/>
+      <c r="B83" s="135" t="str">
+        <v>Database date to public release</v>
+      </c>
+      <c r="C83" s="135" t="str">
+        <v>2,558 datasets with eligible sequence-database date</v>
+      </c>
+      <c r="D83" s="135" t="str">
+        <v>Study cohort</v>
+      </c>
+      <c r="E83" s="140" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F83" s="149" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G83" s="149" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H83" s="145" t="str">
+        <v>95% interval</v>
+      </c>
+      <c r="I83" s="135" t="str">
+        <v>years</v>
+      </c>
+      <c r="J83" s="135" t="str">
+        <v>Median interval; main dated FASTA represents a dataset.</v>
+      </c>
+      <c r="K83" s="135" t="str">
+        <v>Table S15; Fig. 5a</v>
+      </c>
+      <c r="L83" s="121"/>
+    </row>
+    <row r="84" ht="43" customHeight="1">
+      <c r="A84" s="121"/>
+      <c r="B84" s="134" t="str">
+        <v>Software first appearance to public release</v>
+      </c>
+      <c r="C84" s="134" t="str">
+        <v>10,466 datasets with recovered software-release timing</v>
+      </c>
+      <c r="D84" s="134" t="str">
+        <v>Study cohort</v>
+      </c>
+      <c r="E84" s="141" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F84" s="146" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G84" s="146" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H84" s="143" t="str">
+        <v>95% interval</v>
+      </c>
+      <c r="I84" s="134" t="str">
+        <v>years</v>
+      </c>
+      <c r="J84" s="134" t="str">
+        <v>Median is a lower bound measured from first recorded PRIDE appearance.</v>
+      </c>
+      <c r="K84" s="134" t="str">
+        <v>Table S11; Supplementary Fig. 5</v>
+      </c>
+      <c r="L84" s="121"/>
+    </row>
+    <row r="85" ht="43" customHeight="1">
+      <c r="A85" s="121"/>
+      <c r="B85" s="135" t="str">
+        <v>Database date precedes latest measurement</v>
+      </c>
+      <c r="C85" s="135" t="str">
+        <v>1,006 datasets with both relevant dates</v>
+      </c>
+      <c r="D85" s="135" t="str">
+        <v>Study cohort</v>
+      </c>
+      <c r="E85" s="139" t="n">
+        <v>71</v>
+      </c>
+      <c r="F85" s="144"/>
+      <c r="G85" s="144"/>
+      <c r="H85" s="145" t="str"/>
+      <c r="I85" s="135" t="str">
+        <v>% of paired datasets</v>
+      </c>
+      <c r="J85" s="135" t="str"/>
+      <c r="K85" s="135" t="str">
+        <v>Table S15; Fig. 5a</v>
+      </c>
+      <c r="L85" s="121"/>
+    </row>
+    <row r="86" ht="43" customHeight="1">
+      <c r="A86" s="121"/>
+      <c r="B86" s="134" t="str">
+        <v>Software first appearance precedes latest measurement</v>
+      </c>
+      <c r="C86" s="134" t="str">
+        <v>3,986 datasets with both relevant dates</v>
+      </c>
+      <c r="D86" s="134" t="str">
+        <v>Study cohort</v>
+      </c>
+      <c r="E86" s="138" t="n">
+        <v>79</v>
+      </c>
+      <c r="F86" s="142"/>
+      <c r="G86" s="142"/>
+      <c r="H86" s="143" t="str"/>
+      <c r="I86" s="134" t="str">
+        <v>% of paired datasets</v>
+      </c>
+      <c r="J86" s="134" t="str"/>
+      <c r="K86" s="134" t="str">
+        <v>Table S15; Fig. 5a</v>
+      </c>
+      <c r="L86" s="121"/>
+    </row>
+    <row r="87" ht="43" customHeight="1">
+      <c r="A87" s="121"/>
+      <c r="B87" s="135" t="str">
+        <v>Days with clustered public releases</v>
+      </c>
+      <c r="C87" s="135" t="str">
+        <v>At least 50 datasets made public on a day</v>
+      </c>
+      <c r="D87" s="135" t="str">
+        <v>From October 2018 onwards</v>
+      </c>
+      <c r="E87" s="139" t="n">
+        <v>62</v>
+      </c>
+      <c r="F87" s="144"/>
+      <c r="G87" s="144"/>
+      <c r="H87" s="145" t="str"/>
+      <c r="I87" s="135" t="str">
+        <v>days</v>
+      </c>
+      <c r="J87" s="135" t="str"/>
+      <c r="K87" s="135" t="str">
+        <v>Table S16; Supplementary Fig. 13</v>
+      </c>
+      <c r="L87" s="121"/>
+    </row>
+    <row r="88" ht="43" customHeight="1">
+      <c r="A88" s="121"/>
+      <c r="B88" s="134" t="str">
+        <v>Median publication-to-release delay</v>
+      </c>
+      <c r="C88" s="134" t="str">
+        <v>Days with at least 50 public releases</v>
+      </c>
+      <c r="D88" s="134" t="str">
+        <v>From October 2018 onwards</v>
+      </c>
+      <c r="E88" s="138" t="n">
+        <v>95</v>
+      </c>
+      <c r="F88" s="142"/>
+      <c r="G88" s="142"/>
+      <c r="H88" s="143" t="str"/>
+      <c r="I88" s="134" t="str">
+        <v>days</v>
+      </c>
+      <c r="J88" s="134" t="str">
+        <v>Who set the release date is not recorded.</v>
+      </c>
+      <c r="K88" s="134" t="str">
+        <v>Table S16; Supplementary Fig. 13</v>
+      </c>
+      <c r="L88" s="121"/>
+    </row>
+    <row r="89" ht="43" customHeight="1">
+      <c r="A89" s="121"/>
+      <c r="B89" s="135" t="str">
+        <v>Median publication-to-release delay</v>
+      </c>
+      <c r="C89" s="135" t="str">
+        <v>Other days</v>
+      </c>
+      <c r="D89" s="135" t="str">
+        <v>From October 2018 onwards</v>
+      </c>
+      <c r="E89" s="139" t="n">
+        <v>11</v>
+      </c>
+      <c r="F89" s="144"/>
+      <c r="G89" s="144"/>
+      <c r="H89" s="145" t="str"/>
+      <c r="I89" s="135" t="str">
+        <v>days</v>
+      </c>
+      <c r="J89" s="135" t="str">
+        <v>Who set the release date is not recorded.</v>
+      </c>
+      <c r="K89" s="135" t="str">
+        <v>Table S16; Supplementary Fig. 13</v>
+      </c>
+      <c r="L89" s="121"/>
+    </row>
+    <row r="90" ht="43" customHeight="1">
+      <c r="A90" s="121"/>
+      <c r="B90" s="134" t="str">
+        <v>Papers in journals with proteom in title</v>
+      </c>
+      <c r="C90" s="134" t="str">
+        <v>PRIDE-linked papers</v>
+      </c>
+      <c r="D90" s="134" t="str">
+        <v>2013</v>
+      </c>
+      <c r="E90" s="138" t="n">
+        <v>142</v>
+      </c>
+      <c r="F90" s="142"/>
+      <c r="G90" s="142"/>
+      <c r="H90" s="143" t="str"/>
+      <c r="I90" s="134" t="str">
+        <v>papers</v>
+      </c>
+      <c r="J90" s="134" t="str"/>
+      <c r="K90" s="134" t="str">
+        <v>Table S17; Fig. 5b,c</v>
+      </c>
+      <c r="L90" s="121"/>
+    </row>
+    <row r="91" ht="43" customHeight="1">
+      <c r="A91" s="121"/>
+      <c r="B91" s="135" t="str">
+        <v>Papers in journals with proteom in title</v>
+      </c>
+      <c r="C91" s="135" t="str">
+        <v>PRIDE-linked papers</v>
+      </c>
+      <c r="D91" s="135" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E91" s="139" t="n">
+        <v>259</v>
+      </c>
+      <c r="F91" s="144"/>
+      <c r="G91" s="144"/>
+      <c r="H91" s="145" t="str"/>
+      <c r="I91" s="135" t="str">
+        <v>papers</v>
+      </c>
+      <c r="J91" s="135" t="str"/>
+      <c r="K91" s="135" t="str">
+        <v>Table S17; Fig. 5b,c</v>
+      </c>
+      <c r="L91" s="121"/>
+    </row>
+    <row r="92" ht="43" customHeight="1">
+      <c r="A92" s="121"/>
+      <c r="B92" s="134" t="str">
+        <v>Top-ten journal concentration</v>
+      </c>
+      <c r="C92" s="134" t="str">
+        <v>PRIDE-linked papers</v>
+      </c>
+      <c r="D92" s="134" t="str">
+        <v>2013</v>
+      </c>
+      <c r="E92" s="138" t="n">
+        <v>66</v>
+      </c>
+      <c r="F92" s="142"/>
+      <c r="G92" s="142"/>
+      <c r="H92" s="143" t="str"/>
+      <c r="I92" s="134" t="str">
+        <v>% of papers</v>
+      </c>
+      <c r="J92" s="134" t="str"/>
+      <c r="K92" s="134" t="str">
+        <v>Table S18; Fig. 5c</v>
+      </c>
+      <c r="L92" s="121"/>
+    </row>
+    <row r="93" ht="43" customHeight="1">
+      <c r="A93" s="121"/>
+      <c r="B93" s="135" t="str">
+        <v>Top-ten journal concentration</v>
+      </c>
+      <c r="C93" s="135" t="str">
+        <v>PRIDE-linked papers</v>
+      </c>
+      <c r="D93" s="135" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E93" s="139" t="n">
+        <v>31</v>
+      </c>
+      <c r="F93" s="144"/>
+      <c r="G93" s="144"/>
+      <c r="H93" s="145" t="str"/>
+      <c r="I93" s="135" t="str">
+        <v>% of papers</v>
+      </c>
+      <c r="J93" s="135" t="str"/>
+      <c r="K93" s="135" t="str">
+        <v>Table S18; Fig. 5c</v>
+      </c>
+      <c r="L93" s="121"/>
+    </row>
+    <row r="94" ht="43" customHeight="1">
+      <c r="A94" s="121"/>
+      <c r="B94" s="134" t="str">
+        <v>Chemistry research-field assignment</v>
+      </c>
+      <c r="C94" s="134" t="str">
+        <v>Linked datasets with research-field assignment</v>
+      </c>
+      <c r="D94" s="134" t="str">
+        <v>2013</v>
+      </c>
+      <c r="E94" s="138" t="n">
+        <v>26</v>
+      </c>
+      <c r="F94" s="142"/>
+      <c r="G94" s="142"/>
+      <c r="H94" s="143" t="str"/>
+      <c r="I94" s="134" t="str">
+        <v>% of linked datasets</v>
+      </c>
+      <c r="J94" s="134" t="str">
+        <v>Almost all chemistry assignments were spectroscopy.</v>
+      </c>
+      <c r="K94" s="134" t="str">
+        <v>Supplementary Fig. 12; Gallery/data/36-research-fields-by-year.csv</v>
+      </c>
+      <c r="L94" s="121"/>
+    </row>
+    <row r="95" ht="43" customHeight="1">
+      <c r="A95" s="121"/>
+      <c r="B95" s="135" t="str">
+        <v>Chemistry research-field assignment</v>
+      </c>
+      <c r="C95" s="135" t="str">
+        <v>Linked datasets with research-field assignment</v>
+      </c>
+      <c r="D95" s="135" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E95" s="139" t="n">
+        <v>6</v>
+      </c>
+      <c r="F95" s="144"/>
+      <c r="G95" s="144"/>
+      <c r="H95" s="145" t="str"/>
+      <c r="I95" s="135" t="str">
+        <v>% of linked datasets</v>
+      </c>
+      <c r="J95" s="135" t="str">
+        <v>Almost all chemistry assignments were spectroscopy.</v>
+      </c>
+      <c r="K95" s="135" t="str">
+        <v>Supplementary Fig. 12; Gallery/data/36-research-fields-by-year.csv</v>
+      </c>
+      <c r="L95" s="121"/>
+    </row>
+    <row r="96" ht="43" customHeight="1">
+      <c r="A96" s="121"/>
+      <c r="B96" s="134" t="str">
+        <v>Medicine research-field assignment</v>
+      </c>
+      <c r="C96" s="134" t="str">
+        <v>Linked datasets with research-field assignment</v>
+      </c>
+      <c r="D96" s="134" t="str">
+        <v>2013</v>
+      </c>
+      <c r="E96" s="138" t="n">
+        <v>18</v>
+      </c>
+      <c r="F96" s="142"/>
+      <c r="G96" s="142"/>
+      <c r="H96" s="143" t="str"/>
+      <c r="I96" s="134" t="str">
+        <v>% of linked datasets</v>
+      </c>
+      <c r="J96" s="134" t="str"/>
+      <c r="K96" s="134" t="str">
+        <v>Supplementary Fig. 12; Gallery/data/36-research-fields-by-year.csv</v>
+      </c>
+      <c r="L96" s="121"/>
+    </row>
+    <row r="97" ht="43" customHeight="1">
+      <c r="A97" s="121"/>
+      <c r="B97" s="135" t="str">
+        <v>Medicine research-field assignment</v>
+      </c>
+      <c r="C97" s="135" t="str">
+        <v>Linked datasets with research-field assignment</v>
+      </c>
+      <c r="D97" s="135" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E97" s="139" t="n">
+        <v>29</v>
+      </c>
+      <c r="F97" s="144"/>
+      <c r="G97" s="144"/>
+      <c r="H97" s="145" t="str"/>
+      <c r="I97" s="135" t="str">
+        <v>% of linked datasets</v>
+      </c>
+      <c r="J97" s="135" t="str"/>
+      <c r="K97" s="135" t="str">
+        <v>Supplementary Fig. 12; Gallery/data/36-research-fields-by-year.csv</v>
+      </c>
+      <c r="L97" s="121"/>
+    </row>
+    <row r="98" ht="57" customHeight="1">
+      <c r="A98" s="121"/>
+      <c r="B98" s="134" t="str">
+        <v>Qualifying mention analysis population</v>
+      </c>
+      <c r="C98" s="134" t="str">
+        <v>Datasets released in 2013–2022</v>
+      </c>
+      <c r="D98" s="134" t="str">
+        <v>Release calendar year and next three calendar years</v>
+      </c>
+      <c r="E98" s="138" t="n">
+        <v>20684</v>
+      </c>
+      <c r="F98" s="142"/>
+      <c r="G98" s="142"/>
+      <c r="H98" s="143" t="str"/>
+      <c r="I98" s="134" t="str">
+        <v>datasets</v>
+      </c>
+      <c r="J98" s="134" t="str">
+        <v>Mentioning paper is not primary reference, names at least 2 contributor groups and no more than 100 datasets. Same-year chronology is unresolved.</v>
+      </c>
+      <c r="K98" s="134" t="str">
+        <v>Table S19; Methods</v>
+      </c>
+      <c r="L98" s="121"/>
+    </row>
+    <row r="99" ht="43" customHeight="1">
+      <c r="A99" s="121"/>
+      <c r="B99" s="135" t="str">
+        <v>Extended-window standard-file rate ratio</v>
+      </c>
+      <c r="C99" s="135" t="str">
+        <v>2013–2020 releases; 11,741 datasets</v>
+      </c>
+      <c r="D99" s="135" t="str">
+        <v>Release calendar year and next five calendar years</v>
+      </c>
+      <c r="E99" s="140" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="F99" s="149" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G99" s="149" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H99" s="145" t="str">
+        <v>95% interval</v>
+      </c>
+      <c r="I99" s="135" t="str">
+        <v>unadjusted rate ratio</v>
+      </c>
+      <c r="J99" s="135" t="str"/>
+      <c r="K99" s="135" t="str">
+        <v>Table S20; Supplementary Methods</v>
+      </c>
+      <c r="L99" s="121"/>
+    </row>
+    <row r="100" ht="57" customHeight="1">
+      <c r="A100" s="121"/>
+      <c r="B100" s="134" t="str">
+        <v>Restricted-cohort standard-file rate ratio</v>
+      </c>
+      <c r="C100" s="134" t="str">
+        <v>4,399 human datasets; Thermo Fisher only; no DIA detected; MaxQuant or Proteome Discoverer</v>
+      </c>
+      <c r="D100" s="134" t="str">
+        <v>2013–2022 releases; main mention window</v>
+      </c>
+      <c r="E100" s="141" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F100" s="146" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G100" s="146" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H100" s="143" t="str">
+        <v>95% interval</v>
+      </c>
+      <c r="I100" s="134" t="str">
+        <v>unadjusted rate ratio</v>
+      </c>
+      <c r="J100" s="134" t="str">
+        <v>These restrictions do not establish raw-file presence or confirm DDA.</v>
+      </c>
+      <c r="K100" s="134" t="str">
+        <v>Table S20; Supplementary Methods</v>
+      </c>
+      <c r="L100" s="121"/>
+    </row>
+    <row r="101" ht="43" customHeight="1">
+      <c r="A101" s="121"/>
+      <c r="B101" s="135" t="str">
+        <v>SDRF datasets released before format existed</v>
+      </c>
+      <c r="C101" s="135" t="str">
+        <v>205 SDRF datasets in the mention-model cohort</v>
+      </c>
+      <c r="D101" s="135" t="str">
+        <v>Release before availability of the SDRF format</v>
+      </c>
+      <c r="E101" s="139" t="n">
+        <v>91</v>
+      </c>
+      <c r="F101" s="144"/>
+      <c r="G101" s="144"/>
+      <c r="H101" s="145" t="str"/>
+      <c r="I101" s="135" t="str">
+        <v>datasets</v>
+      </c>
+      <c r="J101" s="135" t="str">
+        <v>Files added later, often through reanalysis projects; temporal direction of the association is unresolved.</v>
+      </c>
+      <c r="K101" s="135" t="str">
+        <v>Table S20; Findings-ledger.md</v>
+      </c>
+      <c r="L101" s="121"/>
+    </row>
+    <row r="102" ht="25" customHeight="1">
+      <c r="A102" s="121"/>
+      <c r="B102" s="121"/>
+      <c r="C102" s="121"/>
+      <c r="D102" s="121"/>
+      <c r="E102" s="121"/>
+      <c r="F102" s="121"/>
+      <c r="G102" s="121"/>
+      <c r="H102" s="121"/>
+      <c r="I102" s="121"/>
+      <c r="J102" s="121"/>
+      <c r="K102" s="121"/>
+      <c r="L102" s="121"/>
+    </row>
+    <row r="103" ht="25" customHeight="1">
+      <c r="A103" s="121"/>
+      <c r="B103" s="121"/>
+      <c r="C103" s="121"/>
+      <c r="D103" s="121"/>
+      <c r="E103" s="121"/>
+      <c r="F103" s="121"/>
+      <c r="G103" s="121"/>
+      <c r="H103" s="121"/>
+      <c r="I103" s="121"/>
+      <c r="J103" s="121"/>
+      <c r="K103" s="121"/>
+      <c r="L103" s="121"/>
+    </row>
+    <row r="104" ht="25" customHeight="1">
+      <c r="A104" s="121"/>
+      <c r="B104" s="123" t="str">
+        <v>Definition and provenance</v>
+      </c>
+      <c r="C104" s="123"/>
+      <c r="D104" s="123"/>
+      <c r="E104" s="121"/>
+      <c r="F104" s="121"/>
+      <c r="G104" s="121"/>
+      <c r="H104" s="121"/>
+      <c r="I104" s="121"/>
+      <c r="J104" s="121"/>
+      <c r="K104" s="121"/>
+      <c r="L104" s="121"/>
+    </row>
+    <row r="105" ht="70" customHeight="1">
+      <c r="A105" s="121"/>
+      <c r="B105" s="127" t="str">
+        <v>Reported comparisons supporting the Results. Values retain manuscript rounding; source tables retain full precision. Bounds are explicitly labelled as 95% intervals or observed/estimated ranges. Blank bounds mean no interval was reported here, not zero uncertainty. This is a curated reporting table, not a new analysis.</v>
+      </c>
+      <c r="C105" s="127"/>
+      <c r="D105" s="127"/>
+      <c r="E105" s="121"/>
+      <c r="F105" s="121"/>
+      <c r="G105" s="121"/>
+      <c r="H105" s="121"/>
+      <c r="I105" s="121"/>
+      <c r="J105" s="121"/>
+      <c r="K105" s="121"/>
+      <c r="L105" s="121"/>
+    </row>
+    <row r="106" ht="25" customHeight="1">
+      <c r="A106" s="121"/>
+      <c r="B106" s="121"/>
+      <c r="C106" s="121"/>
+      <c r="D106" s="121"/>
+      <c r="E106" s="121"/>
+      <c r="F106" s="121"/>
+      <c r="G106" s="121"/>
+      <c r="H106" s="121"/>
+      <c r="I106" s="121"/>
+      <c r="J106" s="121"/>
+      <c r="K106" s="121"/>
+      <c r="L106" s="121"/>
+    </row>
+    <row r="107" ht="25" customHeight="1">
+      <c r="A107" s="121"/>
+      <c r="B107" s="121"/>
+      <c r="C107" s="121"/>
+      <c r="D107" s="121"/>
+      <c r="E107" s="121"/>
+      <c r="F107" s="121"/>
+      <c r="G107" s="121"/>
+      <c r="H107" s="121"/>
+      <c r="I107" s="121"/>
+      <c r="J107" s="121"/>
+      <c r="K107" s="121"/>
+      <c r="L107" s="121"/>
+    </row>
+    <row r="108" ht="25" customHeight="1">
+      <c r="A108" s="121"/>
+      <c r="B108" s="121"/>
+      <c r="C108" s="121"/>
+      <c r="D108" s="121"/>
+      <c r="E108" s="121"/>
+      <c r="F108" s="121"/>
+      <c r="G108" s="121"/>
+      <c r="H108" s="121"/>
+      <c r="I108" s="121"/>
+      <c r="J108" s="121"/>
+      <c r="K108" s="121"/>
+      <c r="L108" s="121"/>
+    </row>
+    <row r="109" ht="25" customHeight="1">
+      <c r="A109" s="121"/>
+      <c r="B109" s="121"/>
+      <c r="C109" s="121"/>
+      <c r="D109" s="121"/>
+      <c r="E109" s="121"/>
+      <c r="F109" s="121"/>
+      <c r="G109" s="121"/>
+      <c r="H109" s="121"/>
+      <c r="I109" s="121"/>
+      <c r="J109" s="121"/>
+      <c r="K109" s="121"/>
+      <c r="L109" s="121"/>
+    </row>
+    <row r="110" ht="25" customHeight="1">
+      <c r="A110" s="121"/>
+      <c r="B110" s="121"/>
+      <c r="C110" s="121"/>
+      <c r="D110" s="121"/>
+      <c r="E110" s="121"/>
+      <c r="F110" s="121"/>
+      <c r="G110" s="121"/>
+      <c r="H110" s="121"/>
+      <c r="I110" s="121"/>
+      <c r="J110" s="121"/>
+      <c r="K110" s="121"/>
+      <c r="L110" s="121"/>
+    </row>
+    <row r="111" ht="25" customHeight="1">
+      <c r="A111" s="121"/>
+      <c r="B111" s="121"/>
+      <c r="C111" s="121"/>
+      <c r="D111" s="121"/>
+      <c r="E111" s="121"/>
+      <c r="F111" s="121"/>
+      <c r="G111" s="121"/>
+      <c r="H111" s="121"/>
+      <c r="I111" s="121"/>
+      <c r="J111" s="121"/>
+      <c r="K111" s="121"/>
+      <c r="L111" s="121"/>
+    </row>
+    <row r="112" ht="25" customHeight="1">
+      <c r="A112" s="121"/>
+      <c r="B112" s="121"/>
+      <c r="C112" s="121"/>
+      <c r="D112" s="121"/>
+      <c r="E112" s="121"/>
+      <c r="F112" s="121"/>
+      <c r="G112" s="121"/>
+      <c r="H112" s="121"/>
+      <c r="I112" s="121"/>
+      <c r="J112" s="121"/>
+      <c r="K112" s="121"/>
+      <c r="L112" s="121"/>
+    </row>
+    <row r="113" ht="25" customHeight="1">
+      <c r="A113" s="121"/>
+      <c r="B113" s="121"/>
+      <c r="C113" s="121"/>
+      <c r="D113" s="121"/>
+      <c r="E113" s="121"/>
+      <c r="F113" s="121"/>
+      <c r="G113" s="121"/>
+      <c r="H113" s="121"/>
+      <c r="I113" s="121"/>
+      <c r="J113" s="121"/>
+      <c r="K113" s="121"/>
+      <c r="L113" s="121"/>
+    </row>
+  </sheetData>
+  <mergeCells>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B105:D105"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B6" location="'Contents'!B2"/>
+  </hyperlinks>
+  <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.15" footer="0.15"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToWidth="1" fitToHeight="0"/>
+  <tableParts count="1">
+    <tablePart ns1:id="Rbc9541fcab6f4b64"/>
   </tableParts>
 </worksheet>
 </file>
@@ -22426,7 +25511,7 @@
     <mergeCell ref="B100:E100"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B6" location="'Contents'!B2" display="Contents" tooltip="Return to contents"/>
+    <hyperlink ref="B6" location="'Contents'!B2"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0" horizontalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.15" footer="0.2"/>
@@ -22435,7 +25520,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS2&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="R7ccc65d368944179"/>
+    <tablePart ns1:id="R02ce76a9f86743a9"/>
   </tableParts>
 </worksheet>
 </file>
@@ -23644,7 +26729,7 @@
     <mergeCell ref="B28:G28"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B6" location="'Contents'!B2" display="Contents" tooltip="Return to contents"/>
+    <hyperlink ref="B6" location="'Contents'!B2"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0" horizontalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.15" footer="0.2"/>
@@ -23653,7 +26738,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS3&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="Rb20cb82031ab44c5"/>
+    <tablePart ns1:id="Rff1044c4d2214aa0"/>
   </tableParts>
 </worksheet>
 </file>
@@ -24708,7 +27793,7 @@
     <mergeCell ref="B38:G38"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B6" location="'Contents'!B2" display="Contents" tooltip="Return to contents"/>
+    <hyperlink ref="B6" location="'Contents'!B2"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0" horizontalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.15" footer="0.2"/>
@@ -24717,7 +27802,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS4&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="R8f449789c18c440a"/>
+    <tablePart ns1:id="R9dc9331ec5454a3c"/>
   </tableParts>
 </worksheet>
 </file>
@@ -25313,7 +28398,7 @@
     <mergeCell ref="B24:E24"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B6" location="'Contents'!B2" display="Contents" tooltip="Return to contents"/>
+    <hyperlink ref="B6" location="'Contents'!B2"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0" horizontalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.15" footer="0.2"/>
@@ -25322,7 +28407,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS5&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="R4dbcff9f68df435f"/>
+    <tablePart ns1:id="R371660ae7aae4d55"/>
   </tableParts>
 </worksheet>
 </file>
@@ -28676,7 +31761,7 @@
     <mergeCell ref="B85:G85"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B6" location="'Contents'!B2" display="Contents" tooltip="Return to contents"/>
+    <hyperlink ref="B6" location="'Contents'!B2"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0" horizontalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.15" footer="0.2"/>
@@ -28685,7 +31770,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS6&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="R7b035b02cd9a40a6"/>
+    <tablePart ns1:id="R360651a9cbf74d87"/>
   </tableParts>
 </worksheet>
 </file>
@@ -31357,7 +34442,7 @@
     <mergeCell ref="B57:G57"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B6" location="'Contents'!B2" display="Contents" tooltip="Return to contents"/>
+    <hyperlink ref="B6" location="'Contents'!B2"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0" horizontalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.15" footer="0.2"/>
@@ -31366,7 +34451,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS7&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="R4b434d0cf46840e8"/>
+    <tablePart ns1:id="R92170317539a436e"/>
   </tableParts>
 </worksheet>
 </file>
@@ -38170,7 +41255,7 @@
     <mergeCell ref="B91:G91"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B6" location="'Contents'!B2" display="Contents" tooltip="Return to contents"/>
+    <hyperlink ref="B6" location="'Contents'!B2"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0" horizontalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.15" footer="0.2"/>
@@ -38179,7 +41264,7 @@
     <oddFooter>&amp;LPRIDE supplementary tables&amp;CS8&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart ns1:id="R39126c0ed6f94ee1"/>
+    <tablePart ns1:id="R015281d9c4794d98"/>
   </tableParts>
 </worksheet>
 </file>